--- a/phy112/Grades/grades_report_2026.xlsx
+++ b/phy112/Grades/grades_report_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ptohos/Documents/MyCourses/FYS112/2026/Grades/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E02832EE-607E-7A4E-AF65-FFE8DCADB801}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF11DF78-C4C2-D540-822A-83B593C2E4DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5600" yWindow="7060" windowWidth="32920" windowHeight="19260" tabRatio="334" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3060" yWindow="1200" windowWidth="32920" windowHeight="19260" tabRatio="334" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Quiz" sheetId="1" r:id="rId1"/>
@@ -352,7 +352,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -478,9 +478,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -992,15 +989,17 @@
       <c r="W1"/>
     </row>
     <row r="2" spans="1:23" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="52">
+      <c r="A2" s="51">
         <v>230</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50">
+      <c r="B2" s="49"/>
+      <c r="C2" s="49">
         <v>4</v>
       </c>
-      <c r="D2" s="45"/>
-      <c r="E2" s="50"/>
+      <c r="D2" s="49">
+        <v>16</v>
+      </c>
+      <c r="E2" s="49"/>
       <c r="F2" s="18"/>
       <c r="G2" s="18"/>
       <c r="H2" s="18"/>
@@ -1019,20 +1018,22 @@
       <c r="U2" s="18"/>
       <c r="V2" s="33">
         <f t="shared" ref="V2:V39" si="0">$V$42 * ( (SUM(B2:U2))/((SUM($B$46:$U$46))*$B$42) )</f>
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="W2"/>
     </row>
     <row r="3" spans="1:23" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="52">
+      <c r="A3" s="51">
         <v>434</v>
       </c>
-      <c r="B3" s="50"/>
-      <c r="C3" s="50">
+      <c r="B3" s="49"/>
+      <c r="C3" s="49">
         <v>12</v>
       </c>
-      <c r="D3" s="45"/>
-      <c r="E3" s="50"/>
+      <c r="D3" s="49">
+        <v>12</v>
+      </c>
+      <c r="E3" s="49"/>
       <c r="F3" s="18"/>
       <c r="G3" s="18"/>
       <c r="H3" s="18"/>
@@ -1047,7 +1048,7 @@
       <c r="Q3" s="18"/>
       <c r="R3" s="18"/>
       <c r="S3" s="18"/>
-      <c r="T3" s="51"/>
+      <c r="T3" s="50"/>
       <c r="U3" s="18"/>
       <c r="V3" s="33">
         <f t="shared" si="0"/>
@@ -1056,15 +1057,17 @@
       <c r="W3"/>
     </row>
     <row r="4" spans="1:23" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="52">
+      <c r="A4" s="51">
         <v>556</v>
       </c>
-      <c r="B4" s="50"/>
-      <c r="C4" s="50">
+      <c r="B4" s="49"/>
+      <c r="C4" s="49">
         <v>12</v>
       </c>
-      <c r="D4" s="45"/>
-      <c r="E4" s="50"/>
+      <c r="D4" s="49">
+        <v>16</v>
+      </c>
+      <c r="E4" s="49"/>
       <c r="F4" s="18"/>
       <c r="G4" s="18"/>
       <c r="H4" s="18"/>
@@ -1083,20 +1086,22 @@
       <c r="U4" s="18"/>
       <c r="V4" s="33">
         <f t="shared" si="0"/>
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="W4"/>
     </row>
     <row r="5" spans="1:23" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="52">
+      <c r="A5" s="51">
         <v>731</v>
       </c>
-      <c r="B5" s="50"/>
-      <c r="C5" s="50">
+      <c r="B5" s="49"/>
+      <c r="C5" s="49">
         <v>4</v>
       </c>
-      <c r="D5" s="45"/>
-      <c r="E5" s="50"/>
+      <c r="D5" s="49">
+        <v>4</v>
+      </c>
+      <c r="E5" s="49"/>
       <c r="F5" s="18"/>
       <c r="G5" s="18"/>
       <c r="H5" s="18"/>
@@ -1120,15 +1125,17 @@
       <c r="W5"/>
     </row>
     <row r="6" spans="1:23" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="52">
+      <c r="A6" s="51">
         <v>1032</v>
       </c>
-      <c r="B6" s="50"/>
-      <c r="C6" s="50">
+      <c r="B6" s="49"/>
+      <c r="C6" s="49">
         <v>16</v>
       </c>
-      <c r="D6" s="45"/>
-      <c r="E6" s="50"/>
+      <c r="D6" s="49">
+        <v>12</v>
+      </c>
+      <c r="E6" s="49"/>
       <c r="F6" s="18"/>
       <c r="G6" s="18"/>
       <c r="H6" s="18"/>
@@ -1147,20 +1154,22 @@
       <c r="U6" s="18"/>
       <c r="V6" s="33">
         <f t="shared" si="0"/>
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="W6"/>
     </row>
     <row r="7" spans="1:23" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="52">
+      <c r="A7" s="51">
         <v>1199</v>
       </c>
-      <c r="B7" s="50"/>
-      <c r="C7" s="50">
+      <c r="B7" s="49"/>
+      <c r="C7" s="49">
         <v>18</v>
       </c>
-      <c r="D7" s="45"/>
-      <c r="E7" s="50"/>
+      <c r="D7" s="49">
+        <v>18</v>
+      </c>
+      <c r="E7" s="49"/>
       <c r="F7" s="18"/>
       <c r="G7" s="18"/>
       <c r="H7" s="18"/>
@@ -1184,15 +1193,17 @@
       <c r="W7"/>
     </row>
     <row r="8" spans="1:23" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="52">
+      <c r="A8" s="51">
         <v>1653</v>
       </c>
-      <c r="B8" s="50"/>
-      <c r="C8" s="50">
+      <c r="B8" s="49"/>
+      <c r="C8" s="49">
         <v>16</v>
       </c>
-      <c r="D8" s="45"/>
-      <c r="E8" s="50"/>
+      <c r="D8" s="49">
+        <v>14</v>
+      </c>
+      <c r="E8" s="49"/>
       <c r="F8" s="18"/>
       <c r="G8" s="18"/>
       <c r="H8" s="18"/>
@@ -1211,18 +1222,20 @@
       <c r="U8" s="18"/>
       <c r="V8" s="33">
         <f t="shared" si="0"/>
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="W8"/>
     </row>
     <row r="9" spans="1:23" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="52">
+      <c r="A9" s="51">
         <v>1786</v>
       </c>
-      <c r="B9" s="50"/>
-      <c r="C9" s="50"/>
-      <c r="D9" s="45"/>
-      <c r="E9" s="50"/>
+      <c r="B9" s="49"/>
+      <c r="C9" s="49"/>
+      <c r="D9" s="49">
+        <v>12</v>
+      </c>
+      <c r="E9" s="49"/>
       <c r="F9" s="18"/>
       <c r="G9" s="18"/>
       <c r="H9" s="18"/>
@@ -1241,20 +1254,22 @@
       <c r="U9" s="18"/>
       <c r="V9" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W9"/>
     </row>
     <row r="10" spans="1:23" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="52">
+      <c r="A10" s="51">
         <v>2040</v>
       </c>
-      <c r="B10" s="50"/>
-      <c r="C10" s="50">
+      <c r="B10" s="49"/>
+      <c r="C10" s="49">
         <v>16</v>
       </c>
-      <c r="D10" s="45"/>
-      <c r="E10" s="50"/>
+      <c r="D10" s="49">
+        <v>12</v>
+      </c>
+      <c r="E10" s="49"/>
       <c r="F10" s="18"/>
       <c r="G10" s="18"/>
       <c r="H10" s="18"/>
@@ -1273,20 +1288,22 @@
       <c r="U10" s="18"/>
       <c r="V10" s="33">
         <f t="shared" si="0"/>
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="W10"/>
     </row>
     <row r="11" spans="1:23" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="52">
+      <c r="A11" s="51">
         <v>2283</v>
       </c>
-      <c r="B11" s="50"/>
-      <c r="C11" s="50">
+      <c r="B11" s="49"/>
+      <c r="C11" s="49">
         <v>4</v>
       </c>
-      <c r="D11" s="45"/>
-      <c r="E11" s="50"/>
+      <c r="D11" s="49">
+        <v>4</v>
+      </c>
+      <c r="E11" s="49"/>
       <c r="F11" s="18"/>
       <c r="G11" s="18"/>
       <c r="H11" s="18"/>
@@ -1310,15 +1327,17 @@
       <c r="W11"/>
     </row>
     <row r="12" spans="1:23" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="52">
+      <c r="A12" s="51">
         <v>2293</v>
       </c>
-      <c r="B12" s="50"/>
-      <c r="C12" s="50">
+      <c r="B12" s="49"/>
+      <c r="C12" s="49">
         <v>12</v>
       </c>
-      <c r="D12" s="45"/>
-      <c r="E12" s="50"/>
+      <c r="D12" s="49">
+        <v>12</v>
+      </c>
+      <c r="E12" s="49"/>
       <c r="F12" s="18"/>
       <c r="G12" s="18"/>
       <c r="H12" s="18"/>
@@ -1342,15 +1361,17 @@
       <c r="W12"/>
     </row>
     <row r="13" spans="1:23" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="52">
+      <c r="A13" s="51">
         <v>2376</v>
       </c>
-      <c r="B13" s="50"/>
-      <c r="C13" s="50">
+      <c r="B13" s="49"/>
+      <c r="C13" s="49">
         <v>12</v>
       </c>
-      <c r="D13" s="45"/>
-      <c r="E13" s="50"/>
+      <c r="D13" s="49">
+        <v>14</v>
+      </c>
+      <c r="E13" s="49"/>
       <c r="F13" s="18"/>
       <c r="G13" s="18"/>
       <c r="H13" s="18"/>
@@ -1369,20 +1390,22 @@
       <c r="U13" s="18"/>
       <c r="V13" s="33">
         <f t="shared" si="0"/>
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="W13"/>
     </row>
     <row r="14" spans="1:23" s="2" customFormat="1" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="52">
+      <c r="A14" s="51">
         <v>2438</v>
       </c>
-      <c r="B14" s="50"/>
-      <c r="C14" s="50">
+      <c r="B14" s="49"/>
+      <c r="C14" s="49">
         <v>16</v>
       </c>
-      <c r="D14" s="45"/>
-      <c r="E14" s="50"/>
+      <c r="D14" s="49">
+        <v>18</v>
+      </c>
+      <c r="E14" s="49"/>
       <c r="F14" s="18"/>
       <c r="G14" s="18"/>
       <c r="H14" s="18"/>
@@ -1401,19 +1424,21 @@
       <c r="U14" s="18"/>
       <c r="V14" s="33">
         <f t="shared" si="0"/>
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="15" spans="1:23" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="52">
+      <c r="A15" s="51">
         <v>2476</v>
       </c>
-      <c r="B15" s="50"/>
-      <c r="C15" s="50">
+      <c r="B15" s="49"/>
+      <c r="C15" s="49">
         <v>18</v>
       </c>
-      <c r="D15" s="45"/>
-      <c r="E15" s="50"/>
+      <c r="D15" s="49">
+        <v>20</v>
+      </c>
+      <c r="E15" s="49"/>
       <c r="F15" s="18"/>
       <c r="G15" s="18"/>
       <c r="H15" s="18"/>
@@ -1432,20 +1457,22 @@
       <c r="U15" s="18"/>
       <c r="V15" s="33">
         <f t="shared" si="0"/>
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="W15"/>
     </row>
     <row r="16" spans="1:23" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="52">
+      <c r="A16" s="51">
         <v>2979</v>
       </c>
-      <c r="B16" s="50"/>
-      <c r="C16" s="50">
+      <c r="B16" s="49"/>
+      <c r="C16" s="49">
         <v>4</v>
       </c>
-      <c r="D16" s="45"/>
-      <c r="E16" s="50"/>
+      <c r="D16" s="49">
+        <v>12</v>
+      </c>
+      <c r="E16" s="49"/>
       <c r="F16" s="18"/>
       <c r="G16" s="18"/>
       <c r="H16" s="18"/>
@@ -1464,18 +1491,18 @@
       <c r="U16" s="18"/>
       <c r="V16" s="33">
         <f t="shared" si="0"/>
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="W16"/>
     </row>
     <row r="17" spans="1:23" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="52">
+      <c r="A17" s="51">
         <v>3132</v>
       </c>
-      <c r="B17" s="50"/>
-      <c r="C17" s="50"/>
-      <c r="D17" s="45"/>
-      <c r="E17" s="50"/>
+      <c r="B17" s="49"/>
+      <c r="C17" s="49"/>
+      <c r="D17" s="49"/>
+      <c r="E17" s="49"/>
       <c r="F17" s="18"/>
       <c r="G17" s="18"/>
       <c r="H17" s="18"/>
@@ -1499,15 +1526,17 @@
       <c r="W17"/>
     </row>
     <row r="18" spans="1:23" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="52">
+      <c r="A18" s="51">
         <v>3183</v>
       </c>
-      <c r="B18" s="50"/>
-      <c r="C18" s="50">
+      <c r="B18" s="49"/>
+      <c r="C18" s="49">
         <v>14</v>
       </c>
-      <c r="D18" s="45"/>
-      <c r="E18" s="50"/>
+      <c r="D18" s="49">
+        <v>18</v>
+      </c>
+      <c r="E18" s="49"/>
       <c r="F18" s="18"/>
       <c r="G18" s="18"/>
       <c r="H18" s="18"/>
@@ -1526,20 +1555,22 @@
       <c r="U18" s="18"/>
       <c r="V18" s="33">
         <f t="shared" si="0"/>
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="W18"/>
     </row>
     <row r="19" spans="1:23" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="52">
+      <c r="A19" s="51">
         <v>3190</v>
       </c>
-      <c r="B19" s="50"/>
-      <c r="C19" s="50">
+      <c r="B19" s="49"/>
+      <c r="C19" s="49">
         <v>4</v>
       </c>
-      <c r="D19" s="45"/>
-      <c r="E19" s="50"/>
+      <c r="D19" s="49">
+        <v>14</v>
+      </c>
+      <c r="E19" s="49"/>
       <c r="F19" s="18"/>
       <c r="G19" s="18"/>
       <c r="H19" s="18"/>
@@ -1558,18 +1589,20 @@
       <c r="U19" s="18"/>
       <c r="V19" s="33">
         <f t="shared" si="0"/>
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="W19"/>
     </row>
     <row r="20" spans="1:23" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="52">
+      <c r="A20" s="51">
         <v>3192</v>
       </c>
-      <c r="B20" s="50"/>
-      <c r="C20" s="50"/>
-      <c r="D20" s="45"/>
-      <c r="E20" s="50"/>
+      <c r="B20" s="49"/>
+      <c r="C20" s="49"/>
+      <c r="D20" s="49">
+        <v>20</v>
+      </c>
+      <c r="E20" s="49"/>
       <c r="F20" s="18"/>
       <c r="G20" s="18"/>
       <c r="H20" s="18"/>
@@ -1588,20 +1621,22 @@
       <c r="U20" s="18"/>
       <c r="V20" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W20"/>
     </row>
     <row r="21" spans="1:23" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="52">
+      <c r="A21" s="51">
         <v>3217</v>
       </c>
-      <c r="B21" s="50"/>
-      <c r="C21" s="50">
+      <c r="B21" s="49"/>
+      <c r="C21" s="49">
         <v>16</v>
       </c>
-      <c r="D21" s="45"/>
-      <c r="E21" s="50"/>
+      <c r="D21" s="49">
+        <v>12</v>
+      </c>
+      <c r="E21" s="49"/>
       <c r="F21" s="18"/>
       <c r="G21" s="18"/>
       <c r="H21" s="18"/>
@@ -1620,20 +1655,22 @@
       <c r="U21" s="18"/>
       <c r="V21" s="33">
         <f t="shared" si="0"/>
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="W21"/>
     </row>
     <row r="22" spans="1:23" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="52">
+      <c r="A22" s="51">
         <v>3279</v>
       </c>
-      <c r="B22" s="50"/>
-      <c r="C22" s="50">
+      <c r="B22" s="49"/>
+      <c r="C22" s="49">
         <v>12</v>
       </c>
-      <c r="D22" s="45"/>
-      <c r="E22" s="50"/>
+      <c r="D22" s="49">
+        <v>14</v>
+      </c>
+      <c r="E22" s="49"/>
       <c r="F22" s="18"/>
       <c r="G22" s="18"/>
       <c r="H22" s="18"/>
@@ -1652,20 +1689,22 @@
       <c r="U22" s="18"/>
       <c r="V22" s="33">
         <f t="shared" si="0"/>
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="W22"/>
     </row>
     <row r="23" spans="1:23" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="52">
+      <c r="A23" s="51">
         <v>3360</v>
       </c>
-      <c r="B23" s="50"/>
-      <c r="C23" s="50">
+      <c r="B23" s="49"/>
+      <c r="C23" s="49">
         <v>18</v>
       </c>
-      <c r="D23" s="45"/>
-      <c r="E23" s="50"/>
+      <c r="D23" s="49">
+        <v>16</v>
+      </c>
+      <c r="E23" s="49"/>
       <c r="F23" s="18"/>
       <c r="G23" s="18"/>
       <c r="H23" s="18"/>
@@ -1684,18 +1723,20 @@
       <c r="U23" s="18"/>
       <c r="V23" s="33">
         <f t="shared" si="0"/>
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="W23"/>
     </row>
     <row r="24" spans="1:23" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="52">
+      <c r="A24" s="51">
         <v>3466</v>
       </c>
-      <c r="B24" s="50"/>
-      <c r="C24" s="50"/>
-      <c r="D24" s="45"/>
-      <c r="E24" s="50"/>
+      <c r="B24" s="49"/>
+      <c r="C24" s="49"/>
+      <c r="D24" s="49">
+        <v>12</v>
+      </c>
+      <c r="E24" s="49"/>
       <c r="F24" s="18"/>
       <c r="G24" s="18"/>
       <c r="H24" s="18"/>
@@ -1714,20 +1755,22 @@
       <c r="U24" s="18"/>
       <c r="V24" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W24"/>
     </row>
     <row r="25" spans="1:23" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="52">
+      <c r="A25" s="51">
         <v>3474</v>
       </c>
-      <c r="B25" s="50"/>
-      <c r="C25" s="50">
+      <c r="B25" s="49"/>
+      <c r="C25" s="49">
         <v>18</v>
       </c>
-      <c r="D25" s="45"/>
-      <c r="E25" s="50"/>
+      <c r="D25" s="49">
+        <v>20</v>
+      </c>
+      <c r="E25" s="49"/>
       <c r="F25" s="18"/>
       <c r="G25" s="18"/>
       <c r="H25" s="18"/>
@@ -1746,20 +1789,22 @@
       <c r="U25" s="18"/>
       <c r="V25" s="33">
         <f t="shared" si="0"/>
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="W25"/>
     </row>
     <row r="26" spans="1:23" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="52">
+      <c r="A26" s="51">
         <v>3481</v>
       </c>
-      <c r="B26" s="50"/>
-      <c r="C26" s="50">
+      <c r="B26" s="49"/>
+      <c r="C26" s="49">
         <v>12</v>
       </c>
-      <c r="D26" s="45"/>
-      <c r="E26" s="50"/>
+      <c r="D26" s="49">
+        <v>4</v>
+      </c>
+      <c r="E26" s="49"/>
       <c r="F26" s="18"/>
       <c r="G26" s="18"/>
       <c r="H26" s="18"/>
@@ -1778,20 +1823,20 @@
       <c r="U26" s="18"/>
       <c r="V26" s="33">
         <f t="shared" si="0"/>
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="W26"/>
     </row>
     <row r="27" spans="1:23" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="52">
+      <c r="A27" s="51">
         <v>4218</v>
       </c>
-      <c r="B27" s="50"/>
-      <c r="C27" s="50">
+      <c r="B27" s="49"/>
+      <c r="C27" s="49">
         <v>12</v>
       </c>
-      <c r="D27" s="45"/>
-      <c r="E27" s="50"/>
+      <c r="D27" s="49"/>
+      <c r="E27" s="49"/>
       <c r="F27" s="18"/>
       <c r="G27" s="18"/>
       <c r="H27" s="18"/>
@@ -1810,20 +1855,22 @@
       <c r="U27" s="18"/>
       <c r="V27" s="33">
         <f t="shared" si="0"/>
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="W27"/>
     </row>
     <row r="28" spans="1:23" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="52">
+      <c r="A28" s="51">
         <v>4365</v>
       </c>
-      <c r="B28" s="50"/>
-      <c r="C28" s="50">
+      <c r="B28" s="49"/>
+      <c r="C28" s="49">
         <v>12</v>
       </c>
-      <c r="D28" s="45"/>
-      <c r="E28" s="50"/>
+      <c r="D28" s="49">
+        <v>12</v>
+      </c>
+      <c r="E28" s="49"/>
       <c r="F28" s="18"/>
       <c r="G28" s="18"/>
       <c r="H28" s="18"/>
@@ -1847,15 +1894,17 @@
       <c r="W28"/>
     </row>
     <row r="29" spans="1:23" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="52">
+      <c r="A29" s="51">
         <v>4367</v>
       </c>
-      <c r="B29" s="50"/>
-      <c r="C29" s="50">
+      <c r="B29" s="49"/>
+      <c r="C29" s="49">
         <v>16</v>
       </c>
-      <c r="D29" s="45"/>
-      <c r="E29" s="50"/>
+      <c r="D29" s="49">
+        <v>14</v>
+      </c>
+      <c r="E29" s="49"/>
       <c r="F29" s="18"/>
       <c r="G29" s="18"/>
       <c r="H29" s="18"/>
@@ -1874,20 +1923,22 @@
       <c r="U29" s="18"/>
       <c r="V29" s="33">
         <f t="shared" si="0"/>
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="W29"/>
     </row>
     <row r="30" spans="1:23" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="52">
+      <c r="A30" s="51">
         <v>4434</v>
       </c>
-      <c r="B30" s="50"/>
-      <c r="C30" s="50">
+      <c r="B30" s="49"/>
+      <c r="C30" s="49">
         <v>12</v>
       </c>
-      <c r="D30" s="45"/>
-      <c r="E30" s="50"/>
+      <c r="D30" s="49">
+        <v>12</v>
+      </c>
+      <c r="E30" s="49"/>
       <c r="F30" s="18"/>
       <c r="G30" s="18"/>
       <c r="H30" s="18"/>
@@ -1911,15 +1962,17 @@
       <c r="W30"/>
     </row>
     <row r="31" spans="1:23" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="52">
+      <c r="A31" s="51">
         <v>4449</v>
       </c>
-      <c r="B31" s="50"/>
-      <c r="C31" s="50">
+      <c r="B31" s="49"/>
+      <c r="C31" s="49">
         <v>4</v>
       </c>
-      <c r="D31" s="45"/>
-      <c r="E31" s="50"/>
+      <c r="D31" s="49">
+        <v>14</v>
+      </c>
+      <c r="E31" s="49"/>
       <c r="F31" s="18"/>
       <c r="G31" s="18"/>
       <c r="H31" s="18"/>
@@ -1938,20 +1991,22 @@
       <c r="U31" s="18"/>
       <c r="V31" s="33">
         <f t="shared" si="0"/>
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="W31"/>
     </row>
     <row r="32" spans="1:23" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="52">
+      <c r="A32" s="51">
         <v>5282</v>
       </c>
-      <c r="B32" s="50"/>
-      <c r="C32" s="50">
+      <c r="B32" s="49"/>
+      <c r="C32" s="49">
         <v>12</v>
       </c>
-      <c r="D32" s="45"/>
-      <c r="E32" s="50"/>
+      <c r="D32" s="49">
+        <v>12</v>
+      </c>
+      <c r="E32" s="49"/>
       <c r="F32" s="18"/>
       <c r="G32" s="18"/>
       <c r="H32" s="18"/>
@@ -1975,13 +2030,13 @@
       <c r="W32"/>
     </row>
     <row r="33" spans="1:23" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="52">
+      <c r="A33" s="51">
         <v>6679</v>
       </c>
-      <c r="B33" s="50"/>
-      <c r="C33" s="50"/>
-      <c r="D33" s="45"/>
-      <c r="E33" s="50"/>
+      <c r="B33" s="49"/>
+      <c r="C33" s="49"/>
+      <c r="D33" s="49"/>
+      <c r="E33" s="49"/>
       <c r="F33" s="18"/>
       <c r="G33" s="18"/>
       <c r="H33" s="18"/>
@@ -2005,13 +2060,13 @@
       <c r="W33"/>
     </row>
     <row r="34" spans="1:23" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="52">
+      <c r="A34" s="51">
         <v>7596</v>
       </c>
-      <c r="B34" s="50"/>
-      <c r="C34" s="50"/>
-      <c r="D34" s="45"/>
-      <c r="E34" s="50"/>
+      <c r="B34" s="49"/>
+      <c r="C34" s="49"/>
+      <c r="D34" s="49"/>
+      <c r="E34" s="49"/>
       <c r="F34" s="18"/>
       <c r="G34" s="18"/>
       <c r="H34" s="18"/>
@@ -2035,15 +2090,17 @@
       <c r="W34"/>
     </row>
     <row r="35" spans="1:23" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="52">
+      <c r="A35" s="51">
         <v>7618</v>
       </c>
-      <c r="B35" s="50"/>
-      <c r="C35" s="50">
+      <c r="B35" s="49"/>
+      <c r="C35" s="49">
         <v>4</v>
       </c>
-      <c r="D35" s="45"/>
-      <c r="E35" s="50"/>
+      <c r="D35" s="49">
+        <v>14</v>
+      </c>
+      <c r="E35" s="49"/>
       <c r="F35" s="18"/>
       <c r="G35" s="18"/>
       <c r="H35" s="18"/>
@@ -2062,20 +2119,20 @@
       <c r="U35" s="18"/>
       <c r="V35" s="33">
         <f t="shared" si="0"/>
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="W35"/>
     </row>
     <row r="36" spans="1:23" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="52">
+      <c r="A36" s="51">
         <v>7630</v>
       </c>
-      <c r="B36" s="50"/>
-      <c r="C36" s="50">
+      <c r="B36" s="49"/>
+      <c r="C36" s="49">
         <v>12</v>
       </c>
-      <c r="D36" s="45"/>
-      <c r="E36" s="50"/>
+      <c r="D36" s="49"/>
+      <c r="E36" s="49"/>
       <c r="F36" s="18"/>
       <c r="G36" s="18"/>
       <c r="H36" s="18"/>
@@ -2094,20 +2151,22 @@
       <c r="U36" s="18"/>
       <c r="V36" s="33">
         <f t="shared" si="0"/>
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="W36"/>
     </row>
     <row r="37" spans="1:23" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="52">
+      <c r="A37" s="51">
         <v>7651</v>
       </c>
-      <c r="B37" s="50"/>
-      <c r="C37" s="50">
+      <c r="B37" s="49"/>
+      <c r="C37" s="49">
         <v>4</v>
       </c>
-      <c r="D37" s="45"/>
-      <c r="E37" s="50"/>
+      <c r="D37" s="49">
+        <v>14</v>
+      </c>
+      <c r="E37" s="49"/>
       <c r="F37" s="18"/>
       <c r="G37" s="18"/>
       <c r="H37" s="18"/>
@@ -2126,20 +2185,22 @@
       <c r="U37" s="18"/>
       <c r="V37" s="33">
         <f t="shared" si="0"/>
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="W37"/>
     </row>
     <row r="38" spans="1:23" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A38" s="52">
+      <c r="A38" s="51">
         <v>7776</v>
       </c>
-      <c r="B38" s="50"/>
-      <c r="C38" s="50">
+      <c r="B38" s="49"/>
+      <c r="C38" s="49">
         <v>12</v>
       </c>
-      <c r="D38" s="45"/>
-      <c r="E38" s="50"/>
+      <c r="D38" s="49">
+        <v>12</v>
+      </c>
+      <c r="E38" s="49"/>
       <c r="F38" s="18"/>
       <c r="G38" s="18"/>
       <c r="H38" s="18"/>
@@ -2163,15 +2224,17 @@
       <c r="W38"/>
     </row>
     <row r="39" spans="1:23" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A39" s="52">
+      <c r="A39" s="51">
         <v>9852</v>
       </c>
-      <c r="B39" s="50"/>
-      <c r="C39" s="50">
+      <c r="B39" s="49"/>
+      <c r="C39" s="49">
         <v>20</v>
       </c>
-      <c r="D39" s="45"/>
-      <c r="E39" s="50"/>
+      <c r="D39" s="49">
+        <v>16</v>
+      </c>
+      <c r="E39" s="49"/>
       <c r="F39" s="18"/>
       <c r="G39" s="18"/>
       <c r="H39" s="18"/>
@@ -2190,20 +2253,22 @@
       <c r="U39" s="18"/>
       <c r="V39" s="33">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="W39"/>
     </row>
     <row r="40" spans="1:23" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A40" s="52">
+      <c r="A40" s="51">
         <v>9951</v>
       </c>
-      <c r="B40" s="50"/>
-      <c r="C40" s="50">
+      <c r="B40" s="49"/>
+      <c r="C40" s="49">
         <v>16</v>
       </c>
-      <c r="D40" s="45"/>
-      <c r="E40" s="50"/>
+      <c r="D40" s="49">
+        <v>20</v>
+      </c>
+      <c r="E40" s="49"/>
       <c r="F40" s="18"/>
       <c r="G40" s="18"/>
       <c r="H40" s="18"/>
@@ -2222,7 +2287,7 @@
       <c r="U40" s="18"/>
       <c r="V40" s="33">
         <f t="shared" ref="V40" si="1">$V$42 * ( (SUM(B40:U40))/((SUM($B$46:$U$46))*$B$42) )</f>
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="W40"/>
     </row>
@@ -2332,9 +2397,9 @@
         <f t="shared" ref="C43:V43" si="2">AVERAGE(C$2:C$39)</f>
         <v>11.8125</v>
       </c>
-      <c r="D43" s="29" t="e">
+      <c r="D43" s="29">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+        <v>13.515151515151516</v>
       </c>
       <c r="E43" s="29" t="e">
         <f t="shared" si="2"/>
@@ -2406,7 +2471,7 @@
       </c>
       <c r="V43" s="29">
         <f t="shared" si="2"/>
-        <v>0.99473684210526303</v>
+        <v>1.0842105263157895</v>
       </c>
       <c r="W43"/>
     </row>
@@ -2422,9 +2487,9 @@
         <f t="shared" ref="C44:V44" si="3">STDEV(C$2:C$39)</f>
         <v>5.1395838917800694</v>
       </c>
-      <c r="D44" s="29" t="e">
+      <c r="D44" s="29">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
+        <v>4.0009468576295477</v>
       </c>
       <c r="E44" s="29" t="e">
         <f t="shared" si="3"/>
@@ -2496,7 +2561,7 @@
       </c>
       <c r="V44" s="29">
         <f t="shared" si="3"/>
-        <v>0.64176587817502262</v>
+        <v>0.52014879149297955</v>
       </c>
       <c r="W44"/>
     </row>
@@ -2512,9 +2577,9 @@
         <f t="shared" ref="C45:V45" si="4">MEDIAN(C$2:C$39)</f>
         <v>12</v>
       </c>
-      <c r="D45" s="29" t="e">
+      <c r="D45" s="29">
         <f t="shared" si="4"/>
-        <v>#NUM!</v>
+        <v>14</v>
       </c>
       <c r="E45" s="29" t="e">
         <f t="shared" si="4"/>
@@ -2604,7 +2669,7 @@
       </c>
       <c r="D46" s="32">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E46" s="32">
         <f t="shared" si="5"/>
@@ -2995,141 +3060,141 @@
       <c r="G1" s="22"/>
     </row>
     <row r="2" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="52">
+      <c r="A2" s="51">
         <v>230</v>
       </c>
       <c r="B2" s="41"/>
-      <c r="C2" s="50"/>
+      <c r="C2" s="49"/>
       <c r="D2" s="19"/>
       <c r="F2" s="19"/>
       <c r="G2" s="19"/>
     </row>
     <row r="3" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="52">
+      <c r="A3" s="51">
         <v>434</v>
       </c>
       <c r="B3" s="42"/>
-      <c r="C3" s="50"/>
+      <c r="C3" s="49"/>
       <c r="D3" s="19"/>
       <c r="F3" s="19"/>
       <c r="G3" s="19"/>
     </row>
     <row r="4" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="52">
+      <c r="A4" s="51">
         <v>556</v>
       </c>
       <c r="B4" s="41"/>
-      <c r="C4" s="50"/>
+      <c r="C4" s="49"/>
       <c r="D4" s="19"/>
       <c r="F4" s="19"/>
       <c r="G4" s="19"/>
     </row>
     <row r="5" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="52">
+      <c r="A5" s="51">
         <v>731</v>
       </c>
       <c r="B5" s="41"/>
-      <c r="C5" s="50"/>
+      <c r="C5" s="49"/>
       <c r="D5" s="19"/>
       <c r="F5" s="19"/>
       <c r="G5" s="19"/>
     </row>
     <row r="6" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="52">
+      <c r="A6" s="51">
         <v>1032</v>
       </c>
       <c r="B6" s="41"/>
-      <c r="C6" s="50"/>
+      <c r="C6" s="49"/>
       <c r="D6" s="19"/>
       <c r="F6" s="19"/>
       <c r="G6" s="19"/>
     </row>
     <row r="7" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="52">
+      <c r="A7" s="51">
         <v>1199</v>
       </c>
       <c r="B7" s="41"/>
-      <c r="C7" s="50"/>
+      <c r="C7" s="49"/>
       <c r="D7" s="19"/>
       <c r="F7" s="19"/>
       <c r="G7" s="19"/>
     </row>
     <row r="8" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="52">
+      <c r="A8" s="51">
         <v>1653</v>
       </c>
       <c r="B8" s="41"/>
-      <c r="C8" s="50"/>
+      <c r="C8" s="49"/>
       <c r="D8" s="19"/>
       <c r="F8" s="19"/>
       <c r="G8" s="19"/>
     </row>
     <row r="9" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="52">
+      <c r="A9" s="51">
         <v>1786</v>
       </c>
       <c r="B9" s="41"/>
-      <c r="C9" s="50"/>
+      <c r="C9" s="49"/>
       <c r="D9" s="19"/>
       <c r="F9" s="19"/>
       <c r="G9" s="19"/>
     </row>
     <row r="10" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="52">
+      <c r="A10" s="51">
         <v>2040</v>
       </c>
       <c r="B10" s="41"/>
-      <c r="C10" s="50"/>
+      <c r="C10" s="49"/>
       <c r="D10" s="19"/>
       <c r="F10" s="19"/>
       <c r="G10" s="19"/>
     </row>
     <row r="11" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="52">
+      <c r="A11" s="51">
         <v>2283</v>
       </c>
       <c r="B11" s="41"/>
-      <c r="C11" s="50"/>
+      <c r="C11" s="49"/>
       <c r="D11" s="19"/>
       <c r="F11" s="19"/>
       <c r="G11" s="19"/>
     </row>
     <row r="12" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="52">
+      <c r="A12" s="51">
         <v>2293</v>
       </c>
       <c r="B12" s="41"/>
-      <c r="C12" s="50"/>
+      <c r="C12" s="49"/>
       <c r="D12" s="19"/>
       <c r="F12" s="19"/>
       <c r="G12" s="19"/>
     </row>
     <row r="13" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="52">
+      <c r="A13" s="51">
         <v>2376</v>
       </c>
       <c r="B13" s="41"/>
-      <c r="C13" s="50"/>
+      <c r="C13" s="49"/>
       <c r="D13" s="19"/>
       <c r="F13" s="19"/>
       <c r="G13" s="19"/>
     </row>
     <row r="14" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="52">
+      <c r="A14" s="51">
         <v>2438</v>
       </c>
       <c r="B14" s="41"/>
-      <c r="C14" s="50"/>
+      <c r="C14" s="49"/>
       <c r="D14" s="19"/>
       <c r="F14" s="19"/>
       <c r="G14" s="19"/>
     </row>
     <row r="15" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="52">
+      <c r="A15" s="51">
         <v>2476</v>
       </c>
       <c r="B15" s="41"/>
-      <c r="C15" s="50"/>
+      <c r="C15" s="49"/>
       <c r="D15" s="19"/>
       <c r="F15" s="19"/>
       <c r="G15" s="19"/>
@@ -3138,213 +3203,213 @@
       </c>
     </row>
     <row r="16" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="52">
+      <c r="A16" s="51">
         <v>2979</v>
       </c>
       <c r="B16" s="41"/>
-      <c r="C16" s="50"/>
+      <c r="C16" s="49"/>
       <c r="D16" s="19"/>
       <c r="F16" s="19"/>
       <c r="G16" s="19"/>
     </row>
     <row r="17" spans="1:7" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="52">
+      <c r="A17" s="51">
         <v>3132</v>
       </c>
       <c r="B17" s="41"/>
-      <c r="C17" s="50"/>
+      <c r="C17" s="49"/>
       <c r="D17" s="19"/>
       <c r="F17" s="19"/>
       <c r="G17" s="19"/>
     </row>
     <row r="18" spans="1:7" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="52">
+      <c r="A18" s="51">
         <v>3183</v>
       </c>
       <c r="B18" s="41"/>
-      <c r="C18" s="50"/>
+      <c r="C18" s="49"/>
       <c r="D18" s="19"/>
     </row>
     <row r="19" spans="1:7" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="52">
+      <c r="A19" s="51">
         <v>3190</v>
       </c>
       <c r="B19" s="41"/>
-      <c r="C19" s="50"/>
+      <c r="C19" s="49"/>
       <c r="D19" s="19"/>
     </row>
     <row r="20" spans="1:7" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="52">
+      <c r="A20" s="51">
         <v>3192</v>
       </c>
       <c r="B20" s="41"/>
-      <c r="C20" s="50"/>
+      <c r="C20" s="49"/>
       <c r="D20" s="19"/>
     </row>
     <row r="21" spans="1:7" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="52">
+      <c r="A21" s="51">
         <v>3217</v>
       </c>
       <c r="B21" s="41"/>
-      <c r="C21" s="50"/>
+      <c r="C21" s="49"/>
       <c r="D21" s="19"/>
     </row>
     <row r="22" spans="1:7" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="52">
+      <c r="A22" s="51">
         <v>3279</v>
       </c>
       <c r="B22" s="41"/>
-      <c r="C22" s="50"/>
+      <c r="C22" s="49"/>
       <c r="D22" s="19"/>
     </row>
     <row r="23" spans="1:7" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="52">
+      <c r="A23" s="51">
         <v>3360</v>
       </c>
       <c r="B23" s="41"/>
-      <c r="C23" s="50"/>
+      <c r="C23" s="49"/>
       <c r="D23" s="19"/>
     </row>
     <row r="24" spans="1:7" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="52">
+      <c r="A24" s="51">
         <v>3466</v>
       </c>
       <c r="B24" s="41"/>
-      <c r="C24" s="50"/>
+      <c r="C24" s="49"/>
       <c r="D24" s="19"/>
     </row>
     <row r="25" spans="1:7" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="52">
+      <c r="A25" s="51">
         <v>3474</v>
       </c>
       <c r="B25" s="41"/>
-      <c r="C25" s="50"/>
+      <c r="C25" s="49"/>
       <c r="D25" s="19"/>
     </row>
     <row r="26" spans="1:7" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="52">
+      <c r="A26" s="51">
         <v>3481</v>
       </c>
       <c r="B26" s="41"/>
-      <c r="C26" s="50"/>
+      <c r="C26" s="49"/>
       <c r="D26" s="19"/>
     </row>
     <row r="27" spans="1:7" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="52">
+      <c r="A27" s="51">
         <v>4218</v>
       </c>
       <c r="B27" s="41"/>
-      <c r="C27" s="50"/>
+      <c r="C27" s="49"/>
       <c r="D27" s="19"/>
     </row>
     <row r="28" spans="1:7" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="52">
+      <c r="A28" s="51">
         <v>4365</v>
       </c>
       <c r="B28" s="41"/>
-      <c r="C28" s="50"/>
+      <c r="C28" s="49"/>
       <c r="D28" s="19"/>
     </row>
     <row r="29" spans="1:7" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="52">
+      <c r="A29" s="51">
         <v>4367</v>
       </c>
       <c r="B29" s="41"/>
-      <c r="C29" s="50"/>
+      <c r="C29" s="49"/>
       <c r="D29" s="19"/>
     </row>
     <row r="30" spans="1:7" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="52">
+      <c r="A30" s="51">
         <v>4434</v>
       </c>
       <c r="B30" s="41"/>
-      <c r="C30" s="50"/>
+      <c r="C30" s="49"/>
       <c r="D30" s="19"/>
     </row>
     <row r="31" spans="1:7" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="52">
+      <c r="A31" s="51">
         <v>4449</v>
       </c>
       <c r="B31" s="41"/>
-      <c r="C31" s="50"/>
+      <c r="C31" s="49"/>
       <c r="D31" s="19"/>
     </row>
     <row r="32" spans="1:7" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="52">
+      <c r="A32" s="51">
         <v>5282</v>
       </c>
       <c r="B32" s="41"/>
-      <c r="C32" s="50"/>
+      <c r="C32" s="49"/>
       <c r="D32" s="19"/>
     </row>
     <row r="33" spans="1:25" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="52">
+      <c r="A33" s="51">
         <v>6679</v>
       </c>
       <c r="B33" s="41"/>
-      <c r="C33" s="50"/>
+      <c r="C33" s="49"/>
       <c r="D33" s="19"/>
     </row>
     <row r="34" spans="1:25" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="52">
+      <c r="A34" s="51">
         <v>7596</v>
       </c>
       <c r="B34" s="41"/>
-      <c r="C34" s="50"/>
+      <c r="C34" s="49"/>
       <c r="D34" s="19"/>
     </row>
     <row r="35" spans="1:25" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="52">
+      <c r="A35" s="51">
         <v>7618</v>
       </c>
       <c r="B35" s="41"/>
-      <c r="C35" s="50"/>
+      <c r="C35" s="49"/>
       <c r="D35" s="19"/>
     </row>
     <row r="36" spans="1:25" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="52">
+      <c r="A36" s="51">
         <v>7630</v>
       </c>
       <c r="B36" s="41"/>
-      <c r="C36" s="50"/>
+      <c r="C36" s="49"/>
       <c r="D36" s="19"/>
     </row>
     <row r="37" spans="1:25" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="52">
+      <c r="A37" s="51">
         <v>7651</v>
       </c>
       <c r="B37" s="41"/>
-      <c r="C37" s="50"/>
+      <c r="C37" s="49"/>
       <c r="D37" s="19"/>
     </row>
     <row r="38" spans="1:25" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A38" s="52">
+      <c r="A38" s="51">
         <v>7776</v>
       </c>
       <c r="B38" s="41"/>
-      <c r="C38" s="50"/>
+      <c r="C38" s="49"/>
       <c r="D38" s="19"/>
     </row>
     <row r="39" spans="1:25" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A39" s="52">
+      <c r="A39" s="51">
         <v>9852</v>
       </c>
       <c r="B39" s="41"/>
-      <c r="C39" s="50"/>
+      <c r="C39" s="49"/>
       <c r="D39" s="19"/>
     </row>
     <row r="40" spans="1:25" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A40" s="52">
+      <c r="A40" s="51">
         <v>9951</v>
       </c>
       <c r="B40" s="41"/>
-      <c r="C40" s="50"/>
+      <c r="C40" s="49"/>
       <c r="D40" s="19"/>
     </row>
     <row r="41" spans="1:25" ht="29" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="46"/>
-      <c r="B41" s="47"/>
-      <c r="C41" s="47"/>
+      <c r="A41" s="45"/>
+      <c r="B41" s="46"/>
+      <c r="C41" s="46"/>
       <c r="D41" s="19"/>
     </row>
     <row r="42" spans="1:25" ht="29" customHeight="1" x14ac:dyDescent="0.15">
@@ -3652,15 +3717,15 @@
       <c r="G1" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="49"/>
+      <c r="H1" s="48"/>
     </row>
     <row r="2" spans="1:8" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="52">
+      <c r="A2" s="51">
         <v>230</v>
       </c>
       <c r="B2" s="33">
         <f>Quiz!V2</f>
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="C2" s="41">
         <f>Exams!B2</f>
@@ -3672,20 +3737,20 @@
       </c>
       <c r="E2" s="33">
         <f>$B2+($C2/$C$42)*3.5+($D2/$D$42)*4.5</f>
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="F2" s="33">
         <f>0.5*INT(E2/0.5)+INT( ((E2-INT(E2/0.5)*0.5)/0.25))*0.5</f>
-        <v>0.5</v>
-      </c>
-      <c r="G2" s="48">
+        <v>1</v>
+      </c>
+      <c r="G2" s="47">
         <f>IF(F2&gt;4.75,1,0)</f>
         <v>0</v>
       </c>
       <c r="H2" s="24"/>
     </row>
     <row r="3" spans="1:8" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="52">
+      <c r="A3" s="51">
         <v>434</v>
       </c>
       <c r="B3" s="33">
@@ -3708,18 +3773,18 @@
         <f t="shared" ref="F3:F19" si="1">0.5*INT(E3/0.5)+INT( ((E3-INT(E3/0.5)*0.5)/0.25))*0.5</f>
         <v>1</v>
       </c>
-      <c r="G3" s="48">
+      <c r="G3" s="47">
         <f t="shared" ref="G3:G19" si="2">IF(F3&gt;4.75,1,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="52">
+      <c r="A4" s="51">
         <v>556</v>
       </c>
       <c r="B4" s="33">
         <f>Quiz!V4</f>
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="C4" s="41">
         <f>Exams!B4</f>
@@ -3731,19 +3796,19 @@
       </c>
       <c r="E4" s="33">
         <f t="shared" si="0"/>
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="F4" s="33">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="G4" s="48">
+        <v>1.5</v>
+      </c>
+      <c r="G4" s="47">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="52">
+      <c r="A5" s="51">
         <v>731</v>
       </c>
       <c r="B5" s="33">
@@ -3766,18 +3831,18 @@
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
-      <c r="G5" s="48">
+      <c r="G5" s="47">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="52">
+      <c r="A6" s="51">
         <v>1032</v>
       </c>
       <c r="B6" s="33">
         <f>Quiz!V6</f>
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="C6" s="41">
         <f>Exams!B6</f>
@@ -3789,19 +3854,19 @@
       </c>
       <c r="E6" s="33">
         <f t="shared" si="0"/>
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="F6" s="33">
         <f t="shared" si="1"/>
         <v>1.5</v>
       </c>
-      <c r="G6" s="48">
+      <c r="G6" s="47">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="52">
+      <c r="A7" s="51">
         <v>1199</v>
       </c>
       <c r="B7" s="33">
@@ -3824,18 +3889,18 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="G7" s="48">
+      <c r="G7" s="47">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="52">
+      <c r="A8" s="51">
         <v>1653</v>
       </c>
       <c r="B8" s="33">
         <f>Quiz!V8</f>
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="C8" s="41">
         <f>Exams!B8</f>
@@ -3847,24 +3912,24 @@
       </c>
       <c r="E8" s="33">
         <f t="shared" si="0"/>
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="F8" s="33">
         <f t="shared" si="1"/>
         <v>1.5</v>
       </c>
-      <c r="G8" s="48">
+      <c r="G8" s="47">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="52">
+      <c r="A9" s="51">
         <v>1786</v>
       </c>
       <c r="B9" s="33">
         <f>Quiz!V9</f>
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="C9" s="41">
         <f>Exams!B9</f>
@@ -3876,24 +3941,24 @@
       </c>
       <c r="E9" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="F9" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G9" s="48">
+        <v>0.5</v>
+      </c>
+      <c r="G9" s="47">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="52">
+      <c r="A10" s="51">
         <v>2040</v>
       </c>
       <c r="B10" s="33">
         <f>Quiz!V10</f>
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="C10" s="41">
         <f>Exams!B10</f>
@@ -3905,19 +3970,19 @@
       </c>
       <c r="E10" s="33">
         <f t="shared" si="0"/>
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="F10" s="33">
         <f t="shared" si="1"/>
         <v>1.5</v>
       </c>
-      <c r="G10" s="48">
+      <c r="G10" s="47">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="52">
+      <c r="A11" s="51">
         <v>2283</v>
       </c>
       <c r="B11" s="33">
@@ -3940,13 +4005,13 @@
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
-      <c r="G11" s="48">
+      <c r="G11" s="47">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="52">
+      <c r="A12" s="51">
         <v>2293</v>
       </c>
       <c r="B12" s="33">
@@ -3969,18 +4034,18 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="G12" s="48">
+      <c r="G12" s="47">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="52">
+      <c r="A13" s="51">
         <v>2376</v>
       </c>
       <c r="B13" s="33">
         <f>Quiz!V13</f>
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="C13" s="41">
         <f>Exams!B13</f>
@@ -3992,24 +4057,24 @@
       </c>
       <c r="E13" s="33">
         <f t="shared" si="0"/>
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="F13" s="33">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="G13" s="48">
+        <v>1.5</v>
+      </c>
+      <c r="G13" s="47">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="52">
+      <c r="A14" s="51">
         <v>2438</v>
       </c>
       <c r="B14" s="33">
         <f>Quiz!V14</f>
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="C14" s="41">
         <f>Exams!B14</f>
@@ -4021,24 +4086,24 @@
       </c>
       <c r="E14" s="33">
         <f t="shared" si="0"/>
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="F14" s="33">
         <f t="shared" si="1"/>
         <v>1.5</v>
       </c>
-      <c r="G14" s="48">
+      <c r="G14" s="47">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="52">
+      <c r="A15" s="51">
         <v>2476</v>
       </c>
       <c r="B15" s="33">
         <f>Quiz!V15</f>
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="C15" s="41">
         <f>Exams!B15</f>
@@ -4050,24 +4115,24 @@
       </c>
       <c r="E15" s="33">
         <f t="shared" si="0"/>
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="F15" s="33">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="G15" s="48">
+      <c r="G15" s="47">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="52">
+      <c r="A16" s="51">
         <v>2979</v>
       </c>
       <c r="B16" s="33">
         <f>Quiz!V16</f>
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="C16" s="41">
         <f>Exams!B16</f>
@@ -4079,19 +4144,19 @@
       </c>
       <c r="E16" s="33">
         <f t="shared" si="0"/>
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="F16" s="33">
         <f t="shared" si="1"/>
-        <v>0.5</v>
-      </c>
-      <c r="G16" s="48">
+        <v>1</v>
+      </c>
+      <c r="G16" s="47">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="52">
+      <c r="A17" s="51">
         <v>3132</v>
       </c>
       <c r="B17" s="33">
@@ -4114,18 +4179,18 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G17" s="48">
+      <c r="G17" s="47">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="52">
+      <c r="A18" s="51">
         <v>3183</v>
       </c>
       <c r="B18" s="33">
         <f>Quiz!V18</f>
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="C18" s="41">
         <f>Exams!B18</f>
@@ -4137,24 +4202,24 @@
       </c>
       <c r="E18" s="33">
         <f t="shared" si="0"/>
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="F18" s="33">
         <f t="shared" si="1"/>
         <v>1.5</v>
       </c>
-      <c r="G18" s="48">
+      <c r="G18" s="47">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="52">
+      <c r="A19" s="51">
         <v>3190</v>
       </c>
       <c r="B19" s="33">
         <f>Quiz!V19</f>
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="C19" s="41">
         <f>Exams!B19</f>
@@ -4166,24 +4231,24 @@
       </c>
       <c r="E19" s="33">
         <f t="shared" si="0"/>
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="F19" s="33">
         <f t="shared" si="1"/>
-        <v>0.5</v>
-      </c>
-      <c r="G19" s="48">
+        <v>1</v>
+      </c>
+      <c r="G19" s="47">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="52">
+      <c r="A20" s="51">
         <v>3192</v>
       </c>
       <c r="B20" s="33">
         <f>Quiz!V20</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" s="41">
         <f>Exams!B20</f>
@@ -4195,24 +4260,24 @@
       </c>
       <c r="E20" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" s="33">
         <f t="shared" ref="F20:F25" si="3">0.5*INT(E20/0.5)+INT( ((E20-INT(E20/0.5)*0.5)/0.25))*0.5</f>
-        <v>0</v>
-      </c>
-      <c r="G20" s="48">
+        <v>1</v>
+      </c>
+      <c r="G20" s="47">
         <f t="shared" ref="G20:G25" si="4">IF(F20&gt;4.75,1,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="52">
+      <c r="A21" s="51">
         <v>3217</v>
       </c>
       <c r="B21" s="33">
         <f>Quiz!V21</f>
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="C21" s="41">
         <f>Exams!B21</f>
@@ -4224,24 +4289,24 @@
       </c>
       <c r="E21" s="33">
         <f t="shared" si="0"/>
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="F21" s="33">
         <f t="shared" si="3"/>
         <v>1.5</v>
       </c>
-      <c r="G21" s="48">
+      <c r="G21" s="47">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="52">
+      <c r="A22" s="51">
         <v>3279</v>
       </c>
       <c r="B22" s="33">
         <f>Quiz!V22</f>
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="C22" s="41">
         <f>Exams!B22</f>
@@ -4253,24 +4318,24 @@
       </c>
       <c r="E22" s="33">
         <f t="shared" si="0"/>
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="F22" s="33">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="G22" s="48">
+        <v>1.5</v>
+      </c>
+      <c r="G22" s="47">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="52">
+      <c r="A23" s="51">
         <v>3360</v>
       </c>
       <c r="B23" s="33">
         <f>Quiz!V23</f>
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="C23" s="41">
         <f>Exams!B23</f>
@@ -4282,24 +4347,24 @@
       </c>
       <c r="E23" s="33">
         <f t="shared" si="0"/>
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="F23" s="33">
         <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="G23" s="48">
+        <v>1.5</v>
+      </c>
+      <c r="G23" s="47">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="52">
+      <c r="A24" s="51">
         <v>3466</v>
       </c>
       <c r="B24" s="33">
         <f>Quiz!V24</f>
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="C24" s="41">
         <f>Exams!B24</f>
@@ -4311,24 +4376,24 @@
       </c>
       <c r="E24" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="F24" s="33">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="G24" s="48">
+        <v>0.5</v>
+      </c>
+      <c r="G24" s="47">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="52">
+      <c r="A25" s="51">
         <v>3474</v>
       </c>
       <c r="B25" s="33">
         <f>Quiz!V25</f>
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="C25" s="41">
         <f>Exams!B25</f>
@@ -4340,24 +4405,24 @@
       </c>
       <c r="E25" s="33">
         <f t="shared" si="0"/>
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="F25" s="33">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="G25" s="48">
+      <c r="G25" s="47">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="52">
+      <c r="A26" s="51">
         <v>3481</v>
       </c>
       <c r="B26" s="33">
         <f>Quiz!V26</f>
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="C26" s="41">
         <f>Exams!B26</f>
@@ -4369,24 +4434,24 @@
       </c>
       <c r="E26" s="33">
         <f t="shared" si="0"/>
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="F26" s="33">
         <f t="shared" ref="F26:F40" si="5">0.5*INT(E26/0.5)+INT( ((E26-INT(E26/0.5)*0.5)/0.25))*0.5</f>
         <v>1</v>
       </c>
-      <c r="G26" s="48">
+      <c r="G26" s="47">
         <f t="shared" ref="G26:G32" si="6">IF(F26&gt;4.75,1,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="52">
+      <c r="A27" s="51">
         <v>4218</v>
       </c>
       <c r="B27" s="33">
         <f>Quiz!V27</f>
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="C27" s="41">
         <f>Exams!B27</f>
@@ -4398,19 +4463,19 @@
       </c>
       <c r="E27" s="33">
         <f t="shared" si="0"/>
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="F27" s="33">
         <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="G27" s="48">
+        <v>0.5</v>
+      </c>
+      <c r="G27" s="47">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="52">
+      <c r="A28" s="51">
         <v>4365</v>
       </c>
       <c r="B28" s="33">
@@ -4433,18 +4498,18 @@
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="G28" s="48">
+      <c r="G28" s="47">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="52">
+      <c r="A29" s="51">
         <v>4367</v>
       </c>
       <c r="B29" s="33">
         <f>Quiz!V29</f>
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="C29" s="41">
         <f>Exams!B29</f>
@@ -4456,19 +4521,19 @@
       </c>
       <c r="E29" s="33">
         <f t="shared" si="0"/>
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="F29" s="33">
         <f t="shared" si="5"/>
         <v>1.5</v>
       </c>
-      <c r="G29" s="48">
+      <c r="G29" s="47">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="52">
+      <c r="A30" s="51">
         <v>4434</v>
       </c>
       <c r="B30" s="33">
@@ -4491,18 +4556,18 @@
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="G30" s="48">
+      <c r="G30" s="47">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="52">
+      <c r="A31" s="51">
         <v>4449</v>
       </c>
       <c r="B31" s="33">
         <f>Quiz!V31</f>
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="C31" s="41">
         <f>Exams!B31</f>
@@ -4514,19 +4579,19 @@
       </c>
       <c r="E31" s="33">
         <f t="shared" si="0"/>
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="F31" s="33">
         <f t="shared" si="5"/>
-        <v>0.5</v>
-      </c>
-      <c r="G31" s="48">
+        <v>1</v>
+      </c>
+      <c r="G31" s="47">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="52">
+      <c r="A32" s="51">
         <v>5282</v>
       </c>
       <c r="B32" s="33">
@@ -4549,13 +4614,13 @@
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="G32" s="48">
+      <c r="G32" s="47">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="52">
+      <c r="A33" s="51">
         <v>6679</v>
       </c>
       <c r="B33" s="33">
@@ -4578,13 +4643,13 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G33" s="48">
+      <c r="G33" s="47">
         <f>IF(F33&gt;4.75,1,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="52">
+      <c r="A34" s="51">
         <v>7596</v>
       </c>
       <c r="B34" s="33">
@@ -4607,18 +4672,18 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G34" s="48">
+      <c r="G34" s="47">
         <f t="shared" ref="G34:G40" si="7">IF(F34&gt;4.75,1,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="52">
+      <c r="A35" s="51">
         <v>7618</v>
       </c>
       <c r="B35" s="33">
         <f>Quiz!V35</f>
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="C35" s="41">
         <f>Exams!B35</f>
@@ -4630,24 +4695,24 @@
       </c>
       <c r="E35" s="33">
         <f t="shared" si="0"/>
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="F35" s="33">
         <f t="shared" si="5"/>
-        <v>0.5</v>
-      </c>
-      <c r="G35" s="48">
+        <v>1</v>
+      </c>
+      <c r="G35" s="47">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="52">
+      <c r="A36" s="51">
         <v>7630</v>
       </c>
       <c r="B36" s="33">
         <f>Quiz!V36</f>
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="C36" s="41">
         <f>Exams!B36</f>
@@ -4659,24 +4724,24 @@
       </c>
       <c r="E36" s="33">
         <f t="shared" si="0"/>
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="F36" s="33">
         <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="G36" s="48">
+        <v>0.5</v>
+      </c>
+      <c r="G36" s="47">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="52">
+      <c r="A37" s="51">
         <v>7651</v>
       </c>
       <c r="B37" s="33">
         <f>Quiz!V37</f>
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="C37" s="41">
         <f>Exams!B37</f>
@@ -4688,19 +4753,19 @@
       </c>
       <c r="E37" s="33">
         <f t="shared" si="0"/>
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="F37" s="33">
         <f t="shared" si="5"/>
-        <v>0.5</v>
-      </c>
-      <c r="G37" s="48">
+        <v>1</v>
+      </c>
+      <c r="G37" s="47">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A38" s="52">
+      <c r="A38" s="51">
         <v>7776</v>
       </c>
       <c r="B38" s="33">
@@ -4723,18 +4788,18 @@
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="G38" s="48">
+      <c r="G38" s="47">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A39" s="52">
+      <c r="A39" s="51">
         <v>9852</v>
       </c>
       <c r="B39" s="33">
         <f>Quiz!V39</f>
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="C39" s="41">
         <f>Exams!B39</f>
@@ -4746,24 +4811,24 @@
       </c>
       <c r="E39" s="33">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="F39" s="33">
         <f t="shared" ref="F39" si="8">0.5*INT(E39/0.5)+INT( ((E39-INT(E39/0.5)*0.5)/0.25))*0.5</f>
         <v>2</v>
       </c>
-      <c r="G39" s="48">
+      <c r="G39" s="47">
         <f t="shared" ref="G39" si="9">IF(F39&gt;4.75,1,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A40" s="52">
+      <c r="A40" s="51">
         <v>9951</v>
       </c>
       <c r="B40" s="33">
         <f>Quiz!V40</f>
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="C40" s="41">
         <f>Exams!B40</f>
@@ -4775,13 +4840,13 @@
       </c>
       <c r="E40" s="33">
         <f t="shared" si="0"/>
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="F40" s="33">
         <f t="shared" si="5"/>
-        <v>1.5</v>
-      </c>
-      <c r="G40" s="48">
+        <v>2</v>
+      </c>
+      <c r="G40" s="47">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -4827,27 +4892,27 @@
         <v>23</v>
       </c>
       <c r="B43" s="29">
-        <f>AVERAGE(B$2:B$40)</f>
-        <v>1.0102564102564102</v>
+        <f t="shared" ref="B43:G43" si="10">AVERAGE(B$2:B$40)</f>
+        <v>1.1025641025641026</v>
       </c>
       <c r="C43" s="29">
-        <f>AVERAGE(C$2:C$40)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="D43" s="29">
-        <f>AVERAGE(D$2:D$40)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="E43" s="29">
-        <f>AVERAGE(E$2:E$40)</f>
-        <v>1.0102564102564102</v>
+        <f t="shared" si="10"/>
+        <v>1.1025641025641026</v>
       </c>
       <c r="F43" s="29">
-        <f>AVERAGE(F$2:F$40)</f>
-        <v>0.97435897435897434</v>
+        <f t="shared" si="10"/>
+        <v>1.1153846153846154</v>
       </c>
       <c r="G43" s="29">
-        <f>AVERAGE(G$2:G$40)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
@@ -4856,27 +4921,27 @@
         <v>24</v>
       </c>
       <c r="B44" s="29">
-        <f>STDEV(B$2:B$40)</f>
-        <v>0.64063901971098192</v>
+        <f t="shared" ref="B44:G44" si="11">STDEV(B$2:B$40)</f>
+        <v>0.52590132128574707</v>
       </c>
       <c r="C44" s="29">
-        <f>STDEV(C$2:C$40)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="D44" s="29">
-        <f>STDEV(D$2:D$40)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="E44" s="29">
-        <f>STDEV(E$2:E$40)</f>
-        <v>0.64063901971098192</v>
+        <f t="shared" si="11"/>
+        <v>0.52590132128574707</v>
       </c>
       <c r="F44" s="29">
-        <f>STDEV(F$2:F$40)</f>
-        <v>0.62774364056723386</v>
+        <f t="shared" si="11"/>
+        <v>0.55561178302956782</v>
       </c>
       <c r="G44" s="29">
-        <f>STDEV(G$2:G$40)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -4885,27 +4950,27 @@
         <v>25</v>
       </c>
       <c r="B45" s="29">
-        <f>MEDIAN(B$2:B$40)</f>
+        <f t="shared" ref="B45:G45" si="12">MEDIAN(B$2:B$40)</f>
         <v>1.2</v>
       </c>
       <c r="C45" s="29">
-        <f>MEDIAN(C$2:C$40)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="D45" s="29">
-        <f>MEDIAN(D$2:D$40)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="E45" s="29">
-        <f>MEDIAN(E$2:E$40)</f>
+        <f t="shared" si="12"/>
         <v>1.2</v>
       </c>
       <c r="F45" s="29">
-        <f>MEDIAN(F$2:F$40)</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="G45" s="29">
-        <f>MEDIAN(G$2:G$40)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>

--- a/phy112/Grades/grades_report_2026.xlsx
+++ b/phy112/Grades/grades_report_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
   <workbookPr date1904="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ptohos/Documents/MyCourses/FYS112/2026/Grades/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF11DF78-C4C2-D540-822A-83B593C2E4DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7245DE6C-EF07-A04E-9886-C2EA4728E426}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3060" yWindow="1200" windowWidth="32920" windowHeight="19260" tabRatio="334" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1640" yWindow="1200" windowWidth="32920" windowHeight="19260" tabRatio="334" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Quiz" sheetId="1" r:id="rId1"/>
@@ -999,7 +999,9 @@
       <c r="D2" s="49">
         <v>16</v>
       </c>
-      <c r="E2" s="49"/>
+      <c r="E2" s="49">
+        <v>4</v>
+      </c>
       <c r="F2" s="18"/>
       <c r="G2" s="18"/>
       <c r="H2" s="18"/>
@@ -1018,7 +1020,7 @@
       <c r="U2" s="18"/>
       <c r="V2" s="33">
         <f t="shared" ref="V2:V39" si="0">$V$42 * ( (SUM(B2:U2))/((SUM($B$46:$U$46))*$B$42) )</f>
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="W2"/>
     </row>
@@ -1033,7 +1035,9 @@
       <c r="D3" s="49">
         <v>12</v>
       </c>
-      <c r="E3" s="49"/>
+      <c r="E3" s="49">
+        <v>4</v>
+      </c>
       <c r="F3" s="18"/>
       <c r="G3" s="18"/>
       <c r="H3" s="18"/>
@@ -1052,7 +1056,7 @@
       <c r="U3" s="18"/>
       <c r="V3" s="33">
         <f t="shared" si="0"/>
-        <v>1.2</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="W3"/>
     </row>
@@ -1067,7 +1071,9 @@
       <c r="D4" s="49">
         <v>16</v>
       </c>
-      <c r="E4" s="49"/>
+      <c r="E4" s="49">
+        <v>4</v>
+      </c>
       <c r="F4" s="18"/>
       <c r="G4" s="18"/>
       <c r="H4" s="18"/>
@@ -1086,7 +1092,7 @@
       <c r="U4" s="18"/>
       <c r="V4" s="33">
         <f t="shared" si="0"/>
-        <v>1.4</v>
+        <v>1.0666666666666667</v>
       </c>
       <c r="W4"/>
     </row>
@@ -1101,7 +1107,9 @@
       <c r="D5" s="49">
         <v>4</v>
       </c>
-      <c r="E5" s="49"/>
+      <c r="E5" s="49">
+        <v>4</v>
+      </c>
       <c r="F5" s="18"/>
       <c r="G5" s="18"/>
       <c r="H5" s="18"/>
@@ -1135,7 +1143,9 @@
       <c r="D6" s="49">
         <v>12</v>
       </c>
-      <c r="E6" s="49"/>
+      <c r="E6" s="49">
+        <v>12</v>
+      </c>
       <c r="F6" s="18"/>
       <c r="G6" s="18"/>
       <c r="H6" s="18"/>
@@ -1154,7 +1164,7 @@
       <c r="U6" s="18"/>
       <c r="V6" s="33">
         <f t="shared" si="0"/>
-        <v>1.4</v>
+        <v>1.3333333333333333</v>
       </c>
       <c r="W6"/>
     </row>
@@ -1169,7 +1179,9 @@
       <c r="D7" s="49">
         <v>18</v>
       </c>
-      <c r="E7" s="49"/>
+      <c r="E7" s="49">
+        <v>4</v>
+      </c>
       <c r="F7" s="18"/>
       <c r="G7" s="18"/>
       <c r="H7" s="18"/>
@@ -1188,7 +1200,7 @@
       <c r="U7" s="18"/>
       <c r="V7" s="33">
         <f t="shared" si="0"/>
-        <v>1.8</v>
+        <v>1.3333333333333333</v>
       </c>
       <c r="W7"/>
     </row>
@@ -1203,7 +1215,9 @@
       <c r="D8" s="49">
         <v>14</v>
       </c>
-      <c r="E8" s="49"/>
+      <c r="E8" s="49">
+        <v>4</v>
+      </c>
       <c r="F8" s="18"/>
       <c r="G8" s="18"/>
       <c r="H8" s="18"/>
@@ -1222,7 +1236,7 @@
       <c r="U8" s="18"/>
       <c r="V8" s="33">
         <f t="shared" si="0"/>
-        <v>1.5</v>
+        <v>1.1333333333333333</v>
       </c>
       <c r="W8"/>
     </row>
@@ -1235,7 +1249,9 @@
       <c r="D9" s="49">
         <v>12</v>
       </c>
-      <c r="E9" s="49"/>
+      <c r="E9" s="49">
+        <v>20</v>
+      </c>
       <c r="F9" s="18"/>
       <c r="G9" s="18"/>
       <c r="H9" s="18"/>
@@ -1254,7 +1270,7 @@
       <c r="U9" s="18"/>
       <c r="V9" s="33">
         <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>1.0666666666666667</v>
       </c>
       <c r="W9"/>
     </row>
@@ -1269,7 +1285,9 @@
       <c r="D10" s="49">
         <v>12</v>
       </c>
-      <c r="E10" s="49"/>
+      <c r="E10" s="49">
+        <v>20</v>
+      </c>
       <c r="F10" s="18"/>
       <c r="G10" s="18"/>
       <c r="H10" s="18"/>
@@ -1288,7 +1306,7 @@
       <c r="U10" s="18"/>
       <c r="V10" s="33">
         <f t="shared" si="0"/>
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="W10"/>
     </row>
@@ -1303,7 +1321,9 @@
       <c r="D11" s="49">
         <v>4</v>
       </c>
-      <c r="E11" s="49"/>
+      <c r="E11" s="49">
+        <v>4</v>
+      </c>
       <c r="F11" s="18"/>
       <c r="G11" s="18"/>
       <c r="H11" s="18"/>
@@ -1337,7 +1357,9 @@
       <c r="D12" s="49">
         <v>12</v>
       </c>
-      <c r="E12" s="49"/>
+      <c r="E12" s="49">
+        <v>4</v>
+      </c>
       <c r="F12" s="18"/>
       <c r="G12" s="18"/>
       <c r="H12" s="18"/>
@@ -1356,7 +1378,7 @@
       <c r="U12" s="18"/>
       <c r="V12" s="33">
         <f t="shared" si="0"/>
-        <v>1.2</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="W12"/>
     </row>
@@ -1371,7 +1393,9 @@
       <c r="D13" s="49">
         <v>14</v>
       </c>
-      <c r="E13" s="49"/>
+      <c r="E13" s="49">
+        <v>4</v>
+      </c>
       <c r="F13" s="18"/>
       <c r="G13" s="18"/>
       <c r="H13" s="18"/>
@@ -1390,7 +1414,7 @@
       <c r="U13" s="18"/>
       <c r="V13" s="33">
         <f t="shared" si="0"/>
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="W13"/>
     </row>
@@ -1405,7 +1429,9 @@
       <c r="D14" s="49">
         <v>18</v>
       </c>
-      <c r="E14" s="49"/>
+      <c r="E14" s="49">
+        <v>4</v>
+      </c>
       <c r="F14" s="18"/>
       <c r="G14" s="18"/>
       <c r="H14" s="18"/>
@@ -1424,7 +1450,7 @@
       <c r="U14" s="18"/>
       <c r="V14" s="33">
         <f t="shared" si="0"/>
-        <v>1.7</v>
+        <v>1.2666666666666666</v>
       </c>
     </row>
     <row r="15" spans="1:23" ht="29" customHeight="1" x14ac:dyDescent="0.15">
@@ -1438,7 +1464,9 @@
       <c r="D15" s="49">
         <v>20</v>
       </c>
-      <c r="E15" s="49"/>
+      <c r="E15" s="49">
+        <v>20</v>
+      </c>
       <c r="F15" s="18"/>
       <c r="G15" s="18"/>
       <c r="H15" s="18"/>
@@ -1457,7 +1485,7 @@
       <c r="U15" s="18"/>
       <c r="V15" s="33">
         <f t="shared" si="0"/>
-        <v>1.9</v>
+        <v>1.9333333333333333</v>
       </c>
       <c r="W15"/>
     </row>
@@ -1472,7 +1500,9 @@
       <c r="D16" s="49">
         <v>12</v>
       </c>
-      <c r="E16" s="49"/>
+      <c r="E16" s="49">
+        <v>14</v>
+      </c>
       <c r="F16" s="18"/>
       <c r="G16" s="18"/>
       <c r="H16" s="18"/>
@@ -1491,7 +1521,7 @@
       <c r="U16" s="18"/>
       <c r="V16" s="33">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="W16"/>
     </row>
@@ -1536,7 +1566,9 @@
       <c r="D18" s="49">
         <v>18</v>
       </c>
-      <c r="E18" s="49"/>
+      <c r="E18" s="49">
+        <v>4</v>
+      </c>
       <c r="F18" s="18"/>
       <c r="G18" s="18"/>
       <c r="H18" s="18"/>
@@ -1555,7 +1587,7 @@
       <c r="U18" s="18"/>
       <c r="V18" s="33">
         <f t="shared" si="0"/>
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="W18"/>
     </row>
@@ -1570,7 +1602,9 @@
       <c r="D19" s="49">
         <v>14</v>
       </c>
-      <c r="E19" s="49"/>
+      <c r="E19" s="49">
+        <v>16</v>
+      </c>
       <c r="F19" s="18"/>
       <c r="G19" s="18"/>
       <c r="H19" s="18"/>
@@ -1589,7 +1623,7 @@
       <c r="U19" s="18"/>
       <c r="V19" s="33">
         <f t="shared" si="0"/>
-        <v>0.9</v>
+        <v>1.1333333333333333</v>
       </c>
       <c r="W19"/>
     </row>
@@ -1602,7 +1636,9 @@
       <c r="D20" s="49">
         <v>20</v>
       </c>
-      <c r="E20" s="49"/>
+      <c r="E20" s="49">
+        <v>12</v>
+      </c>
       <c r="F20" s="18"/>
       <c r="G20" s="18"/>
       <c r="H20" s="18"/>
@@ -1621,7 +1657,7 @@
       <c r="U20" s="18"/>
       <c r="V20" s="33">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>1.0666666666666667</v>
       </c>
       <c r="W20"/>
     </row>
@@ -1636,7 +1672,9 @@
       <c r="D21" s="49">
         <v>12</v>
       </c>
-      <c r="E21" s="49"/>
+      <c r="E21" s="49">
+        <v>16</v>
+      </c>
       <c r="F21" s="18"/>
       <c r="G21" s="18"/>
       <c r="H21" s="18"/>
@@ -1655,7 +1693,7 @@
       <c r="U21" s="18"/>
       <c r="V21" s="33">
         <f t="shared" si="0"/>
-        <v>1.4</v>
+        <v>1.4666666666666666</v>
       </c>
       <c r="W21"/>
     </row>
@@ -1670,7 +1708,9 @@
       <c r="D22" s="49">
         <v>14</v>
       </c>
-      <c r="E22" s="49"/>
+      <c r="E22" s="49">
+        <v>4</v>
+      </c>
       <c r="F22" s="18"/>
       <c r="G22" s="18"/>
       <c r="H22" s="18"/>
@@ -1689,7 +1729,7 @@
       <c r="U22" s="18"/>
       <c r="V22" s="33">
         <f t="shared" si="0"/>
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="W22"/>
     </row>
@@ -1704,7 +1744,9 @@
       <c r="D23" s="49">
         <v>16</v>
       </c>
-      <c r="E23" s="49"/>
+      <c r="E23" s="49">
+        <v>20</v>
+      </c>
       <c r="F23" s="18"/>
       <c r="G23" s="18"/>
       <c r="H23" s="18"/>
@@ -1723,7 +1765,7 @@
       <c r="U23" s="18"/>
       <c r="V23" s="33">
         <f t="shared" si="0"/>
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="W23"/>
     </row>
@@ -1736,7 +1778,9 @@
       <c r="D24" s="49">
         <v>12</v>
       </c>
-      <c r="E24" s="49"/>
+      <c r="E24" s="49">
+        <v>12</v>
+      </c>
       <c r="F24" s="18"/>
       <c r="G24" s="18"/>
       <c r="H24" s="18"/>
@@ -1755,7 +1799,7 @@
       <c r="U24" s="18"/>
       <c r="V24" s="33">
         <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W24"/>
     </row>
@@ -1770,7 +1814,9 @@
       <c r="D25" s="49">
         <v>20</v>
       </c>
-      <c r="E25" s="49"/>
+      <c r="E25" s="49">
+        <v>8</v>
+      </c>
       <c r="F25" s="18"/>
       <c r="G25" s="18"/>
       <c r="H25" s="18"/>
@@ -1789,7 +1835,7 @@
       <c r="U25" s="18"/>
       <c r="V25" s="33">
         <f t="shared" si="0"/>
-        <v>1.9</v>
+        <v>1.5333333333333334</v>
       </c>
       <c r="W25"/>
     </row>
@@ -1804,7 +1850,9 @@
       <c r="D26" s="49">
         <v>4</v>
       </c>
-      <c r="E26" s="49"/>
+      <c r="E26" s="49">
+        <v>4</v>
+      </c>
       <c r="F26" s="18"/>
       <c r="G26" s="18"/>
       <c r="H26" s="18"/>
@@ -1823,7 +1871,7 @@
       <c r="U26" s="18"/>
       <c r="V26" s="33">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="W26"/>
     </row>
@@ -1836,7 +1884,9 @@
         <v>12</v>
       </c>
       <c r="D27" s="49"/>
-      <c r="E27" s="49"/>
+      <c r="E27" s="49">
+        <v>4</v>
+      </c>
       <c r="F27" s="18"/>
       <c r="G27" s="18"/>
       <c r="H27" s="18"/>
@@ -1855,7 +1905,7 @@
       <c r="U27" s="18"/>
       <c r="V27" s="33">
         <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.53333333333333333</v>
       </c>
       <c r="W27"/>
     </row>
@@ -1870,7 +1920,9 @@
       <c r="D28" s="49">
         <v>12</v>
       </c>
-      <c r="E28" s="49"/>
+      <c r="E28" s="49">
+        <v>4</v>
+      </c>
       <c r="F28" s="18"/>
       <c r="G28" s="18"/>
       <c r="H28" s="18"/>
@@ -1889,7 +1941,7 @@
       <c r="U28" s="18"/>
       <c r="V28" s="33">
         <f t="shared" si="0"/>
-        <v>1.2</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="W28"/>
     </row>
@@ -1904,7 +1956,9 @@
       <c r="D29" s="49">
         <v>14</v>
       </c>
-      <c r="E29" s="49"/>
+      <c r="E29" s="49">
+        <v>4</v>
+      </c>
       <c r="F29" s="18"/>
       <c r="G29" s="18"/>
       <c r="H29" s="18"/>
@@ -1923,7 +1977,7 @@
       <c r="U29" s="18"/>
       <c r="V29" s="33">
         <f t="shared" si="0"/>
-        <v>1.5</v>
+        <v>1.1333333333333333</v>
       </c>
       <c r="W29"/>
     </row>
@@ -1938,7 +1992,9 @@
       <c r="D30" s="49">
         <v>12</v>
       </c>
-      <c r="E30" s="49"/>
+      <c r="E30" s="49">
+        <v>4</v>
+      </c>
       <c r="F30" s="18"/>
       <c r="G30" s="18"/>
       <c r="H30" s="18"/>
@@ -1957,7 +2013,7 @@
       <c r="U30" s="18"/>
       <c r="V30" s="33">
         <f t="shared" si="0"/>
-        <v>1.2</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="W30"/>
     </row>
@@ -1972,7 +2028,9 @@
       <c r="D31" s="49">
         <v>14</v>
       </c>
-      <c r="E31" s="49"/>
+      <c r="E31" s="49">
+        <v>4</v>
+      </c>
       <c r="F31" s="18"/>
       <c r="G31" s="18"/>
       <c r="H31" s="18"/>
@@ -1991,7 +2049,7 @@
       <c r="U31" s="18"/>
       <c r="V31" s="33">
         <f t="shared" si="0"/>
-        <v>0.9</v>
+        <v>0.73333333333333328</v>
       </c>
       <c r="W31"/>
     </row>
@@ -2006,7 +2064,9 @@
       <c r="D32" s="49">
         <v>12</v>
       </c>
-      <c r="E32" s="49"/>
+      <c r="E32" s="49">
+        <v>12</v>
+      </c>
       <c r="F32" s="18"/>
       <c r="G32" s="18"/>
       <c r="H32" s="18"/>
@@ -2100,7 +2160,9 @@
       <c r="D35" s="49">
         <v>14</v>
       </c>
-      <c r="E35" s="49"/>
+      <c r="E35" s="49">
+        <v>1</v>
+      </c>
       <c r="F35" s="18"/>
       <c r="G35" s="18"/>
       <c r="H35" s="18"/>
@@ -2119,7 +2181,7 @@
       <c r="U35" s="18"/>
       <c r="V35" s="33">
         <f t="shared" si="0"/>
-        <v>0.9</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="W35"/>
     </row>
@@ -2151,7 +2213,7 @@
       <c r="U36" s="18"/>
       <c r="V36" s="33">
         <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W36"/>
     </row>
@@ -2166,7 +2228,9 @@
       <c r="D37" s="49">
         <v>14</v>
       </c>
-      <c r="E37" s="49"/>
+      <c r="E37" s="49">
+        <v>20</v>
+      </c>
       <c r="F37" s="18"/>
       <c r="G37" s="18"/>
       <c r="H37" s="18"/>
@@ -2185,7 +2249,7 @@
       <c r="U37" s="18"/>
       <c r="V37" s="33">
         <f t="shared" si="0"/>
-        <v>0.9</v>
+        <v>1.2666666666666666</v>
       </c>
       <c r="W37"/>
     </row>
@@ -2219,7 +2283,7 @@
       <c r="U38" s="18"/>
       <c r="V38" s="33">
         <f t="shared" si="0"/>
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="W38"/>
     </row>
@@ -2234,7 +2298,9 @@
       <c r="D39" s="49">
         <v>16</v>
       </c>
-      <c r="E39" s="49"/>
+      <c r="E39" s="49">
+        <v>20</v>
+      </c>
       <c r="F39" s="18"/>
       <c r="G39" s="18"/>
       <c r="H39" s="18"/>
@@ -2253,7 +2319,7 @@
       <c r="U39" s="18"/>
       <c r="V39" s="33">
         <f t="shared" si="0"/>
-        <v>1.8</v>
+        <v>1.8666666666666667</v>
       </c>
       <c r="W39"/>
     </row>
@@ -2268,7 +2334,9 @@
       <c r="D40" s="49">
         <v>20</v>
       </c>
-      <c r="E40" s="49"/>
+      <c r="E40" s="49">
+        <v>20</v>
+      </c>
       <c r="F40" s="18"/>
       <c r="G40" s="18"/>
       <c r="H40" s="18"/>
@@ -2287,7 +2355,7 @@
       <c r="U40" s="18"/>
       <c r="V40" s="33">
         <f t="shared" ref="V40" si="1">$V$42 * ( (SUM(B40:U40))/((SUM($B$46:$U$46))*$B$42) )</f>
-        <v>1.8</v>
+        <v>1.8666666666666667</v>
       </c>
       <c r="W40"/>
     </row>
@@ -2401,9 +2469,9 @@
         <f t="shared" si="2"/>
         <v>13.515151515151516</v>
       </c>
-      <c r="E43" s="29" t="e">
+      <c r="E43" s="29">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+        <v>8.9393939393939394</v>
       </c>
       <c r="F43" s="29" t="e">
         <f t="shared" si="2"/>
@@ -2471,7 +2539,7 @@
       </c>
       <c r="V43" s="29">
         <f t="shared" si="2"/>
-        <v>1.0842105263157895</v>
+        <v>0.981578947368421</v>
       </c>
       <c r="W43"/>
     </row>
@@ -2491,9 +2559,9 @@
         <f t="shared" si="3"/>
         <v>4.0009468576295477</v>
       </c>
-      <c r="E44" s="29" t="e">
+      <c r="E44" s="29">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
+        <v>6.6140919347414675</v>
       </c>
       <c r="F44" s="29" t="e">
         <f t="shared" si="3"/>
@@ -2561,7 +2629,7 @@
       </c>
       <c r="V44" s="29">
         <f t="shared" si="3"/>
-        <v>0.52014879149297955</v>
+        <v>0.47576064391199774</v>
       </c>
       <c r="W44"/>
     </row>
@@ -2581,9 +2649,9 @@
         <f t="shared" si="4"/>
         <v>14</v>
       </c>
-      <c r="E45" s="29" t="e">
+      <c r="E45" s="29">
         <f t="shared" si="4"/>
-        <v>#NUM!</v>
+        <v>4</v>
       </c>
       <c r="F45" s="29" t="e">
         <f t="shared" si="4"/>
@@ -2651,7 +2719,7 @@
       </c>
       <c r="V45" s="29">
         <f t="shared" si="4"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="W45"/>
     </row>
@@ -2673,7 +2741,7 @@
       </c>
       <c r="E46" s="32">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F46" s="32">
         <f t="shared" si="5"/>
@@ -3725,7 +3793,7 @@
       </c>
       <c r="B2" s="33">
         <f>Quiz!V2</f>
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="C2" s="41">
         <f>Exams!B2</f>
@@ -3737,7 +3805,7 @@
       </c>
       <c r="E2" s="33">
         <f>$B2+($C2/$C$42)*3.5+($D2/$D$42)*4.5</f>
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="F2" s="33">
         <f>0.5*INT(E2/0.5)+INT( ((E2-INT(E2/0.5)*0.5)/0.25))*0.5</f>
@@ -3755,7 +3823,7 @@
       </c>
       <c r="B3" s="33">
         <f>Quiz!V3</f>
-        <v>1.2</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="C3" s="41">
         <f>Exams!B3</f>
@@ -3767,7 +3835,7 @@
       </c>
       <c r="E3" s="33">
         <f t="shared" ref="E3:E40" si="0">$B3+($C3/$C$42)*3.5+($D3/$D$42)*4.5</f>
-        <v>1.2</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="F3" s="33">
         <f t="shared" ref="F3:F19" si="1">0.5*INT(E3/0.5)+INT( ((E3-INT(E3/0.5)*0.5)/0.25))*0.5</f>
@@ -3784,7 +3852,7 @@
       </c>
       <c r="B4" s="33">
         <f>Quiz!V4</f>
-        <v>1.4</v>
+        <v>1.0666666666666667</v>
       </c>
       <c r="C4" s="41">
         <f>Exams!B4</f>
@@ -3796,11 +3864,11 @@
       </c>
       <c r="E4" s="33">
         <f t="shared" si="0"/>
-        <v>1.4</v>
+        <v>1.0666666666666667</v>
       </c>
       <c r="F4" s="33">
         <f t="shared" si="1"/>
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G4" s="47">
         <f t="shared" si="2"/>
@@ -3842,7 +3910,7 @@
       </c>
       <c r="B6" s="33">
         <f>Quiz!V6</f>
-        <v>1.4</v>
+        <v>1.3333333333333333</v>
       </c>
       <c r="C6" s="41">
         <f>Exams!B6</f>
@@ -3854,7 +3922,7 @@
       </c>
       <c r="E6" s="33">
         <f t="shared" si="0"/>
-        <v>1.4</v>
+        <v>1.3333333333333333</v>
       </c>
       <c r="F6" s="33">
         <f t="shared" si="1"/>
@@ -3871,7 +3939,7 @@
       </c>
       <c r="B7" s="33">
         <f>Quiz!V7</f>
-        <v>1.8</v>
+        <v>1.3333333333333333</v>
       </c>
       <c r="C7" s="41">
         <f>Exams!B7</f>
@@ -3883,11 +3951,11 @@
       </c>
       <c r="E7" s="33">
         <f t="shared" si="0"/>
-        <v>1.8</v>
+        <v>1.3333333333333333</v>
       </c>
       <c r="F7" s="33">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="G7" s="47">
         <f t="shared" si="2"/>
@@ -3900,7 +3968,7 @@
       </c>
       <c r="B8" s="33">
         <f>Quiz!V8</f>
-        <v>1.5</v>
+        <v>1.1333333333333333</v>
       </c>
       <c r="C8" s="41">
         <f>Exams!B8</f>
@@ -3912,11 +3980,11 @@
       </c>
       <c r="E8" s="33">
         <f t="shared" si="0"/>
-        <v>1.5</v>
+        <v>1.1333333333333333</v>
       </c>
       <c r="F8" s="33">
         <f t="shared" si="1"/>
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G8" s="47">
         <f t="shared" si="2"/>
@@ -3929,7 +3997,7 @@
       </c>
       <c r="B9" s="33">
         <f>Quiz!V9</f>
-        <v>0.6</v>
+        <v>1.0666666666666667</v>
       </c>
       <c r="C9" s="41">
         <f>Exams!B9</f>
@@ -3941,11 +4009,11 @@
       </c>
       <c r="E9" s="33">
         <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>1.0666666666666667</v>
       </c>
       <c r="F9" s="33">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G9" s="47">
         <f t="shared" si="2"/>
@@ -3958,7 +4026,7 @@
       </c>
       <c r="B10" s="33">
         <f>Quiz!V10</f>
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="C10" s="41">
         <f>Exams!B10</f>
@@ -3970,7 +4038,7 @@
       </c>
       <c r="E10" s="33">
         <f t="shared" si="0"/>
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="F10" s="33">
         <f t="shared" si="1"/>
@@ -4016,7 +4084,7 @@
       </c>
       <c r="B12" s="33">
         <f>Quiz!V12</f>
-        <v>1.2</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="C12" s="41">
         <f>Exams!B12</f>
@@ -4028,7 +4096,7 @@
       </c>
       <c r="E12" s="33">
         <f t="shared" si="0"/>
-        <v>1.2</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="F12" s="33">
         <f t="shared" si="1"/>
@@ -4045,7 +4113,7 @@
       </c>
       <c r="B13" s="33">
         <f>Quiz!V13</f>
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="C13" s="41">
         <f>Exams!B13</f>
@@ -4057,11 +4125,11 @@
       </c>
       <c r="E13" s="33">
         <f t="shared" si="0"/>
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="F13" s="33">
         <f t="shared" si="1"/>
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G13" s="47">
         <f t="shared" si="2"/>
@@ -4074,7 +4142,7 @@
       </c>
       <c r="B14" s="33">
         <f>Quiz!V14</f>
-        <v>1.7</v>
+        <v>1.2666666666666666</v>
       </c>
       <c r="C14" s="41">
         <f>Exams!B14</f>
@@ -4086,7 +4154,7 @@
       </c>
       <c r="E14" s="33">
         <f t="shared" si="0"/>
-        <v>1.7</v>
+        <v>1.2666666666666666</v>
       </c>
       <c r="F14" s="33">
         <f t="shared" si="1"/>
@@ -4103,7 +4171,7 @@
       </c>
       <c r="B15" s="33">
         <f>Quiz!V15</f>
-        <v>1.9</v>
+        <v>1.9333333333333333</v>
       </c>
       <c r="C15" s="41">
         <f>Exams!B15</f>
@@ -4115,7 +4183,7 @@
       </c>
       <c r="E15" s="33">
         <f t="shared" si="0"/>
-        <v>1.9</v>
+        <v>1.9333333333333333</v>
       </c>
       <c r="F15" s="33">
         <f t="shared" si="1"/>
@@ -4132,7 +4200,7 @@
       </c>
       <c r="B16" s="33">
         <f>Quiz!V16</f>
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="C16" s="41">
         <f>Exams!B16</f>
@@ -4144,7 +4212,7 @@
       </c>
       <c r="E16" s="33">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="F16" s="33">
         <f t="shared" si="1"/>
@@ -4190,7 +4258,7 @@
       </c>
       <c r="B18" s="33">
         <f>Quiz!V18</f>
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="C18" s="41">
         <f>Exams!B18</f>
@@ -4202,11 +4270,11 @@
       </c>
       <c r="E18" s="33">
         <f t="shared" si="0"/>
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="F18" s="33">
         <f t="shared" si="1"/>
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G18" s="47">
         <f t="shared" si="2"/>
@@ -4219,7 +4287,7 @@
       </c>
       <c r="B19" s="33">
         <f>Quiz!V19</f>
-        <v>0.9</v>
+        <v>1.1333333333333333</v>
       </c>
       <c r="C19" s="41">
         <f>Exams!B19</f>
@@ -4231,7 +4299,7 @@
       </c>
       <c r="E19" s="33">
         <f t="shared" si="0"/>
-        <v>0.9</v>
+        <v>1.1333333333333333</v>
       </c>
       <c r="F19" s="33">
         <f t="shared" si="1"/>
@@ -4248,7 +4316,7 @@
       </c>
       <c r="B20" s="33">
         <f>Quiz!V20</f>
-        <v>1</v>
+        <v>1.0666666666666667</v>
       </c>
       <c r="C20" s="41">
         <f>Exams!B20</f>
@@ -4260,7 +4328,7 @@
       </c>
       <c r="E20" s="33">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>1.0666666666666667</v>
       </c>
       <c r="F20" s="33">
         <f t="shared" ref="F20:F25" si="3">0.5*INT(E20/0.5)+INT( ((E20-INT(E20/0.5)*0.5)/0.25))*0.5</f>
@@ -4277,7 +4345,7 @@
       </c>
       <c r="B21" s="33">
         <f>Quiz!V21</f>
-        <v>1.4</v>
+        <v>1.4666666666666666</v>
       </c>
       <c r="C21" s="41">
         <f>Exams!B21</f>
@@ -4289,7 +4357,7 @@
       </c>
       <c r="E21" s="33">
         <f t="shared" si="0"/>
-        <v>1.4</v>
+        <v>1.4666666666666666</v>
       </c>
       <c r="F21" s="33">
         <f t="shared" si="3"/>
@@ -4306,7 +4374,7 @@
       </c>
       <c r="B22" s="33">
         <f>Quiz!V22</f>
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="C22" s="41">
         <f>Exams!B22</f>
@@ -4318,11 +4386,11 @@
       </c>
       <c r="E22" s="33">
         <f t="shared" si="0"/>
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="F22" s="33">
         <f t="shared" si="3"/>
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G22" s="47">
         <f t="shared" si="4"/>
@@ -4335,7 +4403,7 @@
       </c>
       <c r="B23" s="33">
         <f>Quiz!V23</f>
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="C23" s="41">
         <f>Exams!B23</f>
@@ -4347,11 +4415,11 @@
       </c>
       <c r="E23" s="33">
         <f t="shared" si="0"/>
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="F23" s="33">
         <f t="shared" si="3"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="G23" s="47">
         <f t="shared" si="4"/>
@@ -4364,7 +4432,7 @@
       </c>
       <c r="B24" s="33">
         <f>Quiz!V24</f>
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="C24" s="41">
         <f>Exams!B24</f>
@@ -4376,11 +4444,11 @@
       </c>
       <c r="E24" s="33">
         <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="F24" s="33">
         <f t="shared" si="3"/>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G24" s="47">
         <f t="shared" si="4"/>
@@ -4393,7 +4461,7 @@
       </c>
       <c r="B25" s="33">
         <f>Quiz!V25</f>
-        <v>1.9</v>
+        <v>1.5333333333333334</v>
       </c>
       <c r="C25" s="41">
         <f>Exams!B25</f>
@@ -4405,11 +4473,11 @@
       </c>
       <c r="E25" s="33">
         <f t="shared" si="0"/>
-        <v>1.9</v>
+        <v>1.5333333333333334</v>
       </c>
       <c r="F25" s="33">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="G25" s="47">
         <f t="shared" si="4"/>
@@ -4422,7 +4490,7 @@
       </c>
       <c r="B26" s="33">
         <f>Quiz!V26</f>
-        <v>0.8</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="C26" s="41">
         <f>Exams!B26</f>
@@ -4434,11 +4502,11 @@
       </c>
       <c r="E26" s="33">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="F26" s="33">
         <f t="shared" ref="F26:F40" si="5">0.5*INT(E26/0.5)+INT( ((E26-INT(E26/0.5)*0.5)/0.25))*0.5</f>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G26" s="47">
         <f t="shared" ref="G26:G32" si="6">IF(F26&gt;4.75,1,0)</f>
@@ -4451,7 +4519,7 @@
       </c>
       <c r="B27" s="33">
         <f>Quiz!V27</f>
-        <v>0.6</v>
+        <v>0.53333333333333333</v>
       </c>
       <c r="C27" s="41">
         <f>Exams!B27</f>
@@ -4463,7 +4531,7 @@
       </c>
       <c r="E27" s="33">
         <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.53333333333333333</v>
       </c>
       <c r="F27" s="33">
         <f t="shared" si="5"/>
@@ -4480,7 +4548,7 @@
       </c>
       <c r="B28" s="33">
         <f>Quiz!V28</f>
-        <v>1.2</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="C28" s="41">
         <f>Exams!B28</f>
@@ -4492,7 +4560,7 @@
       </c>
       <c r="E28" s="33">
         <f t="shared" si="0"/>
-        <v>1.2</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="F28" s="33">
         <f t="shared" si="5"/>
@@ -4509,7 +4577,7 @@
       </c>
       <c r="B29" s="33">
         <f>Quiz!V29</f>
-        <v>1.5</v>
+        <v>1.1333333333333333</v>
       </c>
       <c r="C29" s="41">
         <f>Exams!B29</f>
@@ -4521,11 +4589,11 @@
       </c>
       <c r="E29" s="33">
         <f t="shared" si="0"/>
-        <v>1.5</v>
+        <v>1.1333333333333333</v>
       </c>
       <c r="F29" s="33">
         <f t="shared" si="5"/>
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G29" s="47">
         <f t="shared" si="6"/>
@@ -4538,7 +4606,7 @@
       </c>
       <c r="B30" s="33">
         <f>Quiz!V30</f>
-        <v>1.2</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="C30" s="41">
         <f>Exams!B30</f>
@@ -4550,7 +4618,7 @@
       </c>
       <c r="E30" s="33">
         <f t="shared" si="0"/>
-        <v>1.2</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="F30" s="33">
         <f t="shared" si="5"/>
@@ -4567,7 +4635,7 @@
       </c>
       <c r="B31" s="33">
         <f>Quiz!V31</f>
-        <v>0.9</v>
+        <v>0.73333333333333328</v>
       </c>
       <c r="C31" s="41">
         <f>Exams!B31</f>
@@ -4579,11 +4647,11 @@
       </c>
       <c r="E31" s="33">
         <f t="shared" si="0"/>
-        <v>0.9</v>
+        <v>0.73333333333333328</v>
       </c>
       <c r="F31" s="33">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G31" s="47">
         <f t="shared" si="6"/>
@@ -4683,7 +4751,7 @@
       </c>
       <c r="B35" s="33">
         <f>Quiz!V35</f>
-        <v>0.9</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="C35" s="41">
         <f>Exams!B35</f>
@@ -4695,11 +4763,11 @@
       </c>
       <c r="E35" s="33">
         <f t="shared" si="0"/>
-        <v>0.9</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="F35" s="33">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G35" s="47">
         <f t="shared" si="7"/>
@@ -4712,7 +4780,7 @@
       </c>
       <c r="B36" s="33">
         <f>Quiz!V36</f>
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="C36" s="41">
         <f>Exams!B36</f>
@@ -4724,7 +4792,7 @@
       </c>
       <c r="E36" s="33">
         <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="F36" s="33">
         <f t="shared" si="5"/>
@@ -4741,7 +4809,7 @@
       </c>
       <c r="B37" s="33">
         <f>Quiz!V37</f>
-        <v>0.9</v>
+        <v>1.2666666666666666</v>
       </c>
       <c r="C37" s="41">
         <f>Exams!B37</f>
@@ -4753,11 +4821,11 @@
       </c>
       <c r="E37" s="33">
         <f t="shared" si="0"/>
-        <v>0.9</v>
+        <v>1.2666666666666666</v>
       </c>
       <c r="F37" s="33">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G37" s="47">
         <f t="shared" si="7"/>
@@ -4770,7 +4838,7 @@
       </c>
       <c r="B38" s="33">
         <f>Quiz!V38</f>
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="C38" s="41">
         <f>Exams!B38</f>
@@ -4782,7 +4850,7 @@
       </c>
       <c r="E38" s="33">
         <f t="shared" si="0"/>
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="F38" s="33">
         <f t="shared" si="5"/>
@@ -4799,7 +4867,7 @@
       </c>
       <c r="B39" s="33">
         <f>Quiz!V39</f>
-        <v>1.8</v>
+        <v>1.8666666666666667</v>
       </c>
       <c r="C39" s="41">
         <f>Exams!B39</f>
@@ -4811,7 +4879,7 @@
       </c>
       <c r="E39" s="33">
         <f t="shared" si="0"/>
-        <v>1.8</v>
+        <v>1.8666666666666667</v>
       </c>
       <c r="F39" s="33">
         <f t="shared" ref="F39" si="8">0.5*INT(E39/0.5)+INT( ((E39-INT(E39/0.5)*0.5)/0.25))*0.5</f>
@@ -4828,7 +4896,7 @@
       </c>
       <c r="B40" s="33">
         <f>Quiz!V40</f>
-        <v>1.8</v>
+        <v>1.8666666666666667</v>
       </c>
       <c r="C40" s="41">
         <f>Exams!B40</f>
@@ -4840,7 +4908,7 @@
       </c>
       <c r="E40" s="33">
         <f t="shared" si="0"/>
-        <v>1.8</v>
+        <v>1.8666666666666667</v>
       </c>
       <c r="F40" s="33">
         <f t="shared" si="5"/>
@@ -4893,7 +4961,7 @@
       </c>
       <c r="B43" s="29">
         <f t="shared" ref="B43:G43" si="10">AVERAGE(B$2:B$40)</f>
-        <v>1.1025641025641026</v>
+        <v>1.0042735042735043</v>
       </c>
       <c r="C43" s="29">
         <f t="shared" si="10"/>
@@ -4905,11 +4973,11 @@
       </c>
       <c r="E43" s="29">
         <f t="shared" si="10"/>
-        <v>1.1025641025641026</v>
+        <v>1.0042735042735043</v>
       </c>
       <c r="F43" s="29">
         <f t="shared" si="10"/>
-        <v>1.1153846153846154</v>
+        <v>1.0256410256410255</v>
       </c>
       <c r="G43" s="29">
         <f t="shared" si="10"/>
@@ -4922,7 +4990,7 @@
       </c>
       <c r="B44" s="29">
         <f t="shared" ref="B44:G44" si="11">STDEV(B$2:B$40)</f>
-        <v>0.52590132128574707</v>
+        <v>0.49038590169742413</v>
       </c>
       <c r="C44" s="29">
         <f t="shared" si="11"/>
@@ -4934,11 +5002,11 @@
       </c>
       <c r="E44" s="29">
         <f t="shared" si="11"/>
-        <v>0.52590132128574707</v>
+        <v>0.49038590169742413</v>
       </c>
       <c r="F44" s="29">
         <f t="shared" si="11"/>
-        <v>0.55561178302956782</v>
+        <v>0.52501526229341711</v>
       </c>
       <c r="G44" s="29">
         <f t="shared" si="11"/>
@@ -4951,7 +5019,7 @@
       </c>
       <c r="B45" s="29">
         <f t="shared" ref="B45:G45" si="12">MEDIAN(B$2:B$40)</f>
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="C45" s="29">
         <f t="shared" si="12"/>
@@ -4963,7 +5031,7 @@
       </c>
       <c r="E45" s="29">
         <f t="shared" si="12"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="F45" s="29">
         <f t="shared" si="12"/>

--- a/phy112/Grades/grades_report_2026.xlsx
+++ b/phy112/Grades/grades_report_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ptohos/Documents/MyCourses/FYS112/2026/Grades/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7245DE6C-EF07-A04E-9886-C2EA4728E426}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD2BB3D6-A89F-D341-A33F-5D45A06012E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1640" yWindow="1200" windowWidth="32920" windowHeight="19260" tabRatio="334" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1002,7 +1002,9 @@
       <c r="E2" s="49">
         <v>4</v>
       </c>
-      <c r="F2" s="18"/>
+      <c r="F2" s="18">
+        <v>4</v>
+      </c>
       <c r="G2" s="18"/>
       <c r="H2" s="18"/>
       <c r="I2" s="18"/>
@@ -1020,7 +1022,7 @@
       <c r="U2" s="18"/>
       <c r="V2" s="33">
         <f t="shared" ref="V2:V39" si="0">$V$42 * ( (SUM(B2:U2))/((SUM($B$46:$U$46))*$B$42) )</f>
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="W2"/>
     </row>
@@ -1038,7 +1040,9 @@
       <c r="E3" s="49">
         <v>4</v>
       </c>
-      <c r="F3" s="18"/>
+      <c r="F3" s="18">
+        <v>4</v>
+      </c>
       <c r="G3" s="18"/>
       <c r="H3" s="18"/>
       <c r="I3" s="18"/>
@@ -1056,7 +1060,7 @@
       <c r="U3" s="18"/>
       <c r="V3" s="33">
         <f t="shared" si="0"/>
-        <v>0.93333333333333335</v>
+        <v>0.8</v>
       </c>
       <c r="W3"/>
     </row>
@@ -1074,7 +1078,9 @@
       <c r="E4" s="49">
         <v>4</v>
       </c>
-      <c r="F4" s="18"/>
+      <c r="F4" s="18">
+        <v>4</v>
+      </c>
       <c r="G4" s="18"/>
       <c r="H4" s="18"/>
       <c r="I4" s="18"/>
@@ -1092,7 +1098,7 @@
       <c r="U4" s="18"/>
       <c r="V4" s="33">
         <f t="shared" si="0"/>
-        <v>1.0666666666666667</v>
+        <v>0.9</v>
       </c>
       <c r="W4"/>
     </row>
@@ -1110,7 +1116,9 @@
       <c r="E5" s="49">
         <v>4</v>
       </c>
-      <c r="F5" s="18"/>
+      <c r="F5" s="18">
+        <v>4</v>
+      </c>
       <c r="G5" s="18"/>
       <c r="H5" s="18"/>
       <c r="I5" s="18"/>
@@ -1146,7 +1154,9 @@
       <c r="E6" s="49">
         <v>12</v>
       </c>
-      <c r="F6" s="18"/>
+      <c r="F6" s="18">
+        <v>12</v>
+      </c>
       <c r="G6" s="18"/>
       <c r="H6" s="18"/>
       <c r="I6" s="18"/>
@@ -1164,7 +1174,7 @@
       <c r="U6" s="18"/>
       <c r="V6" s="33">
         <f t="shared" si="0"/>
-        <v>1.3333333333333333</v>
+        <v>1.3</v>
       </c>
       <c r="W6"/>
     </row>
@@ -1182,7 +1192,9 @@
       <c r="E7" s="49">
         <v>4</v>
       </c>
-      <c r="F7" s="18"/>
+      <c r="F7" s="18">
+        <v>12</v>
+      </c>
       <c r="G7" s="18"/>
       <c r="H7" s="18"/>
       <c r="I7" s="18"/>
@@ -1200,7 +1212,7 @@
       <c r="U7" s="18"/>
       <c r="V7" s="33">
         <f t="shared" si="0"/>
-        <v>1.3333333333333333</v>
+        <v>1.3</v>
       </c>
       <c r="W7"/>
     </row>
@@ -1218,7 +1230,9 @@
       <c r="E8" s="49">
         <v>4</v>
       </c>
-      <c r="F8" s="18"/>
+      <c r="F8" s="18">
+        <v>4</v>
+      </c>
       <c r="G8" s="18"/>
       <c r="H8" s="18"/>
       <c r="I8" s="18"/>
@@ -1236,7 +1250,7 @@
       <c r="U8" s="18"/>
       <c r="V8" s="33">
         <f t="shared" si="0"/>
-        <v>1.1333333333333333</v>
+        <v>0.95</v>
       </c>
       <c r="W8"/>
     </row>
@@ -1270,7 +1284,7 @@
       <c r="U9" s="18"/>
       <c r="V9" s="33">
         <f t="shared" si="0"/>
-        <v>1.0666666666666667</v>
+        <v>0.8</v>
       </c>
       <c r="W9"/>
     </row>
@@ -1288,7 +1302,9 @@
       <c r="E10" s="49">
         <v>20</v>
       </c>
-      <c r="F10" s="18"/>
+      <c r="F10" s="18">
+        <v>12</v>
+      </c>
       <c r="G10" s="18"/>
       <c r="H10" s="18"/>
       <c r="I10" s="18"/>
@@ -1306,7 +1322,7 @@
       <c r="U10" s="18"/>
       <c r="V10" s="33">
         <f t="shared" si="0"/>
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="W10"/>
     </row>
@@ -1324,7 +1340,9 @@
       <c r="E11" s="49">
         <v>4</v>
       </c>
-      <c r="F11" s="18"/>
+      <c r="F11" s="18">
+        <v>4</v>
+      </c>
       <c r="G11" s="18"/>
       <c r="H11" s="18"/>
       <c r="I11" s="18"/>
@@ -1360,7 +1378,9 @@
       <c r="E12" s="49">
         <v>4</v>
       </c>
-      <c r="F12" s="18"/>
+      <c r="F12" s="18">
+        <v>12</v>
+      </c>
       <c r="G12" s="18"/>
       <c r="H12" s="18"/>
       <c r="I12" s="18"/>
@@ -1378,7 +1398,7 @@
       <c r="U12" s="18"/>
       <c r="V12" s="33">
         <f t="shared" si="0"/>
-        <v>0.93333333333333335</v>
+        <v>1</v>
       </c>
       <c r="W12"/>
     </row>
@@ -1396,7 +1416,9 @@
       <c r="E13" s="49">
         <v>4</v>
       </c>
-      <c r="F13" s="18"/>
+      <c r="F13" s="18">
+        <v>4</v>
+      </c>
       <c r="G13" s="18"/>
       <c r="H13" s="18"/>
       <c r="I13" s="18"/>
@@ -1414,7 +1436,7 @@
       <c r="U13" s="18"/>
       <c r="V13" s="33">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="W13"/>
     </row>
@@ -1432,7 +1454,9 @@
       <c r="E14" s="49">
         <v>4</v>
       </c>
-      <c r="F14" s="18"/>
+      <c r="F14" s="18">
+        <v>4</v>
+      </c>
       <c r="G14" s="18"/>
       <c r="H14" s="18"/>
       <c r="I14" s="18"/>
@@ -1450,7 +1474,7 @@
       <c r="U14" s="18"/>
       <c r="V14" s="33">
         <f t="shared" si="0"/>
-        <v>1.2666666666666666</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="15" spans="1:23" ht="29" customHeight="1" x14ac:dyDescent="0.15">
@@ -1467,7 +1491,9 @@
       <c r="E15" s="49">
         <v>20</v>
       </c>
-      <c r="F15" s="18"/>
+      <c r="F15" s="18">
+        <v>20</v>
+      </c>
       <c r="G15" s="18"/>
       <c r="H15" s="18"/>
       <c r="I15" s="18"/>
@@ -1485,7 +1511,7 @@
       <c r="U15" s="18"/>
       <c r="V15" s="33">
         <f t="shared" si="0"/>
-        <v>1.9333333333333333</v>
+        <v>1.95</v>
       </c>
       <c r="W15"/>
     </row>
@@ -1503,7 +1529,9 @@
       <c r="E16" s="49">
         <v>14</v>
       </c>
-      <c r="F16" s="18"/>
+      <c r="F16" s="18">
+        <v>4</v>
+      </c>
       <c r="G16" s="18"/>
       <c r="H16" s="18"/>
       <c r="I16" s="18"/>
@@ -1521,7 +1549,7 @@
       <c r="U16" s="18"/>
       <c r="V16" s="33">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="W16"/>
     </row>
@@ -1569,7 +1597,9 @@
       <c r="E18" s="49">
         <v>4</v>
       </c>
-      <c r="F18" s="18"/>
+      <c r="F18" s="18">
+        <v>4</v>
+      </c>
       <c r="G18" s="18"/>
       <c r="H18" s="18"/>
       <c r="I18" s="18"/>
@@ -1587,7 +1617,7 @@
       <c r="U18" s="18"/>
       <c r="V18" s="33">
         <f t="shared" si="0"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="W18"/>
     </row>
@@ -1605,7 +1635,9 @@
       <c r="E19" s="49">
         <v>16</v>
       </c>
-      <c r="F19" s="18"/>
+      <c r="F19" s="18">
+        <v>12</v>
+      </c>
       <c r="G19" s="18"/>
       <c r="H19" s="18"/>
       <c r="I19" s="18"/>
@@ -1623,7 +1655,7 @@
       <c r="U19" s="18"/>
       <c r="V19" s="33">
         <f t="shared" si="0"/>
-        <v>1.1333333333333333</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="W19"/>
     </row>
@@ -1639,7 +1671,9 @@
       <c r="E20" s="49">
         <v>12</v>
       </c>
-      <c r="F20" s="18"/>
+      <c r="F20" s="18">
+        <v>4</v>
+      </c>
       <c r="G20" s="18"/>
       <c r="H20" s="18"/>
       <c r="I20" s="18"/>
@@ -1657,7 +1691,7 @@
       <c r="U20" s="18"/>
       <c r="V20" s="33">
         <f t="shared" si="0"/>
-        <v>1.0666666666666667</v>
+        <v>0.9</v>
       </c>
       <c r="W20"/>
     </row>
@@ -1675,7 +1709,9 @@
       <c r="E21" s="49">
         <v>16</v>
       </c>
-      <c r="F21" s="18"/>
+      <c r="F21" s="18">
+        <v>4</v>
+      </c>
       <c r="G21" s="18"/>
       <c r="H21" s="18"/>
       <c r="I21" s="18"/>
@@ -1693,7 +1729,7 @@
       <c r="U21" s="18"/>
       <c r="V21" s="33">
         <f t="shared" si="0"/>
-        <v>1.4666666666666666</v>
+        <v>1.2</v>
       </c>
       <c r="W21"/>
     </row>
@@ -1711,7 +1747,9 @@
       <c r="E22" s="49">
         <v>4</v>
       </c>
-      <c r="F22" s="18"/>
+      <c r="F22" s="18">
+        <v>12</v>
+      </c>
       <c r="G22" s="18"/>
       <c r="H22" s="18"/>
       <c r="I22" s="18"/>
@@ -1729,7 +1767,7 @@
       <c r="U22" s="18"/>
       <c r="V22" s="33">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="W22"/>
     </row>
@@ -1747,7 +1785,9 @@
       <c r="E23" s="49">
         <v>20</v>
       </c>
-      <c r="F23" s="18"/>
+      <c r="F23" s="18">
+        <v>4</v>
+      </c>
       <c r="G23" s="18"/>
       <c r="H23" s="18"/>
       <c r="I23" s="18"/>
@@ -1765,7 +1805,7 @@
       <c r="U23" s="18"/>
       <c r="V23" s="33">
         <f t="shared" si="0"/>
-        <v>1.8</v>
+        <v>1.45</v>
       </c>
       <c r="W23"/>
     </row>
@@ -1781,7 +1821,9 @@
       <c r="E24" s="49">
         <v>12</v>
       </c>
-      <c r="F24" s="18"/>
+      <c r="F24" s="18">
+        <v>4</v>
+      </c>
       <c r="G24" s="18"/>
       <c r="H24" s="18"/>
       <c r="I24" s="18"/>
@@ -1799,7 +1841,7 @@
       <c r="U24" s="18"/>
       <c r="V24" s="33">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="W24"/>
     </row>
@@ -1835,7 +1877,7 @@
       <c r="U25" s="18"/>
       <c r="V25" s="33">
         <f t="shared" si="0"/>
-        <v>1.5333333333333334</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="W25"/>
     </row>
@@ -1853,7 +1895,9 @@
       <c r="E26" s="49">
         <v>4</v>
       </c>
-      <c r="F26" s="18"/>
+      <c r="F26" s="18">
+        <v>4</v>
+      </c>
       <c r="G26" s="18"/>
       <c r="H26" s="18"/>
       <c r="I26" s="18"/>
@@ -1871,7 +1915,7 @@
       <c r="U26" s="18"/>
       <c r="V26" s="33">
         <f t="shared" si="0"/>
-        <v>0.66666666666666663</v>
+        <v>0.6</v>
       </c>
       <c r="W26"/>
     </row>
@@ -1887,7 +1931,9 @@
       <c r="E27" s="49">
         <v>4</v>
       </c>
-      <c r="F27" s="18"/>
+      <c r="F27" s="18">
+        <v>12</v>
+      </c>
       <c r="G27" s="18"/>
       <c r="H27" s="18"/>
       <c r="I27" s="18"/>
@@ -1905,7 +1951,7 @@
       <c r="U27" s="18"/>
       <c r="V27" s="33">
         <f t="shared" si="0"/>
-        <v>0.53333333333333333</v>
+        <v>0.7</v>
       </c>
       <c r="W27"/>
     </row>
@@ -1923,7 +1969,9 @@
       <c r="E28" s="49">
         <v>4</v>
       </c>
-      <c r="F28" s="18"/>
+      <c r="F28" s="18">
+        <v>12</v>
+      </c>
       <c r="G28" s="18"/>
       <c r="H28" s="18"/>
       <c r="I28" s="18"/>
@@ -1941,7 +1989,7 @@
       <c r="U28" s="18"/>
       <c r="V28" s="33">
         <f t="shared" si="0"/>
-        <v>0.93333333333333335</v>
+        <v>1</v>
       </c>
       <c r="W28"/>
     </row>
@@ -1959,7 +2007,9 @@
       <c r="E29" s="49">
         <v>4</v>
       </c>
-      <c r="F29" s="18"/>
+      <c r="F29" s="18">
+        <v>4</v>
+      </c>
       <c r="G29" s="18"/>
       <c r="H29" s="18"/>
       <c r="I29" s="18"/>
@@ -1977,7 +2027,7 @@
       <c r="U29" s="18"/>
       <c r="V29" s="33">
         <f t="shared" si="0"/>
-        <v>1.1333333333333333</v>
+        <v>0.95</v>
       </c>
       <c r="W29"/>
     </row>
@@ -1995,7 +2045,9 @@
       <c r="E30" s="49">
         <v>4</v>
       </c>
-      <c r="F30" s="18"/>
+      <c r="F30" s="18">
+        <v>4</v>
+      </c>
       <c r="G30" s="18"/>
       <c r="H30" s="18"/>
       <c r="I30" s="18"/>
@@ -2013,7 +2065,7 @@
       <c r="U30" s="18"/>
       <c r="V30" s="33">
         <f t="shared" si="0"/>
-        <v>0.93333333333333335</v>
+        <v>0.8</v>
       </c>
       <c r="W30"/>
     </row>
@@ -2031,7 +2083,9 @@
       <c r="E31" s="49">
         <v>4</v>
       </c>
-      <c r="F31" s="18"/>
+      <c r="F31" s="18">
+        <v>4</v>
+      </c>
       <c r="G31" s="18"/>
       <c r="H31" s="18"/>
       <c r="I31" s="18"/>
@@ -2049,7 +2103,7 @@
       <c r="U31" s="18"/>
       <c r="V31" s="33">
         <f t="shared" si="0"/>
-        <v>0.73333333333333328</v>
+        <v>0.65</v>
       </c>
       <c r="W31"/>
     </row>
@@ -2067,7 +2121,9 @@
       <c r="E32" s="49">
         <v>12</v>
       </c>
-      <c r="F32" s="18"/>
+      <c r="F32" s="18">
+        <v>4</v>
+      </c>
       <c r="G32" s="18"/>
       <c r="H32" s="18"/>
       <c r="I32" s="18"/>
@@ -2085,7 +2141,7 @@
       <c r="U32" s="18"/>
       <c r="V32" s="33">
         <f t="shared" si="0"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="W32"/>
     </row>
@@ -2127,7 +2183,9 @@
       <c r="C34" s="49"/>
       <c r="D34" s="49"/>
       <c r="E34" s="49"/>
-      <c r="F34" s="18"/>
+      <c r="F34" s="18">
+        <v>4</v>
+      </c>
       <c r="G34" s="18"/>
       <c r="H34" s="18"/>
       <c r="I34" s="18"/>
@@ -2145,7 +2203,7 @@
       <c r="U34" s="18"/>
       <c r="V34" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W34"/>
     </row>
@@ -2163,7 +2221,9 @@
       <c r="E35" s="49">
         <v>1</v>
       </c>
-      <c r="F35" s="18"/>
+      <c r="F35" s="18">
+        <v>4</v>
+      </c>
       <c r="G35" s="18"/>
       <c r="H35" s="18"/>
       <c r="I35" s="18"/>
@@ -2181,7 +2241,7 @@
       <c r="U35" s="18"/>
       <c r="V35" s="33">
         <f t="shared" si="0"/>
-        <v>0.6333333333333333</v>
+        <v>0.57499999999999996</v>
       </c>
       <c r="W35"/>
     </row>
@@ -2213,7 +2273,7 @@
       <c r="U36" s="18"/>
       <c r="V36" s="33">
         <f t="shared" si="0"/>
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W36"/>
     </row>
@@ -2231,7 +2291,9 @@
       <c r="E37" s="49">
         <v>20</v>
       </c>
-      <c r="F37" s="18"/>
+      <c r="F37" s="18">
+        <v>4</v>
+      </c>
       <c r="G37" s="18"/>
       <c r="H37" s="18"/>
       <c r="I37" s="18"/>
@@ -2249,7 +2311,7 @@
       <c r="U37" s="18"/>
       <c r="V37" s="33">
         <f t="shared" si="0"/>
-        <v>1.2666666666666666</v>
+        <v>1.05</v>
       </c>
       <c r="W37"/>
     </row>
@@ -2265,7 +2327,9 @@
         <v>12</v>
       </c>
       <c r="E38" s="49"/>
-      <c r="F38" s="18"/>
+      <c r="F38" s="18">
+        <v>4</v>
+      </c>
       <c r="G38" s="18"/>
       <c r="H38" s="18"/>
       <c r="I38" s="18"/>
@@ -2283,7 +2347,7 @@
       <c r="U38" s="18"/>
       <c r="V38" s="33">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="W38"/>
     </row>
@@ -2301,7 +2365,9 @@
       <c r="E39" s="49">
         <v>20</v>
       </c>
-      <c r="F39" s="18"/>
+      <c r="F39" s="18">
+        <v>4</v>
+      </c>
       <c r="G39" s="18"/>
       <c r="H39" s="18"/>
       <c r="I39" s="18"/>
@@ -2319,7 +2385,7 @@
       <c r="U39" s="18"/>
       <c r="V39" s="33">
         <f t="shared" si="0"/>
-        <v>1.8666666666666667</v>
+        <v>1.5</v>
       </c>
       <c r="W39"/>
     </row>
@@ -2337,7 +2403,9 @@
       <c r="E40" s="49">
         <v>20</v>
       </c>
-      <c r="F40" s="18"/>
+      <c r="F40" s="18">
+        <v>12</v>
+      </c>
       <c r="G40" s="18"/>
       <c r="H40" s="18"/>
       <c r="I40" s="18"/>
@@ -2355,7 +2423,7 @@
       <c r="U40" s="18"/>
       <c r="V40" s="33">
         <f t="shared" ref="V40" si="1">$V$42 * ( (SUM(B40:U40))/((SUM($B$46:$U$46))*$B$42) )</f>
-        <v>1.8666666666666667</v>
+        <v>1.7</v>
       </c>
       <c r="W40"/>
     </row>
@@ -2473,9 +2541,9 @@
         <f t="shared" si="2"/>
         <v>8.9393939393939394</v>
       </c>
-      <c r="F43" s="29" t="e">
+      <c r="F43" s="29">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+        <v>6.4242424242424239</v>
       </c>
       <c r="G43" s="29" t="e">
         <f t="shared" si="2"/>
@@ -2539,7 +2607,7 @@
       </c>
       <c r="V43" s="29">
         <f t="shared" si="2"/>
-        <v>0.981578947368421</v>
+        <v>0.87565789473684186</v>
       </c>
       <c r="W43"/>
     </row>
@@ -2563,9 +2631,9 @@
         <f t="shared" si="3"/>
         <v>6.6140919347414675</v>
       </c>
-      <c r="F44" s="29" t="e">
+      <c r="F44" s="29">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
+        <v>4.235492172037854</v>
       </c>
       <c r="G44" s="29" t="e">
         <f t="shared" si="3"/>
@@ -2629,7 +2697,7 @@
       </c>
       <c r="V44" s="29">
         <f t="shared" si="3"/>
-        <v>0.47576064391199774</v>
+        <v>0.41339427396469808</v>
       </c>
       <c r="W44"/>
     </row>
@@ -2653,9 +2721,9 @@
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="F45" s="29" t="e">
+      <c r="F45" s="29">
         <f t="shared" si="4"/>
-        <v>#NUM!</v>
+        <v>4</v>
       </c>
       <c r="G45" s="29" t="e">
         <f t="shared" si="4"/>
@@ -2719,7 +2787,7 @@
       </c>
       <c r="V45" s="29">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="W45"/>
     </row>
@@ -2745,7 +2813,7 @@
       </c>
       <c r="F46" s="32">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G46" s="32">
         <f t="shared" si="5"/>
@@ -3793,7 +3861,7 @@
       </c>
       <c r="B2" s="33">
         <f>Quiz!V2</f>
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="C2" s="41">
         <f>Exams!B2</f>
@@ -3805,11 +3873,11 @@
       </c>
       <c r="E2" s="33">
         <f>$B2+($C2/$C$42)*3.5+($D2/$D$42)*4.5</f>
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F2" s="33">
         <f>0.5*INT(E2/0.5)+INT( ((E2-INT(E2/0.5)*0.5)/0.25))*0.5</f>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G2" s="47">
         <f>IF(F2&gt;4.75,1,0)</f>
@@ -3823,7 +3891,7 @@
       </c>
       <c r="B3" s="33">
         <f>Quiz!V3</f>
-        <v>0.93333333333333335</v>
+        <v>0.8</v>
       </c>
       <c r="C3" s="41">
         <f>Exams!B3</f>
@@ -3835,7 +3903,7 @@
       </c>
       <c r="E3" s="33">
         <f t="shared" ref="E3:E40" si="0">$B3+($C3/$C$42)*3.5+($D3/$D$42)*4.5</f>
-        <v>0.93333333333333335</v>
+        <v>0.8</v>
       </c>
       <c r="F3" s="33">
         <f t="shared" ref="F3:F19" si="1">0.5*INT(E3/0.5)+INT( ((E3-INT(E3/0.5)*0.5)/0.25))*0.5</f>
@@ -3852,7 +3920,7 @@
       </c>
       <c r="B4" s="33">
         <f>Quiz!V4</f>
-        <v>1.0666666666666667</v>
+        <v>0.9</v>
       </c>
       <c r="C4" s="41">
         <f>Exams!B4</f>
@@ -3864,7 +3932,7 @@
       </c>
       <c r="E4" s="33">
         <f t="shared" si="0"/>
-        <v>1.0666666666666667</v>
+        <v>0.9</v>
       </c>
       <c r="F4" s="33">
         <f t="shared" si="1"/>
@@ -3910,7 +3978,7 @@
       </c>
       <c r="B6" s="33">
         <f>Quiz!V6</f>
-        <v>1.3333333333333333</v>
+        <v>1.3</v>
       </c>
       <c r="C6" s="41">
         <f>Exams!B6</f>
@@ -3922,7 +3990,7 @@
       </c>
       <c r="E6" s="33">
         <f t="shared" si="0"/>
-        <v>1.3333333333333333</v>
+        <v>1.3</v>
       </c>
       <c r="F6" s="33">
         <f t="shared" si="1"/>
@@ -3939,7 +4007,7 @@
       </c>
       <c r="B7" s="33">
         <f>Quiz!V7</f>
-        <v>1.3333333333333333</v>
+        <v>1.3</v>
       </c>
       <c r="C7" s="41">
         <f>Exams!B7</f>
@@ -3951,7 +4019,7 @@
       </c>
       <c r="E7" s="33">
         <f t="shared" si="0"/>
-        <v>1.3333333333333333</v>
+        <v>1.3</v>
       </c>
       <c r="F7" s="33">
         <f t="shared" si="1"/>
@@ -3968,7 +4036,7 @@
       </c>
       <c r="B8" s="33">
         <f>Quiz!V8</f>
-        <v>1.1333333333333333</v>
+        <v>0.95</v>
       </c>
       <c r="C8" s="41">
         <f>Exams!B8</f>
@@ -3980,7 +4048,7 @@
       </c>
       <c r="E8" s="33">
         <f t="shared" si="0"/>
-        <v>1.1333333333333333</v>
+        <v>0.95</v>
       </c>
       <c r="F8" s="33">
         <f t="shared" si="1"/>
@@ -3997,7 +4065,7 @@
       </c>
       <c r="B9" s="33">
         <f>Quiz!V9</f>
-        <v>1.0666666666666667</v>
+        <v>0.8</v>
       </c>
       <c r="C9" s="41">
         <f>Exams!B9</f>
@@ -4009,7 +4077,7 @@
       </c>
       <c r="E9" s="33">
         <f t="shared" si="0"/>
-        <v>1.0666666666666667</v>
+        <v>0.8</v>
       </c>
       <c r="F9" s="33">
         <f t="shared" si="1"/>
@@ -4026,7 +4094,7 @@
       </c>
       <c r="B10" s="33">
         <f>Quiz!V10</f>
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="C10" s="41">
         <f>Exams!B10</f>
@@ -4038,7 +4106,7 @@
       </c>
       <c r="E10" s="33">
         <f t="shared" si="0"/>
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="F10" s="33">
         <f t="shared" si="1"/>
@@ -4084,7 +4152,7 @@
       </c>
       <c r="B12" s="33">
         <f>Quiz!V12</f>
-        <v>0.93333333333333335</v>
+        <v>1</v>
       </c>
       <c r="C12" s="41">
         <f>Exams!B12</f>
@@ -4096,7 +4164,7 @@
       </c>
       <c r="E12" s="33">
         <f t="shared" si="0"/>
-        <v>0.93333333333333335</v>
+        <v>1</v>
       </c>
       <c r="F12" s="33">
         <f t="shared" si="1"/>
@@ -4113,7 +4181,7 @@
       </c>
       <c r="B13" s="33">
         <f>Quiz!V13</f>
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="C13" s="41">
         <f>Exams!B13</f>
@@ -4125,7 +4193,7 @@
       </c>
       <c r="E13" s="33">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="F13" s="33">
         <f t="shared" si="1"/>
@@ -4142,7 +4210,7 @@
       </c>
       <c r="B14" s="33">
         <f>Quiz!V14</f>
-        <v>1.2666666666666666</v>
+        <v>1.05</v>
       </c>
       <c r="C14" s="41">
         <f>Exams!B14</f>
@@ -4154,11 +4222,11 @@
       </c>
       <c r="E14" s="33">
         <f t="shared" si="0"/>
-        <v>1.2666666666666666</v>
+        <v>1.05</v>
       </c>
       <c r="F14" s="33">
         <f t="shared" si="1"/>
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G14" s="47">
         <f t="shared" si="2"/>
@@ -4171,7 +4239,7 @@
       </c>
       <c r="B15" s="33">
         <f>Quiz!V15</f>
-        <v>1.9333333333333333</v>
+        <v>1.95</v>
       </c>
       <c r="C15" s="41">
         <f>Exams!B15</f>
@@ -4183,7 +4251,7 @@
       </c>
       <c r="E15" s="33">
         <f t="shared" si="0"/>
-        <v>1.9333333333333333</v>
+        <v>1.95</v>
       </c>
       <c r="F15" s="33">
         <f t="shared" si="1"/>
@@ -4200,7 +4268,7 @@
       </c>
       <c r="B16" s="33">
         <f>Quiz!V16</f>
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="C16" s="41">
         <f>Exams!B16</f>
@@ -4212,7 +4280,7 @@
       </c>
       <c r="E16" s="33">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="F16" s="33">
         <f t="shared" si="1"/>
@@ -4258,7 +4326,7 @@
       </c>
       <c r="B18" s="33">
         <f>Quiz!V18</f>
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="C18" s="41">
         <f>Exams!B18</f>
@@ -4270,7 +4338,7 @@
       </c>
       <c r="E18" s="33">
         <f t="shared" si="0"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="F18" s="33">
         <f t="shared" si="1"/>
@@ -4287,7 +4355,7 @@
       </c>
       <c r="B19" s="33">
         <f>Quiz!V19</f>
-        <v>1.1333333333333333</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="C19" s="41">
         <f>Exams!B19</f>
@@ -4299,7 +4367,7 @@
       </c>
       <c r="E19" s="33">
         <f t="shared" si="0"/>
-        <v>1.1333333333333333</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="F19" s="33">
         <f t="shared" si="1"/>
@@ -4316,7 +4384,7 @@
       </c>
       <c r="B20" s="33">
         <f>Quiz!V20</f>
-        <v>1.0666666666666667</v>
+        <v>0.9</v>
       </c>
       <c r="C20" s="41">
         <f>Exams!B20</f>
@@ -4328,7 +4396,7 @@
       </c>
       <c r="E20" s="33">
         <f t="shared" si="0"/>
-        <v>1.0666666666666667</v>
+        <v>0.9</v>
       </c>
       <c r="F20" s="33">
         <f t="shared" ref="F20:F25" si="3">0.5*INT(E20/0.5)+INT( ((E20-INT(E20/0.5)*0.5)/0.25))*0.5</f>
@@ -4345,7 +4413,7 @@
       </c>
       <c r="B21" s="33">
         <f>Quiz!V21</f>
-        <v>1.4666666666666666</v>
+        <v>1.2</v>
       </c>
       <c r="C21" s="41">
         <f>Exams!B21</f>
@@ -4357,11 +4425,11 @@
       </c>
       <c r="E21" s="33">
         <f t="shared" si="0"/>
-        <v>1.4666666666666666</v>
+        <v>1.2</v>
       </c>
       <c r="F21" s="33">
         <f t="shared" si="3"/>
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G21" s="47">
         <f t="shared" si="4"/>
@@ -4374,7 +4442,7 @@
       </c>
       <c r="B22" s="33">
         <f>Quiz!V22</f>
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="C22" s="41">
         <f>Exams!B22</f>
@@ -4386,7 +4454,7 @@
       </c>
       <c r="E22" s="33">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="F22" s="33">
         <f t="shared" si="3"/>
@@ -4403,7 +4471,7 @@
       </c>
       <c r="B23" s="33">
         <f>Quiz!V23</f>
-        <v>1.8</v>
+        <v>1.45</v>
       </c>
       <c r="C23" s="41">
         <f>Exams!B23</f>
@@ -4415,11 +4483,11 @@
       </c>
       <c r="E23" s="33">
         <f t="shared" si="0"/>
-        <v>1.8</v>
+        <v>1.45</v>
       </c>
       <c r="F23" s="33">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="G23" s="47">
         <f t="shared" si="4"/>
@@ -4432,7 +4500,7 @@
       </c>
       <c r="B24" s="33">
         <f>Quiz!V24</f>
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="C24" s="41">
         <f>Exams!B24</f>
@@ -4444,11 +4512,11 @@
       </c>
       <c r="E24" s="33">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F24" s="33">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G24" s="47">
         <f t="shared" si="4"/>
@@ -4461,7 +4529,7 @@
       </c>
       <c r="B25" s="33">
         <f>Quiz!V25</f>
-        <v>1.5333333333333334</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="C25" s="41">
         <f>Exams!B25</f>
@@ -4473,11 +4541,11 @@
       </c>
       <c r="E25" s="33">
         <f t="shared" si="0"/>
-        <v>1.5333333333333334</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="F25" s="33">
         <f t="shared" si="3"/>
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G25" s="47">
         <f t="shared" si="4"/>
@@ -4490,7 +4558,7 @@
       </c>
       <c r="B26" s="33">
         <f>Quiz!V26</f>
-        <v>0.66666666666666663</v>
+        <v>0.6</v>
       </c>
       <c r="C26" s="41">
         <f>Exams!B26</f>
@@ -4502,7 +4570,7 @@
       </c>
       <c r="E26" s="33">
         <f t="shared" si="0"/>
-        <v>0.66666666666666663</v>
+        <v>0.6</v>
       </c>
       <c r="F26" s="33">
         <f t="shared" ref="F26:F40" si="5">0.5*INT(E26/0.5)+INT( ((E26-INT(E26/0.5)*0.5)/0.25))*0.5</f>
@@ -4519,7 +4587,7 @@
       </c>
       <c r="B27" s="33">
         <f>Quiz!V27</f>
-        <v>0.53333333333333333</v>
+        <v>0.7</v>
       </c>
       <c r="C27" s="41">
         <f>Exams!B27</f>
@@ -4531,7 +4599,7 @@
       </c>
       <c r="E27" s="33">
         <f t="shared" si="0"/>
-        <v>0.53333333333333333</v>
+        <v>0.7</v>
       </c>
       <c r="F27" s="33">
         <f t="shared" si="5"/>
@@ -4548,7 +4616,7 @@
       </c>
       <c r="B28" s="33">
         <f>Quiz!V28</f>
-        <v>0.93333333333333335</v>
+        <v>1</v>
       </c>
       <c r="C28" s="41">
         <f>Exams!B28</f>
@@ -4560,7 +4628,7 @@
       </c>
       <c r="E28" s="33">
         <f t="shared" si="0"/>
-        <v>0.93333333333333335</v>
+        <v>1</v>
       </c>
       <c r="F28" s="33">
         <f t="shared" si="5"/>
@@ -4577,7 +4645,7 @@
       </c>
       <c r="B29" s="33">
         <f>Quiz!V29</f>
-        <v>1.1333333333333333</v>
+        <v>0.95</v>
       </c>
       <c r="C29" s="41">
         <f>Exams!B29</f>
@@ -4589,7 +4657,7 @@
       </c>
       <c r="E29" s="33">
         <f t="shared" si="0"/>
-        <v>1.1333333333333333</v>
+        <v>0.95</v>
       </c>
       <c r="F29" s="33">
         <f t="shared" si="5"/>
@@ -4606,7 +4674,7 @@
       </c>
       <c r="B30" s="33">
         <f>Quiz!V30</f>
-        <v>0.93333333333333335</v>
+        <v>0.8</v>
       </c>
       <c r="C30" s="41">
         <f>Exams!B30</f>
@@ -4618,7 +4686,7 @@
       </c>
       <c r="E30" s="33">
         <f t="shared" si="0"/>
-        <v>0.93333333333333335</v>
+        <v>0.8</v>
       </c>
       <c r="F30" s="33">
         <f t="shared" si="5"/>
@@ -4635,7 +4703,7 @@
       </c>
       <c r="B31" s="33">
         <f>Quiz!V31</f>
-        <v>0.73333333333333328</v>
+        <v>0.65</v>
       </c>
       <c r="C31" s="41">
         <f>Exams!B31</f>
@@ -4647,7 +4715,7 @@
       </c>
       <c r="E31" s="33">
         <f t="shared" si="0"/>
-        <v>0.73333333333333328</v>
+        <v>0.65</v>
       </c>
       <c r="F31" s="33">
         <f t="shared" si="5"/>
@@ -4664,7 +4732,7 @@
       </c>
       <c r="B32" s="33">
         <f>Quiz!V32</f>
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="C32" s="41">
         <f>Exams!B32</f>
@@ -4676,7 +4744,7 @@
       </c>
       <c r="E32" s="33">
         <f t="shared" si="0"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="F32" s="33">
         <f t="shared" si="5"/>
@@ -4722,7 +4790,7 @@
       </c>
       <c r="B34" s="33">
         <f>Quiz!V34</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C34" s="41">
         <f>Exams!B34</f>
@@ -4734,7 +4802,7 @@
       </c>
       <c r="E34" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="F34" s="33">
         <f t="shared" si="5"/>
@@ -4751,7 +4819,7 @@
       </c>
       <c r="B35" s="33">
         <f>Quiz!V35</f>
-        <v>0.6333333333333333</v>
+        <v>0.57499999999999996</v>
       </c>
       <c r="C35" s="41">
         <f>Exams!B35</f>
@@ -4763,7 +4831,7 @@
       </c>
       <c r="E35" s="33">
         <f t="shared" si="0"/>
-        <v>0.6333333333333333</v>
+        <v>0.57499999999999996</v>
       </c>
       <c r="F35" s="33">
         <f t="shared" si="5"/>
@@ -4780,7 +4848,7 @@
       </c>
       <c r="B36" s="33">
         <f>Quiz!V36</f>
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="C36" s="41">
         <f>Exams!B36</f>
@@ -4792,7 +4860,7 @@
       </c>
       <c r="E36" s="33">
         <f t="shared" si="0"/>
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="F36" s="33">
         <f t="shared" si="5"/>
@@ -4809,7 +4877,7 @@
       </c>
       <c r="B37" s="33">
         <f>Quiz!V37</f>
-        <v>1.2666666666666666</v>
+        <v>1.05</v>
       </c>
       <c r="C37" s="41">
         <f>Exams!B37</f>
@@ -4821,11 +4889,11 @@
       </c>
       <c r="E37" s="33">
         <f t="shared" si="0"/>
-        <v>1.2666666666666666</v>
+        <v>1.05</v>
       </c>
       <c r="F37" s="33">
         <f t="shared" si="5"/>
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G37" s="47">
         <f t="shared" si="7"/>
@@ -4838,7 +4906,7 @@
       </c>
       <c r="B38" s="33">
         <f>Quiz!V38</f>
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="C38" s="41">
         <f>Exams!B38</f>
@@ -4850,11 +4918,11 @@
       </c>
       <c r="E38" s="33">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F38" s="33">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G38" s="47">
         <f t="shared" si="7"/>
@@ -4867,7 +4935,7 @@
       </c>
       <c r="B39" s="33">
         <f>Quiz!V39</f>
-        <v>1.8666666666666667</v>
+        <v>1.5</v>
       </c>
       <c r="C39" s="41">
         <f>Exams!B39</f>
@@ -4879,11 +4947,11 @@
       </c>
       <c r="E39" s="33">
         <f t="shared" si="0"/>
-        <v>1.8666666666666667</v>
+        <v>1.5</v>
       </c>
       <c r="F39" s="33">
         <f t="shared" ref="F39" si="8">0.5*INT(E39/0.5)+INT( ((E39-INT(E39/0.5)*0.5)/0.25))*0.5</f>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="G39" s="47">
         <f t="shared" ref="G39" si="9">IF(F39&gt;4.75,1,0)</f>
@@ -4896,7 +4964,7 @@
       </c>
       <c r="B40" s="33">
         <f>Quiz!V40</f>
-        <v>1.8666666666666667</v>
+        <v>1.7</v>
       </c>
       <c r="C40" s="41">
         <f>Exams!B40</f>
@@ -4908,11 +4976,11 @@
       </c>
       <c r="E40" s="33">
         <f t="shared" si="0"/>
-        <v>1.8666666666666667</v>
+        <v>1.7</v>
       </c>
       <c r="F40" s="33">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="G40" s="47">
         <f t="shared" si="7"/>
@@ -4961,7 +5029,7 @@
       </c>
       <c r="B43" s="29">
         <f t="shared" ref="B43:G43" si="10">AVERAGE(B$2:B$40)</f>
-        <v>1.0042735042735043</v>
+        <v>0.89679487179487161</v>
       </c>
       <c r="C43" s="29">
         <f t="shared" si="10"/>
@@ -4973,11 +5041,11 @@
       </c>
       <c r="E43" s="29">
         <f t="shared" si="10"/>
-        <v>1.0042735042735043</v>
+        <v>0.89679487179487161</v>
       </c>
       <c r="F43" s="29">
         <f t="shared" si="10"/>
-        <v>1.0256410256410255</v>
+        <v>0.89743589743589747</v>
       </c>
       <c r="G43" s="29">
         <f t="shared" si="10"/>
@@ -4990,7 +5058,7 @@
       </c>
       <c r="B44" s="29">
         <f t="shared" ref="B44:G44" si="11">STDEV(B$2:B$40)</f>
-        <v>0.49038590169742413</v>
+        <v>0.42874432201163926</v>
       </c>
       <c r="C44" s="29">
         <f t="shared" si="11"/>
@@ -5002,11 +5070,11 @@
       </c>
       <c r="E44" s="29">
         <f t="shared" si="11"/>
-        <v>0.49038590169742413</v>
+        <v>0.42874432201163926</v>
       </c>
       <c r="F44" s="29">
         <f t="shared" si="11"/>
-        <v>0.52501526229341711</v>
+        <v>0.44691173006191792</v>
       </c>
       <c r="G44" s="29">
         <f t="shared" si="11"/>
@@ -5019,7 +5087,7 @@
       </c>
       <c r="B45" s="29">
         <f t="shared" ref="B45:G45" si="12">MEDIAN(B$2:B$40)</f>
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="C45" s="29">
         <f t="shared" si="12"/>
@@ -5031,7 +5099,7 @@
       </c>
       <c r="E45" s="29">
         <f t="shared" si="12"/>
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="F45" s="29">
         <f t="shared" si="12"/>

--- a/phy112/Grades/grades_report_2026.xlsx
+++ b/phy112/Grades/grades_report_2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr date1904="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ptohos/Documents/MyCourses/FYS112/2026/Grades/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD2BB3D6-A89F-D341-A33F-5D45A06012E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7217C8FA-18CD-B94D-9639-D2AC54D3C4D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1640" yWindow="1200" windowWidth="32920" windowHeight="19260" tabRatio="334" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1005,7 +1005,9 @@
       <c r="F2" s="18">
         <v>4</v>
       </c>
-      <c r="G2" s="18"/>
+      <c r="G2" s="18">
+        <v>12</v>
+      </c>
       <c r="H2" s="18"/>
       <c r="I2" s="18"/>
       <c r="J2" s="18"/>
@@ -1022,7 +1024,7 @@
       <c r="U2" s="18"/>
       <c r="V2" s="33">
         <f t="shared" ref="V2:V39" si="0">$V$42 * ( (SUM(B2:U2))/((SUM($B$46:$U$46))*$B$42) )</f>
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="W2"/>
     </row>
@@ -1043,7 +1045,9 @@
       <c r="F3" s="18">
         <v>4</v>
       </c>
-      <c r="G3" s="18"/>
+      <c r="G3" s="18">
+        <v>4</v>
+      </c>
       <c r="H3" s="18"/>
       <c r="I3" s="18"/>
       <c r="J3" s="18"/>
@@ -1060,7 +1064,7 @@
       <c r="U3" s="18"/>
       <c r="V3" s="33">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.72</v>
       </c>
       <c r="W3"/>
     </row>
@@ -1081,7 +1085,9 @@
       <c r="F4" s="18">
         <v>4</v>
       </c>
-      <c r="G4" s="18"/>
+      <c r="G4" s="18">
+        <v>15</v>
+      </c>
       <c r="H4" s="18"/>
       <c r="I4" s="18"/>
       <c r="J4" s="18"/>
@@ -1098,7 +1104,7 @@
       <c r="U4" s="18"/>
       <c r="V4" s="33">
         <f t="shared" si="0"/>
-        <v>0.9</v>
+        <v>1.02</v>
       </c>
       <c r="W4"/>
     </row>
@@ -1136,7 +1142,7 @@
       <c r="U5" s="18"/>
       <c r="V5" s="33">
         <f t="shared" si="0"/>
-        <v>0.4</v>
+        <v>0.32</v>
       </c>
       <c r="W5"/>
     </row>
@@ -1157,7 +1163,9 @@
       <c r="F6" s="18">
         <v>12</v>
       </c>
-      <c r="G6" s="18"/>
+      <c r="G6" s="18">
+        <v>4</v>
+      </c>
       <c r="H6" s="18"/>
       <c r="I6" s="18"/>
       <c r="J6" s="18"/>
@@ -1174,7 +1182,7 @@
       <c r="U6" s="18"/>
       <c r="V6" s="33">
         <f t="shared" si="0"/>
-        <v>1.3</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="W6"/>
     </row>
@@ -1195,7 +1203,9 @@
       <c r="F7" s="18">
         <v>12</v>
       </c>
-      <c r="G7" s="18"/>
+      <c r="G7" s="18">
+        <v>20</v>
+      </c>
       <c r="H7" s="18"/>
       <c r="I7" s="18"/>
       <c r="J7" s="18"/>
@@ -1212,7 +1222,7 @@
       <c r="U7" s="18"/>
       <c r="V7" s="33">
         <f t="shared" si="0"/>
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="W7"/>
     </row>
@@ -1233,7 +1243,9 @@
       <c r="F8" s="18">
         <v>4</v>
       </c>
-      <c r="G8" s="18"/>
+      <c r="G8" s="18">
+        <v>4</v>
+      </c>
       <c r="H8" s="18"/>
       <c r="I8" s="18"/>
       <c r="J8" s="18"/>
@@ -1250,7 +1262,7 @@
       <c r="U8" s="18"/>
       <c r="V8" s="33">
         <f t="shared" si="0"/>
-        <v>0.95</v>
+        <v>0.84</v>
       </c>
       <c r="W8"/>
     </row>
@@ -1267,7 +1279,9 @@
         <v>20</v>
       </c>
       <c r="F9" s="18"/>
-      <c r="G9" s="18"/>
+      <c r="G9" s="18">
+        <v>4</v>
+      </c>
       <c r="H9" s="18"/>
       <c r="I9" s="18"/>
       <c r="J9" s="18"/>
@@ -1284,7 +1298,7 @@
       <c r="U9" s="18"/>
       <c r="V9" s="33">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.72</v>
       </c>
       <c r="W9"/>
     </row>
@@ -1322,7 +1336,7 @@
       <c r="U10" s="18"/>
       <c r="V10" s="33">
         <f t="shared" si="0"/>
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="W10"/>
     </row>
@@ -1360,7 +1374,7 @@
       <c r="U11" s="18"/>
       <c r="V11" s="33">
         <f t="shared" si="0"/>
-        <v>0.4</v>
+        <v>0.32</v>
       </c>
       <c r="W11"/>
     </row>
@@ -1381,7 +1395,9 @@
       <c r="F12" s="18">
         <v>12</v>
       </c>
-      <c r="G12" s="18"/>
+      <c r="G12" s="18">
+        <v>12</v>
+      </c>
       <c r="H12" s="18"/>
       <c r="I12" s="18"/>
       <c r="J12" s="18"/>
@@ -1398,7 +1414,7 @@
       <c r="U12" s="18"/>
       <c r="V12" s="33">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="W12"/>
     </row>
@@ -1419,7 +1435,9 @@
       <c r="F13" s="18">
         <v>4</v>
       </c>
-      <c r="G13" s="18"/>
+      <c r="G13" s="18">
+        <v>4</v>
+      </c>
       <c r="H13" s="18"/>
       <c r="I13" s="18"/>
       <c r="J13" s="18"/>
@@ -1436,7 +1454,7 @@
       <c r="U13" s="18"/>
       <c r="V13" s="33">
         <f t="shared" si="0"/>
-        <v>0.85</v>
+        <v>0.76</v>
       </c>
       <c r="W13"/>
     </row>
@@ -1457,7 +1475,9 @@
       <c r="F14" s="18">
         <v>4</v>
       </c>
-      <c r="G14" s="18"/>
+      <c r="G14" s="18">
+        <v>12</v>
+      </c>
       <c r="H14" s="18"/>
       <c r="I14" s="18"/>
       <c r="J14" s="18"/>
@@ -1474,7 +1494,7 @@
       <c r="U14" s="18"/>
       <c r="V14" s="33">
         <f t="shared" si="0"/>
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="15" spans="1:23" ht="29" customHeight="1" x14ac:dyDescent="0.15">
@@ -1494,7 +1514,9 @@
       <c r="F15" s="18">
         <v>20</v>
       </c>
-      <c r="G15" s="18"/>
+      <c r="G15" s="18">
+        <v>12</v>
+      </c>
       <c r="H15" s="18"/>
       <c r="I15" s="18"/>
       <c r="J15" s="18"/>
@@ -1511,7 +1533,7 @@
       <c r="U15" s="18"/>
       <c r="V15" s="33">
         <f t="shared" si="0"/>
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="W15"/>
     </row>
@@ -1532,7 +1554,9 @@
       <c r="F16" s="18">
         <v>4</v>
       </c>
-      <c r="G16" s="18"/>
+      <c r="G16" s="18">
+        <v>4</v>
+      </c>
       <c r="H16" s="18"/>
       <c r="I16" s="18"/>
       <c r="J16" s="18"/>
@@ -1549,7 +1573,7 @@
       <c r="U16" s="18"/>
       <c r="V16" s="33">
         <f t="shared" si="0"/>
-        <v>0.85</v>
+        <v>0.76</v>
       </c>
       <c r="W16"/>
     </row>
@@ -1600,7 +1624,9 @@
       <c r="F18" s="18">
         <v>4</v>
       </c>
-      <c r="G18" s="18"/>
+      <c r="G18" s="18">
+        <v>4</v>
+      </c>
       <c r="H18" s="18"/>
       <c r="I18" s="18"/>
       <c r="J18" s="18"/>
@@ -1617,7 +1643,7 @@
       <c r="U18" s="18"/>
       <c r="V18" s="33">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="W18"/>
     </row>
@@ -1638,7 +1664,9 @@
       <c r="F19" s="18">
         <v>12</v>
       </c>
-      <c r="G19" s="18"/>
+      <c r="G19" s="18">
+        <v>12</v>
+      </c>
       <c r="H19" s="18"/>
       <c r="I19" s="18"/>
       <c r="J19" s="18"/>
@@ -1655,7 +1683,7 @@
       <c r="U19" s="18"/>
       <c r="V19" s="33">
         <f t="shared" si="0"/>
-        <v>1.1499999999999999</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="W19"/>
     </row>
@@ -1674,7 +1702,9 @@
       <c r="F20" s="18">
         <v>4</v>
       </c>
-      <c r="G20" s="18"/>
+      <c r="G20" s="18">
+        <v>4</v>
+      </c>
       <c r="H20" s="18"/>
       <c r="I20" s="18"/>
       <c r="J20" s="18"/>
@@ -1691,7 +1721,7 @@
       <c r="U20" s="18"/>
       <c r="V20" s="33">
         <f t="shared" si="0"/>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="W20"/>
     </row>
@@ -1712,7 +1742,9 @@
       <c r="F21" s="18">
         <v>4</v>
       </c>
-      <c r="G21" s="18"/>
+      <c r="G21" s="18">
+        <v>20</v>
+      </c>
       <c r="H21" s="18"/>
       <c r="I21" s="18"/>
       <c r="J21" s="18"/>
@@ -1729,7 +1761,7 @@
       <c r="U21" s="18"/>
       <c r="V21" s="33">
         <f t="shared" si="0"/>
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="W21"/>
     </row>
@@ -1750,7 +1782,9 @@
       <c r="F22" s="18">
         <v>12</v>
       </c>
-      <c r="G22" s="18"/>
+      <c r="G22" s="18">
+        <v>12</v>
+      </c>
       <c r="H22" s="18"/>
       <c r="I22" s="18"/>
       <c r="J22" s="18"/>
@@ -1767,7 +1801,7 @@
       <c r="U22" s="18"/>
       <c r="V22" s="33">
         <f t="shared" si="0"/>
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="W22"/>
     </row>
@@ -1788,7 +1822,9 @@
       <c r="F23" s="18">
         <v>4</v>
       </c>
-      <c r="G23" s="18"/>
+      <c r="G23" s="18">
+        <v>20</v>
+      </c>
       <c r="H23" s="18"/>
       <c r="I23" s="18"/>
       <c r="J23" s="18"/>
@@ -1805,7 +1841,7 @@
       <c r="U23" s="18"/>
       <c r="V23" s="33">
         <f t="shared" si="0"/>
-        <v>1.45</v>
+        <v>1.56</v>
       </c>
       <c r="W23"/>
     </row>
@@ -1824,7 +1860,9 @@
       <c r="F24" s="18">
         <v>4</v>
       </c>
-      <c r="G24" s="18"/>
+      <c r="G24" s="18">
+        <v>4</v>
+      </c>
       <c r="H24" s="18"/>
       <c r="I24" s="18"/>
       <c r="J24" s="18"/>
@@ -1841,7 +1879,7 @@
       <c r="U24" s="18"/>
       <c r="V24" s="33">
         <f t="shared" si="0"/>
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="W24"/>
     </row>
@@ -1877,7 +1915,7 @@
       <c r="U25" s="18"/>
       <c r="V25" s="33">
         <f t="shared" si="0"/>
-        <v>1.1499999999999999</v>
+        <v>0.92</v>
       </c>
       <c r="W25"/>
     </row>
@@ -1898,7 +1936,9 @@
       <c r="F26" s="18">
         <v>4</v>
       </c>
-      <c r="G26" s="18"/>
+      <c r="G26" s="18">
+        <v>4</v>
+      </c>
       <c r="H26" s="18"/>
       <c r="I26" s="18"/>
       <c r="J26" s="18"/>
@@ -1915,7 +1955,7 @@
       <c r="U26" s="18"/>
       <c r="V26" s="33">
         <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="W26"/>
     </row>
@@ -1934,7 +1974,9 @@
       <c r="F27" s="18">
         <v>12</v>
       </c>
-      <c r="G27" s="18"/>
+      <c r="G27" s="18">
+        <v>4</v>
+      </c>
       <c r="H27" s="18"/>
       <c r="I27" s="18"/>
       <c r="J27" s="18"/>
@@ -1951,7 +1993,7 @@
       <c r="U27" s="18"/>
       <c r="V27" s="33">
         <f t="shared" si="0"/>
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="W27"/>
     </row>
@@ -1972,7 +2014,9 @@
       <c r="F28" s="18">
         <v>12</v>
       </c>
-      <c r="G28" s="18"/>
+      <c r="G28" s="18">
+        <v>4</v>
+      </c>
       <c r="H28" s="18"/>
       <c r="I28" s="18"/>
       <c r="J28" s="18"/>
@@ -1989,7 +2033,7 @@
       <c r="U28" s="18"/>
       <c r="V28" s="33">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="W28"/>
     </row>
@@ -2010,7 +2054,9 @@
       <c r="F29" s="18">
         <v>4</v>
       </c>
-      <c r="G29" s="18"/>
+      <c r="G29" s="18">
+        <v>4</v>
+      </c>
       <c r="H29" s="18"/>
       <c r="I29" s="18"/>
       <c r="J29" s="18"/>
@@ -2027,7 +2073,7 @@
       <c r="U29" s="18"/>
       <c r="V29" s="33">
         <f t="shared" si="0"/>
-        <v>0.95</v>
+        <v>0.84</v>
       </c>
       <c r="W29"/>
     </row>
@@ -2048,7 +2094,9 @@
       <c r="F30" s="18">
         <v>4</v>
       </c>
-      <c r="G30" s="18"/>
+      <c r="G30" s="18">
+        <v>12</v>
+      </c>
       <c r="H30" s="18"/>
       <c r="I30" s="18"/>
       <c r="J30" s="18"/>
@@ -2065,7 +2113,7 @@
       <c r="U30" s="18"/>
       <c r="V30" s="33">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
       <c r="W30"/>
     </row>
@@ -2103,7 +2151,7 @@
       <c r="U31" s="18"/>
       <c r="V31" s="33">
         <f t="shared" si="0"/>
-        <v>0.65</v>
+        <v>0.52</v>
       </c>
       <c r="W31"/>
     </row>
@@ -2124,7 +2172,9 @@
       <c r="F32" s="18">
         <v>4</v>
       </c>
-      <c r="G32" s="18"/>
+      <c r="G32" s="18">
+        <v>12</v>
+      </c>
       <c r="H32" s="18"/>
       <c r="I32" s="18"/>
       <c r="J32" s="18"/>
@@ -2141,7 +2191,7 @@
       <c r="U32" s="18"/>
       <c r="V32" s="33">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="W32"/>
     </row>
@@ -2186,7 +2236,9 @@
       <c r="F34" s="18">
         <v>4</v>
       </c>
-      <c r="G34" s="18"/>
+      <c r="G34" s="18">
+        <v>12</v>
+      </c>
       <c r="H34" s="18"/>
       <c r="I34" s="18"/>
       <c r="J34" s="18"/>
@@ -2203,7 +2255,7 @@
       <c r="U34" s="18"/>
       <c r="V34" s="33">
         <f t="shared" si="0"/>
-        <v>0.1</v>
+        <v>0.32</v>
       </c>
       <c r="W34"/>
     </row>
@@ -2224,7 +2276,9 @@
       <c r="F35" s="18">
         <v>4</v>
       </c>
-      <c r="G35" s="18"/>
+      <c r="G35" s="18">
+        <v>12</v>
+      </c>
       <c r="H35" s="18"/>
       <c r="I35" s="18"/>
       <c r="J35" s="18"/>
@@ -2241,7 +2295,7 @@
       <c r="U35" s="18"/>
       <c r="V35" s="33">
         <f t="shared" si="0"/>
-        <v>0.57499999999999996</v>
+        <v>0.7</v>
       </c>
       <c r="W35"/>
     </row>
@@ -2256,7 +2310,9 @@
       <c r="D36" s="49"/>
       <c r="E36" s="49"/>
       <c r="F36" s="18"/>
-      <c r="G36" s="18"/>
+      <c r="G36" s="18">
+        <v>12</v>
+      </c>
       <c r="H36" s="18"/>
       <c r="I36" s="18"/>
       <c r="J36" s="18"/>
@@ -2273,7 +2329,7 @@
       <c r="U36" s="18"/>
       <c r="V36" s="33">
         <f t="shared" si="0"/>
-        <v>0.3</v>
+        <v>0.48</v>
       </c>
       <c r="W36"/>
     </row>
@@ -2294,7 +2350,9 @@
       <c r="F37" s="18">
         <v>4</v>
       </c>
-      <c r="G37" s="18"/>
+      <c r="G37" s="18">
+        <v>12</v>
+      </c>
       <c r="H37" s="18"/>
       <c r="I37" s="18"/>
       <c r="J37" s="18"/>
@@ -2311,7 +2369,7 @@
       <c r="U37" s="18"/>
       <c r="V37" s="33">
         <f t="shared" si="0"/>
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="W37"/>
     </row>
@@ -2330,7 +2388,9 @@
       <c r="F38" s="18">
         <v>4</v>
       </c>
-      <c r="G38" s="18"/>
+      <c r="G38" s="18">
+        <v>12</v>
+      </c>
       <c r="H38" s="18"/>
       <c r="I38" s="18"/>
       <c r="J38" s="18"/>
@@ -2347,7 +2407,7 @@
       <c r="U38" s="18"/>
       <c r="V38" s="33">
         <f t="shared" si="0"/>
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="W38"/>
     </row>
@@ -2368,7 +2428,9 @@
       <c r="F39" s="18">
         <v>4</v>
       </c>
-      <c r="G39" s="18"/>
+      <c r="G39" s="18">
+        <v>4</v>
+      </c>
       <c r="H39" s="18"/>
       <c r="I39" s="18"/>
       <c r="J39" s="18"/>
@@ -2385,7 +2447,7 @@
       <c r="U39" s="18"/>
       <c r="V39" s="33">
         <f t="shared" si="0"/>
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="W39"/>
     </row>
@@ -2423,7 +2485,7 @@
       <c r="U40" s="18"/>
       <c r="V40" s="33">
         <f t="shared" ref="V40" si="1">$V$42 * ( (SUM(B40:U40))/((SUM($B$46:$U$46))*$B$42) )</f>
-        <v>1.7</v>
+        <v>1.36</v>
       </c>
       <c r="W40"/>
     </row>
@@ -2545,9 +2607,9 @@
         <f t="shared" si="2"/>
         <v>6.4242424242424239</v>
       </c>
-      <c r="G43" s="29" t="e">
+      <c r="G43" s="29">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+        <v>9.258064516129032</v>
       </c>
       <c r="H43" s="29" t="e">
         <f t="shared" si="2"/>
@@ -2607,7 +2669,7 @@
       </c>
       <c r="V43" s="29">
         <f t="shared" si="2"/>
-        <v>0.87565789473684186</v>
+        <v>0.85157894736842088</v>
       </c>
       <c r="W43"/>
     </row>
@@ -2635,9 +2697,9 @@
         <f t="shared" si="3"/>
         <v>4.235492172037854</v>
       </c>
-      <c r="G44" s="29" t="e">
+      <c r="G44" s="29">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
+        <v>5.3663627777448664</v>
       </c>
       <c r="H44" s="29" t="e">
         <f t="shared" si="3"/>
@@ -2697,7 +2759,7 @@
       </c>
       <c r="V44" s="29">
         <f t="shared" si="3"/>
-        <v>0.41339427396469808</v>
+        <v>0.3871065662047885</v>
       </c>
       <c r="W44"/>
     </row>
@@ -2725,9 +2787,9 @@
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="G45" s="29" t="e">
+      <c r="G45" s="29">
         <f t="shared" si="4"/>
-        <v>#NUM!</v>
+        <v>12</v>
       </c>
       <c r="H45" s="29" t="e">
         <f t="shared" si="4"/>
@@ -2787,7 +2849,7 @@
       </c>
       <c r="V45" s="29">
         <f t="shared" si="4"/>
-        <v>0.9</v>
+        <v>0.84</v>
       </c>
       <c r="W45"/>
     </row>
@@ -2817,7 +2879,7 @@
       </c>
       <c r="G46" s="32">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H46" s="32">
         <f t="shared" si="5"/>
@@ -3861,7 +3923,7 @@
       </c>
       <c r="B2" s="33">
         <f>Quiz!V2</f>
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="C2" s="41">
         <f>Exams!B2</f>
@@ -3873,11 +3935,11 @@
       </c>
       <c r="E2" s="33">
         <f>$B2+($C2/$C$42)*3.5+($D2/$D$42)*4.5</f>
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="F2" s="33">
         <f>0.5*INT(E2/0.5)+INT( ((E2-INT(E2/0.5)*0.5)/0.25))*0.5</f>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G2" s="47">
         <f>IF(F2&gt;4.75,1,0)</f>
@@ -3891,7 +3953,7 @@
       </c>
       <c r="B3" s="33">
         <f>Quiz!V3</f>
-        <v>0.8</v>
+        <v>0.72</v>
       </c>
       <c r="C3" s="41">
         <f>Exams!B3</f>
@@ -3903,11 +3965,11 @@
       </c>
       <c r="E3" s="33">
         <f t="shared" ref="E3:E40" si="0">$B3+($C3/$C$42)*3.5+($D3/$D$42)*4.5</f>
-        <v>0.8</v>
+        <v>0.72</v>
       </c>
       <c r="F3" s="33">
         <f t="shared" ref="F3:F19" si="1">0.5*INT(E3/0.5)+INT( ((E3-INT(E3/0.5)*0.5)/0.25))*0.5</f>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G3" s="47">
         <f t="shared" ref="G3:G19" si="2">IF(F3&gt;4.75,1,0)</f>
@@ -3920,7 +3982,7 @@
       </c>
       <c r="B4" s="33">
         <f>Quiz!V4</f>
-        <v>0.9</v>
+        <v>1.02</v>
       </c>
       <c r="C4" s="41">
         <f>Exams!B4</f>
@@ -3932,7 +3994,7 @@
       </c>
       <c r="E4" s="33">
         <f t="shared" si="0"/>
-        <v>0.9</v>
+        <v>1.02</v>
       </c>
       <c r="F4" s="33">
         <f t="shared" si="1"/>
@@ -3949,7 +4011,7 @@
       </c>
       <c r="B5" s="33">
         <f>Quiz!V5</f>
-        <v>0.4</v>
+        <v>0.32</v>
       </c>
       <c r="C5" s="41">
         <f>Exams!B5</f>
@@ -3961,7 +4023,7 @@
       </c>
       <c r="E5" s="33">
         <f t="shared" si="0"/>
-        <v>0.4</v>
+        <v>0.32</v>
       </c>
       <c r="F5" s="33">
         <f t="shared" si="1"/>
@@ -3978,7 +4040,7 @@
       </c>
       <c r="B6" s="33">
         <f>Quiz!V6</f>
-        <v>1.3</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="C6" s="41">
         <f>Exams!B6</f>
@@ -3990,11 +4052,11 @@
       </c>
       <c r="E6" s="33">
         <f t="shared" si="0"/>
-        <v>1.3</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="F6" s="33">
         <f t="shared" si="1"/>
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G6" s="47">
         <f t="shared" si="2"/>
@@ -4007,7 +4069,7 @@
       </c>
       <c r="B7" s="33">
         <f>Quiz!V7</f>
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="C7" s="41">
         <f>Exams!B7</f>
@@ -4019,7 +4081,7 @@
       </c>
       <c r="E7" s="33">
         <f t="shared" si="0"/>
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="F7" s="33">
         <f t="shared" si="1"/>
@@ -4036,7 +4098,7 @@
       </c>
       <c r="B8" s="33">
         <f>Quiz!V8</f>
-        <v>0.95</v>
+        <v>0.84</v>
       </c>
       <c r="C8" s="41">
         <f>Exams!B8</f>
@@ -4048,7 +4110,7 @@
       </c>
       <c r="E8" s="33">
         <f t="shared" si="0"/>
-        <v>0.95</v>
+        <v>0.84</v>
       </c>
       <c r="F8" s="33">
         <f t="shared" si="1"/>
@@ -4065,7 +4127,7 @@
       </c>
       <c r="B9" s="33">
         <f>Quiz!V9</f>
-        <v>0.8</v>
+        <v>0.72</v>
       </c>
       <c r="C9" s="41">
         <f>Exams!B9</f>
@@ -4077,11 +4139,11 @@
       </c>
       <c r="E9" s="33">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.72</v>
       </c>
       <c r="F9" s="33">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G9" s="47">
         <f t="shared" si="2"/>
@@ -4094,7 +4156,7 @@
       </c>
       <c r="B10" s="33">
         <f>Quiz!V10</f>
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="C10" s="41">
         <f>Exams!B10</f>
@@ -4106,11 +4168,11 @@
       </c>
       <c r="E10" s="33">
         <f t="shared" si="0"/>
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="F10" s="33">
         <f t="shared" si="1"/>
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G10" s="47">
         <f t="shared" si="2"/>
@@ -4123,7 +4185,7 @@
       </c>
       <c r="B11" s="33">
         <f>Quiz!V11</f>
-        <v>0.4</v>
+        <v>0.32</v>
       </c>
       <c r="C11" s="41">
         <f>Exams!B11</f>
@@ -4135,7 +4197,7 @@
       </c>
       <c r="E11" s="33">
         <f t="shared" si="0"/>
-        <v>0.4</v>
+        <v>0.32</v>
       </c>
       <c r="F11" s="33">
         <f t="shared" si="1"/>
@@ -4152,7 +4214,7 @@
       </c>
       <c r="B12" s="33">
         <f>Quiz!V12</f>
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="C12" s="41">
         <f>Exams!B12</f>
@@ -4164,7 +4226,7 @@
       </c>
       <c r="E12" s="33">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="F12" s="33">
         <f t="shared" si="1"/>
@@ -4181,7 +4243,7 @@
       </c>
       <c r="B13" s="33">
         <f>Quiz!V13</f>
-        <v>0.85</v>
+        <v>0.76</v>
       </c>
       <c r="C13" s="41">
         <f>Exams!B13</f>
@@ -4193,7 +4255,7 @@
       </c>
       <c r="E13" s="33">
         <f t="shared" si="0"/>
-        <v>0.85</v>
+        <v>0.76</v>
       </c>
       <c r="F13" s="33">
         <f t="shared" si="1"/>
@@ -4210,7 +4272,7 @@
       </c>
       <c r="B14" s="33">
         <f>Quiz!V14</f>
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="C14" s="41">
         <f>Exams!B14</f>
@@ -4222,7 +4284,7 @@
       </c>
       <c r="E14" s="33">
         <f t="shared" si="0"/>
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="F14" s="33">
         <f t="shared" si="1"/>
@@ -4239,7 +4301,7 @@
       </c>
       <c r="B15" s="33">
         <f>Quiz!V15</f>
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="C15" s="41">
         <f>Exams!B15</f>
@@ -4251,7 +4313,7 @@
       </c>
       <c r="E15" s="33">
         <f t="shared" si="0"/>
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="F15" s="33">
         <f t="shared" si="1"/>
@@ -4268,7 +4330,7 @@
       </c>
       <c r="B16" s="33">
         <f>Quiz!V16</f>
-        <v>0.85</v>
+        <v>0.76</v>
       </c>
       <c r="C16" s="41">
         <f>Exams!B16</f>
@@ -4280,7 +4342,7 @@
       </c>
       <c r="E16" s="33">
         <f t="shared" si="0"/>
-        <v>0.85</v>
+        <v>0.76</v>
       </c>
       <c r="F16" s="33">
         <f t="shared" si="1"/>
@@ -4326,7 +4388,7 @@
       </c>
       <c r="B18" s="33">
         <f>Quiz!V18</f>
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="C18" s="41">
         <f>Exams!B18</f>
@@ -4338,7 +4400,7 @@
       </c>
       <c r="E18" s="33">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="F18" s="33">
         <f t="shared" si="1"/>
@@ -4355,7 +4417,7 @@
       </c>
       <c r="B19" s="33">
         <f>Quiz!V19</f>
-        <v>1.1499999999999999</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="C19" s="41">
         <f>Exams!B19</f>
@@ -4367,7 +4429,7 @@
       </c>
       <c r="E19" s="33">
         <f t="shared" si="0"/>
-        <v>1.1499999999999999</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="F19" s="33">
         <f t="shared" si="1"/>
@@ -4384,7 +4446,7 @@
       </c>
       <c r="B20" s="33">
         <f>Quiz!V20</f>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="C20" s="41">
         <f>Exams!B20</f>
@@ -4396,7 +4458,7 @@
       </c>
       <c r="E20" s="33">
         <f t="shared" si="0"/>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F20" s="33">
         <f t="shared" ref="F20:F25" si="3">0.5*INT(E20/0.5)+INT( ((E20-INT(E20/0.5)*0.5)/0.25))*0.5</f>
@@ -4413,7 +4475,7 @@
       </c>
       <c r="B21" s="33">
         <f>Quiz!V21</f>
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="C21" s="41">
         <f>Exams!B21</f>
@@ -4425,11 +4487,11 @@
       </c>
       <c r="E21" s="33">
         <f t="shared" si="0"/>
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="F21" s="33">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G21" s="47">
         <f t="shared" si="4"/>
@@ -4442,7 +4504,7 @@
       </c>
       <c r="B22" s="33">
         <f>Quiz!V22</f>
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="C22" s="41">
         <f>Exams!B22</f>
@@ -4454,7 +4516,7 @@
       </c>
       <c r="E22" s="33">
         <f t="shared" si="0"/>
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="F22" s="33">
         <f t="shared" si="3"/>
@@ -4471,7 +4533,7 @@
       </c>
       <c r="B23" s="33">
         <f>Quiz!V23</f>
-        <v>1.45</v>
+        <v>1.56</v>
       </c>
       <c r="C23" s="41">
         <f>Exams!B23</f>
@@ -4483,7 +4545,7 @@
       </c>
       <c r="E23" s="33">
         <f t="shared" si="0"/>
-        <v>1.45</v>
+        <v>1.56</v>
       </c>
       <c r="F23" s="33">
         <f t="shared" si="3"/>
@@ -4500,7 +4562,7 @@
       </c>
       <c r="B24" s="33">
         <f>Quiz!V24</f>
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="C24" s="41">
         <f>Exams!B24</f>
@@ -4512,7 +4574,7 @@
       </c>
       <c r="E24" s="33">
         <f t="shared" si="0"/>
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="F24" s="33">
         <f t="shared" si="3"/>
@@ -4529,7 +4591,7 @@
       </c>
       <c r="B25" s="33">
         <f>Quiz!V25</f>
-        <v>1.1499999999999999</v>
+        <v>0.92</v>
       </c>
       <c r="C25" s="41">
         <f>Exams!B25</f>
@@ -4541,7 +4603,7 @@
       </c>
       <c r="E25" s="33">
         <f t="shared" si="0"/>
-        <v>1.1499999999999999</v>
+        <v>0.92</v>
       </c>
       <c r="F25" s="33">
         <f t="shared" si="3"/>
@@ -4558,7 +4620,7 @@
       </c>
       <c r="B26" s="33">
         <f>Quiz!V26</f>
-        <v>0.6</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="C26" s="41">
         <f>Exams!B26</f>
@@ -4570,7 +4632,7 @@
       </c>
       <c r="E26" s="33">
         <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="F26" s="33">
         <f t="shared" ref="F26:F40" si="5">0.5*INT(E26/0.5)+INT( ((E26-INT(E26/0.5)*0.5)/0.25))*0.5</f>
@@ -4587,7 +4649,7 @@
       </c>
       <c r="B27" s="33">
         <f>Quiz!V27</f>
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="C27" s="41">
         <f>Exams!B27</f>
@@ -4599,7 +4661,7 @@
       </c>
       <c r="E27" s="33">
         <f t="shared" si="0"/>
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="F27" s="33">
         <f t="shared" si="5"/>
@@ -4616,7 +4678,7 @@
       </c>
       <c r="B28" s="33">
         <f>Quiz!V28</f>
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="C28" s="41">
         <f>Exams!B28</f>
@@ -4628,7 +4690,7 @@
       </c>
       <c r="E28" s="33">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="F28" s="33">
         <f t="shared" si="5"/>
@@ -4645,7 +4707,7 @@
       </c>
       <c r="B29" s="33">
         <f>Quiz!V29</f>
-        <v>0.95</v>
+        <v>0.84</v>
       </c>
       <c r="C29" s="41">
         <f>Exams!B29</f>
@@ -4657,7 +4719,7 @@
       </c>
       <c r="E29" s="33">
         <f t="shared" si="0"/>
-        <v>0.95</v>
+        <v>0.84</v>
       </c>
       <c r="F29" s="33">
         <f t="shared" si="5"/>
@@ -4674,7 +4736,7 @@
       </c>
       <c r="B30" s="33">
         <f>Quiz!V30</f>
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
       <c r="C30" s="41">
         <f>Exams!B30</f>
@@ -4686,7 +4748,7 @@
       </c>
       <c r="E30" s="33">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
       <c r="F30" s="33">
         <f t="shared" si="5"/>
@@ -4703,7 +4765,7 @@
       </c>
       <c r="B31" s="33">
         <f>Quiz!V31</f>
-        <v>0.65</v>
+        <v>0.52</v>
       </c>
       <c r="C31" s="41">
         <f>Exams!B31</f>
@@ -4715,7 +4777,7 @@
       </c>
       <c r="E31" s="33">
         <f t="shared" si="0"/>
-        <v>0.65</v>
+        <v>0.52</v>
       </c>
       <c r="F31" s="33">
         <f t="shared" si="5"/>
@@ -4732,7 +4794,7 @@
       </c>
       <c r="B32" s="33">
         <f>Quiz!V32</f>
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="C32" s="41">
         <f>Exams!B32</f>
@@ -4744,7 +4806,7 @@
       </c>
       <c r="E32" s="33">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="F32" s="33">
         <f t="shared" si="5"/>
@@ -4790,7 +4852,7 @@
       </c>
       <c r="B34" s="33">
         <f>Quiz!V34</f>
-        <v>0.1</v>
+        <v>0.32</v>
       </c>
       <c r="C34" s="41">
         <f>Exams!B34</f>
@@ -4802,11 +4864,11 @@
       </c>
       <c r="E34" s="33">
         <f t="shared" si="0"/>
-        <v>0.1</v>
+        <v>0.32</v>
       </c>
       <c r="F34" s="33">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G34" s="47">
         <f t="shared" ref="G34:G40" si="7">IF(F34&gt;4.75,1,0)</f>
@@ -4819,7 +4881,7 @@
       </c>
       <c r="B35" s="33">
         <f>Quiz!V35</f>
-        <v>0.57499999999999996</v>
+        <v>0.7</v>
       </c>
       <c r="C35" s="41">
         <f>Exams!B35</f>
@@ -4831,7 +4893,7 @@
       </c>
       <c r="E35" s="33">
         <f t="shared" si="0"/>
-        <v>0.57499999999999996</v>
+        <v>0.7</v>
       </c>
       <c r="F35" s="33">
         <f t="shared" si="5"/>
@@ -4848,7 +4910,7 @@
       </c>
       <c r="B36" s="33">
         <f>Quiz!V36</f>
-        <v>0.3</v>
+        <v>0.48</v>
       </c>
       <c r="C36" s="41">
         <f>Exams!B36</f>
@@ -4860,7 +4922,7 @@
       </c>
       <c r="E36" s="33">
         <f t="shared" si="0"/>
-        <v>0.3</v>
+        <v>0.48</v>
       </c>
       <c r="F36" s="33">
         <f t="shared" si="5"/>
@@ -4877,7 +4939,7 @@
       </c>
       <c r="B37" s="33">
         <f>Quiz!V37</f>
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="C37" s="41">
         <f>Exams!B37</f>
@@ -4889,7 +4951,7 @@
       </c>
       <c r="E37" s="33">
         <f t="shared" si="0"/>
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="F37" s="33">
         <f t="shared" si="5"/>
@@ -4906,7 +4968,7 @@
       </c>
       <c r="B38" s="33">
         <f>Quiz!V38</f>
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="C38" s="41">
         <f>Exams!B38</f>
@@ -4918,11 +4980,11 @@
       </c>
       <c r="E38" s="33">
         <f t="shared" si="0"/>
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="F38" s="33">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G38" s="47">
         <f t="shared" si="7"/>
@@ -4935,7 +4997,7 @@
       </c>
       <c r="B39" s="33">
         <f>Quiz!V39</f>
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="C39" s="41">
         <f>Exams!B39</f>
@@ -4947,7 +5009,7 @@
       </c>
       <c r="E39" s="33">
         <f t="shared" si="0"/>
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="F39" s="33">
         <f t="shared" ref="F39" si="8">0.5*INT(E39/0.5)+INT( ((E39-INT(E39/0.5)*0.5)/0.25))*0.5</f>
@@ -4964,7 +5026,7 @@
       </c>
       <c r="B40" s="33">
         <f>Quiz!V40</f>
-        <v>1.7</v>
+        <v>1.36</v>
       </c>
       <c r="C40" s="41">
         <f>Exams!B40</f>
@@ -4976,7 +5038,7 @@
       </c>
       <c r="E40" s="33">
         <f t="shared" si="0"/>
-        <v>1.7</v>
+        <v>1.36</v>
       </c>
       <c r="F40" s="33">
         <f t="shared" si="5"/>
@@ -5029,7 +5091,7 @@
       </c>
       <c r="B43" s="29">
         <f t="shared" ref="B43:G43" si="10">AVERAGE(B$2:B$40)</f>
-        <v>0.89679487179487161</v>
+        <v>0.86461538461538445</v>
       </c>
       <c r="C43" s="29">
         <f t="shared" si="10"/>
@@ -5041,7 +5103,7 @@
       </c>
       <c r="E43" s="29">
         <f t="shared" si="10"/>
-        <v>0.89679487179487161</v>
+        <v>0.86461538461538445</v>
       </c>
       <c r="F43" s="29">
         <f t="shared" si="10"/>
@@ -5058,7 +5120,7 @@
       </c>
       <c r="B44" s="29">
         <f t="shared" ref="B44:G44" si="11">STDEV(B$2:B$40)</f>
-        <v>0.42874432201163926</v>
+        <v>0.39055861581670981</v>
       </c>
       <c r="C44" s="29">
         <f t="shared" si="11"/>
@@ -5070,11 +5132,11 @@
       </c>
       <c r="E44" s="29">
         <f t="shared" si="11"/>
-        <v>0.42874432201163926</v>
+        <v>0.39055861581670981</v>
       </c>
       <c r="F44" s="29">
         <f t="shared" si="11"/>
-        <v>0.44691173006191792</v>
+        <v>0.41643043235725746</v>
       </c>
       <c r="G44" s="29">
         <f t="shared" si="11"/>
@@ -5087,7 +5149,7 @@
       </c>
       <c r="B45" s="29">
         <f t="shared" ref="B45:G45" si="12">MEDIAN(B$2:B$40)</f>
-        <v>0.9</v>
+        <v>0.84</v>
       </c>
       <c r="C45" s="29">
         <f t="shared" si="12"/>
@@ -5099,7 +5161,7 @@
       </c>
       <c r="E45" s="29">
         <f t="shared" si="12"/>
-        <v>0.9</v>
+        <v>0.84</v>
       </c>
       <c r="F45" s="29">
         <f t="shared" si="12"/>

--- a/phy112/Grades/grades_report_2026.xlsx
+++ b/phy112/Grades/grades_report_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ptohos/Documents/MyCourses/FYS112/2026/Grades/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7217C8FA-18CD-B94D-9639-D2AC54D3C4D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CF5C68F-C9FD-4D44-A6C2-2E5F0C1991AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1640" yWindow="1200" windowWidth="32920" windowHeight="19260" tabRatio="334" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="540" yWindow="7020" windowWidth="32920" windowHeight="19260" tabRatio="334" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Quiz" sheetId="1" r:id="rId1"/>
@@ -1008,7 +1008,9 @@
       <c r="G2" s="18">
         <v>12</v>
       </c>
-      <c r="H2" s="18"/>
+      <c r="H2" s="18">
+        <v>12</v>
+      </c>
       <c r="I2" s="18"/>
       <c r="J2" s="18"/>
       <c r="K2" s="18"/>
@@ -1024,7 +1026,7 @@
       <c r="U2" s="18"/>
       <c r="V2" s="33">
         <f t="shared" ref="V2:V39" si="0">$V$42 * ( (SUM(B2:U2))/((SUM($B$46:$U$46))*$B$42) )</f>
-        <v>0.8</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="W2"/>
     </row>
@@ -1048,7 +1050,9 @@
       <c r="G3" s="18">
         <v>4</v>
       </c>
-      <c r="H3" s="18"/>
+      <c r="H3" s="18">
+        <v>8</v>
+      </c>
       <c r="I3" s="18"/>
       <c r="J3" s="18"/>
       <c r="K3" s="18"/>
@@ -1064,7 +1068,7 @@
       <c r="U3" s="18"/>
       <c r="V3" s="33">
         <f t="shared" si="0"/>
-        <v>0.72</v>
+        <v>0.73333333333333328</v>
       </c>
       <c r="W3"/>
     </row>
@@ -1088,7 +1092,9 @@
       <c r="G4" s="18">
         <v>15</v>
       </c>
-      <c r="H4" s="18"/>
+      <c r="H4" s="18">
+        <v>12</v>
+      </c>
       <c r="I4" s="18"/>
       <c r="J4" s="18"/>
       <c r="K4" s="18"/>
@@ -1104,7 +1110,7 @@
       <c r="U4" s="18"/>
       <c r="V4" s="33">
         <f t="shared" si="0"/>
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="W4"/>
     </row>
@@ -1126,7 +1132,9 @@
         <v>4</v>
       </c>
       <c r="G5" s="18"/>
-      <c r="H5" s="18"/>
+      <c r="H5" s="18">
+        <v>4</v>
+      </c>
       <c r="I5" s="18"/>
       <c r="J5" s="18"/>
       <c r="K5" s="18"/>
@@ -1142,7 +1150,7 @@
       <c r="U5" s="18"/>
       <c r="V5" s="33">
         <f t="shared" si="0"/>
-        <v>0.32</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="W5"/>
     </row>
@@ -1166,7 +1174,9 @@
       <c r="G6" s="18">
         <v>4</v>
       </c>
-      <c r="H6" s="18"/>
+      <c r="H6" s="18">
+        <v>4</v>
+      </c>
       <c r="I6" s="18"/>
       <c r="J6" s="18"/>
       <c r="K6" s="18"/>
@@ -1182,7 +1192,7 @@
       <c r="U6" s="18"/>
       <c r="V6" s="33">
         <f t="shared" si="0"/>
-        <v>1.1200000000000001</v>
+        <v>1</v>
       </c>
       <c r="W6"/>
     </row>
@@ -1206,7 +1216,9 @@
       <c r="G7" s="18">
         <v>20</v>
       </c>
-      <c r="H7" s="18"/>
+      <c r="H7" s="18">
+        <v>20</v>
+      </c>
       <c r="I7" s="18"/>
       <c r="J7" s="18"/>
       <c r="K7" s="18"/>
@@ -1222,7 +1234,7 @@
       <c r="U7" s="18"/>
       <c r="V7" s="33">
         <f t="shared" si="0"/>
-        <v>1.44</v>
+        <v>1.5333333333333334</v>
       </c>
       <c r="W7"/>
     </row>
@@ -1246,7 +1258,9 @@
       <c r="G8" s="18">
         <v>4</v>
       </c>
-      <c r="H8" s="18"/>
+      <c r="H8" s="18">
+        <v>4</v>
+      </c>
       <c r="I8" s="18"/>
       <c r="J8" s="18"/>
       <c r="K8" s="18"/>
@@ -1262,7 +1276,7 @@
       <c r="U8" s="18"/>
       <c r="V8" s="33">
         <f t="shared" si="0"/>
-        <v>0.84</v>
+        <v>0.76666666666666672</v>
       </c>
       <c r="W8"/>
     </row>
@@ -1282,7 +1296,9 @@
       <c r="G9" s="18">
         <v>4</v>
       </c>
-      <c r="H9" s="18"/>
+      <c r="H9" s="18">
+        <v>12</v>
+      </c>
       <c r="I9" s="18"/>
       <c r="J9" s="18"/>
       <c r="K9" s="18"/>
@@ -1298,7 +1314,7 @@
       <c r="U9" s="18"/>
       <c r="V9" s="33">
         <f t="shared" si="0"/>
-        <v>0.72</v>
+        <v>0.8</v>
       </c>
       <c r="W9"/>
     </row>
@@ -1336,7 +1352,7 @@
       <c r="U10" s="18"/>
       <c r="V10" s="33">
         <f t="shared" si="0"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="W10"/>
     </row>
@@ -1358,7 +1374,9 @@
         <v>4</v>
       </c>
       <c r="G11" s="18"/>
-      <c r="H11" s="18"/>
+      <c r="H11" s="18">
+        <v>20</v>
+      </c>
       <c r="I11" s="18"/>
       <c r="J11" s="18"/>
       <c r="K11" s="18"/>
@@ -1374,7 +1392,7 @@
       <c r="U11" s="18"/>
       <c r="V11" s="33">
         <f t="shared" si="0"/>
-        <v>0.32</v>
+        <v>0.6</v>
       </c>
       <c r="W11"/>
     </row>
@@ -1398,7 +1416,9 @@
       <c r="G12" s="18">
         <v>12</v>
       </c>
-      <c r="H12" s="18"/>
+      <c r="H12" s="18">
+        <v>4</v>
+      </c>
       <c r="I12" s="18"/>
       <c r="J12" s="18"/>
       <c r="K12" s="18"/>
@@ -1414,7 +1434,7 @@
       <c r="U12" s="18"/>
       <c r="V12" s="33">
         <f t="shared" si="0"/>
-        <v>1.04</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="W12"/>
     </row>
@@ -1438,7 +1458,9 @@
       <c r="G13" s="18">
         <v>4</v>
       </c>
-      <c r="H13" s="18"/>
+      <c r="H13" s="18">
+        <v>12</v>
+      </c>
       <c r="I13" s="18"/>
       <c r="J13" s="18"/>
       <c r="K13" s="18"/>
@@ -1454,7 +1476,7 @@
       <c r="U13" s="18"/>
       <c r="V13" s="33">
         <f t="shared" si="0"/>
-        <v>0.76</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="W13"/>
     </row>
@@ -1478,7 +1500,9 @@
       <c r="G14" s="18">
         <v>12</v>
       </c>
-      <c r="H14" s="18"/>
+      <c r="H14" s="18">
+        <v>12</v>
+      </c>
       <c r="I14" s="18"/>
       <c r="J14" s="18"/>
       <c r="K14" s="18"/>
@@ -1494,7 +1518,7 @@
       <c r="U14" s="18"/>
       <c r="V14" s="33">
         <f t="shared" si="0"/>
-        <v>1.08</v>
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:23" ht="29" customHeight="1" x14ac:dyDescent="0.15">
@@ -1517,7 +1541,9 @@
       <c r="G15" s="18">
         <v>12</v>
       </c>
-      <c r="H15" s="18"/>
+      <c r="H15" s="18">
+        <v>20</v>
+      </c>
       <c r="I15" s="18"/>
       <c r="J15" s="18"/>
       <c r="K15" s="18"/>
@@ -1533,7 +1559,7 @@
       <c r="U15" s="18"/>
       <c r="V15" s="33">
         <f t="shared" si="0"/>
-        <v>1.8</v>
+        <v>1.8333333333333333</v>
       </c>
       <c r="W15"/>
     </row>
@@ -1557,7 +1583,9 @@
       <c r="G16" s="18">
         <v>4</v>
       </c>
-      <c r="H16" s="18"/>
+      <c r="H16" s="18">
+        <v>20</v>
+      </c>
       <c r="I16" s="18"/>
       <c r="J16" s="18"/>
       <c r="K16" s="18"/>
@@ -1573,7 +1601,7 @@
       <c r="U16" s="18"/>
       <c r="V16" s="33">
         <f t="shared" si="0"/>
-        <v>0.76</v>
+        <v>0.96666666666666667</v>
       </c>
       <c r="W16"/>
     </row>
@@ -1643,7 +1671,7 @@
       <c r="U18" s="18"/>
       <c r="V18" s="33">
         <f t="shared" si="0"/>
-        <v>0.88</v>
+        <v>0.73333333333333328</v>
       </c>
       <c r="W18"/>
     </row>
@@ -1667,7 +1695,9 @@
       <c r="G19" s="18">
         <v>12</v>
       </c>
-      <c r="H19" s="18"/>
+      <c r="H19" s="18">
+        <v>4</v>
+      </c>
       <c r="I19" s="18"/>
       <c r="J19" s="18"/>
       <c r="K19" s="18"/>
@@ -1683,7 +1713,7 @@
       <c r="U19" s="18"/>
       <c r="V19" s="33">
         <f t="shared" si="0"/>
-        <v>1.1599999999999999</v>
+        <v>1.0333333333333334</v>
       </c>
       <c r="W19"/>
     </row>
@@ -1705,7 +1735,9 @@
       <c r="G20" s="18">
         <v>4</v>
       </c>
-      <c r="H20" s="18"/>
+      <c r="H20" s="18">
+        <v>16</v>
+      </c>
       <c r="I20" s="18"/>
       <c r="J20" s="18"/>
       <c r="K20" s="18"/>
@@ -1721,7 +1753,7 @@
       <c r="U20" s="18"/>
       <c r="V20" s="33">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="W20"/>
     </row>
@@ -1745,7 +1777,9 @@
       <c r="G21" s="18">
         <v>20</v>
       </c>
-      <c r="H21" s="18"/>
+      <c r="H21" s="18">
+        <v>20</v>
+      </c>
       <c r="I21" s="18"/>
       <c r="J21" s="18"/>
       <c r="K21" s="18"/>
@@ -1761,7 +1795,7 @@
       <c r="U21" s="18"/>
       <c r="V21" s="33">
         <f t="shared" si="0"/>
-        <v>1.36</v>
+        <v>1.4666666666666666</v>
       </c>
       <c r="W21"/>
     </row>
@@ -1801,7 +1835,7 @@
       <c r="U22" s="18"/>
       <c r="V22" s="33">
         <f t="shared" si="0"/>
-        <v>1.08</v>
+        <v>0.9</v>
       </c>
       <c r="W22"/>
     </row>
@@ -1825,7 +1859,9 @@
       <c r="G23" s="18">
         <v>20</v>
       </c>
-      <c r="H23" s="18"/>
+      <c r="H23" s="18">
+        <v>20</v>
+      </c>
       <c r="I23" s="18"/>
       <c r="J23" s="18"/>
       <c r="K23" s="18"/>
@@ -1841,7 +1877,7 @@
       <c r="U23" s="18"/>
       <c r="V23" s="33">
         <f t="shared" si="0"/>
-        <v>1.56</v>
+        <v>1.6333333333333333</v>
       </c>
       <c r="W23"/>
     </row>
@@ -1863,7 +1899,9 @@
       <c r="G24" s="18">
         <v>4</v>
       </c>
-      <c r="H24" s="18"/>
+      <c r="H24" s="18">
+        <v>16</v>
+      </c>
       <c r="I24" s="18"/>
       <c r="J24" s="18"/>
       <c r="K24" s="18"/>
@@ -1879,7 +1917,7 @@
       <c r="U24" s="18"/>
       <c r="V24" s="33">
         <f t="shared" si="0"/>
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="W24"/>
     </row>
@@ -1899,7 +1937,9 @@
       </c>
       <c r="F25" s="18"/>
       <c r="G25" s="18"/>
-      <c r="H25" s="18"/>
+      <c r="H25" s="18">
+        <v>20</v>
+      </c>
       <c r="I25" s="18"/>
       <c r="J25" s="18"/>
       <c r="K25" s="18"/>
@@ -1915,7 +1955,7 @@
       <c r="U25" s="18"/>
       <c r="V25" s="33">
         <f t="shared" si="0"/>
-        <v>0.92</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="W25"/>
     </row>
@@ -1939,7 +1979,9 @@
       <c r="G26" s="18">
         <v>4</v>
       </c>
-      <c r="H26" s="18"/>
+      <c r="H26" s="18">
+        <v>8</v>
+      </c>
       <c r="I26" s="18"/>
       <c r="J26" s="18"/>
       <c r="K26" s="18"/>
@@ -1955,7 +1997,7 @@
       <c r="U26" s="18"/>
       <c r="V26" s="33">
         <f t="shared" si="0"/>
-        <v>0.56000000000000005</v>
+        <v>0.6</v>
       </c>
       <c r="W26"/>
     </row>
@@ -1993,7 +2035,7 @@
       <c r="U27" s="18"/>
       <c r="V27" s="33">
         <f t="shared" si="0"/>
-        <v>0.64</v>
+        <v>0.53333333333333333</v>
       </c>
       <c r="W27"/>
     </row>
@@ -2033,7 +2075,7 @@
       <c r="U28" s="18"/>
       <c r="V28" s="33">
         <f t="shared" si="0"/>
-        <v>0.88</v>
+        <v>0.73333333333333328</v>
       </c>
       <c r="W28"/>
     </row>
@@ -2057,7 +2099,9 @@
       <c r="G29" s="18">
         <v>4</v>
       </c>
-      <c r="H29" s="18"/>
+      <c r="H29" s="18">
+        <v>12</v>
+      </c>
       <c r="I29" s="18"/>
       <c r="J29" s="18"/>
       <c r="K29" s="18"/>
@@ -2073,7 +2117,7 @@
       <c r="U29" s="18"/>
       <c r="V29" s="33">
         <f t="shared" si="0"/>
-        <v>0.84</v>
+        <v>0.9</v>
       </c>
       <c r="W29"/>
     </row>
@@ -2097,7 +2141,9 @@
       <c r="G30" s="18">
         <v>12</v>
       </c>
-      <c r="H30" s="18"/>
+      <c r="H30" s="18">
+        <v>12</v>
+      </c>
       <c r="I30" s="18"/>
       <c r="J30" s="18"/>
       <c r="K30" s="18"/>
@@ -2113,7 +2159,7 @@
       <c r="U30" s="18"/>
       <c r="V30" s="33">
         <f t="shared" si="0"/>
-        <v>0.88</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="W30"/>
     </row>
@@ -2135,7 +2181,9 @@
         <v>4</v>
       </c>
       <c r="G31" s="18"/>
-      <c r="H31" s="18"/>
+      <c r="H31" s="18">
+        <v>4</v>
+      </c>
       <c r="I31" s="18"/>
       <c r="J31" s="18"/>
       <c r="K31" s="18"/>
@@ -2151,7 +2199,7 @@
       <c r="U31" s="18"/>
       <c r="V31" s="33">
         <f t="shared" si="0"/>
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="W31"/>
     </row>
@@ -2175,7 +2223,9 @@
       <c r="G32" s="18">
         <v>12</v>
       </c>
-      <c r="H32" s="18"/>
+      <c r="H32" s="18">
+        <v>4</v>
+      </c>
       <c r="I32" s="18"/>
       <c r="J32" s="18"/>
       <c r="K32" s="18"/>
@@ -2191,7 +2241,7 @@
       <c r="U32" s="18"/>
       <c r="V32" s="33">
         <f t="shared" si="0"/>
-        <v>1.04</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="W32"/>
     </row>
@@ -2239,7 +2289,9 @@
       <c r="G34" s="18">
         <v>12</v>
       </c>
-      <c r="H34" s="18"/>
+      <c r="H34" s="18">
+        <v>4</v>
+      </c>
       <c r="I34" s="18"/>
       <c r="J34" s="18"/>
       <c r="K34" s="18"/>
@@ -2255,7 +2307,7 @@
       <c r="U34" s="18"/>
       <c r="V34" s="33">
         <f t="shared" si="0"/>
-        <v>0.32</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="W34"/>
     </row>
@@ -2279,7 +2331,9 @@
       <c r="G35" s="18">
         <v>12</v>
       </c>
-      <c r="H35" s="18"/>
+      <c r="H35" s="18">
+        <v>16</v>
+      </c>
       <c r="I35" s="18"/>
       <c r="J35" s="18"/>
       <c r="K35" s="18"/>
@@ -2295,7 +2349,7 @@
       <c r="U35" s="18"/>
       <c r="V35" s="33">
         <f t="shared" si="0"/>
-        <v>0.7</v>
+        <v>0.85</v>
       </c>
       <c r="W35"/>
     </row>
@@ -2313,7 +2367,9 @@
       <c r="G36" s="18">
         <v>12</v>
       </c>
-      <c r="H36" s="18"/>
+      <c r="H36" s="18">
+        <v>12</v>
+      </c>
       <c r="I36" s="18"/>
       <c r="J36" s="18"/>
       <c r="K36" s="18"/>
@@ -2329,7 +2385,7 @@
       <c r="U36" s="18"/>
       <c r="V36" s="33">
         <f t="shared" si="0"/>
-        <v>0.48</v>
+        <v>0.6</v>
       </c>
       <c r="W36"/>
     </row>
@@ -2353,7 +2409,9 @@
       <c r="G37" s="18">
         <v>12</v>
       </c>
-      <c r="H37" s="18"/>
+      <c r="H37" s="18">
+        <v>16</v>
+      </c>
       <c r="I37" s="18"/>
       <c r="J37" s="18"/>
       <c r="K37" s="18"/>
@@ -2369,7 +2427,7 @@
       <c r="U37" s="18"/>
       <c r="V37" s="33">
         <f t="shared" si="0"/>
-        <v>1.08</v>
+        <v>1.1666666666666667</v>
       </c>
       <c r="W37"/>
     </row>
@@ -2407,7 +2465,7 @@
       <c r="U38" s="18"/>
       <c r="V38" s="33">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="W38"/>
     </row>
@@ -2431,7 +2489,9 @@
       <c r="G39" s="18">
         <v>4</v>
       </c>
-      <c r="H39" s="18"/>
+      <c r="H39" s="18">
+        <v>12</v>
+      </c>
       <c r="I39" s="18"/>
       <c r="J39" s="18"/>
       <c r="K39" s="18"/>
@@ -2447,7 +2507,7 @@
       <c r="U39" s="18"/>
       <c r="V39" s="33">
         <f t="shared" si="0"/>
-        <v>1.28</v>
+        <v>1.2666666666666666</v>
       </c>
       <c r="W39"/>
     </row>
@@ -2469,7 +2529,9 @@
         <v>12</v>
       </c>
       <c r="G40" s="18"/>
-      <c r="H40" s="18"/>
+      <c r="H40" s="18">
+        <v>4</v>
+      </c>
       <c r="I40" s="18"/>
       <c r="J40" s="18"/>
       <c r="K40" s="18"/>
@@ -2485,7 +2547,7 @@
       <c r="U40" s="18"/>
       <c r="V40" s="33">
         <f t="shared" ref="V40" si="1">$V$42 * ( (SUM(B40:U40))/((SUM($B$46:$U$46))*$B$42) )</f>
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="W40"/>
     </row>
@@ -2611,9 +2673,9 @@
         <f t="shared" si="2"/>
         <v>9.258064516129032</v>
       </c>
-      <c r="H43" s="29" t="e">
+      <c r="H43" s="29">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+        <v>12</v>
       </c>
       <c r="I43" s="29" t="e">
         <f t="shared" si="2"/>
@@ -2669,7 +2731,7 @@
       </c>
       <c r="V43" s="29">
         <f t="shared" si="2"/>
-        <v>0.85157894736842088</v>
+        <v>0.86754385964912306</v>
       </c>
       <c r="W43"/>
     </row>
@@ -2701,9 +2763,9 @@
         <f t="shared" si="3"/>
         <v>5.3663627777448664</v>
       </c>
-      <c r="H44" s="29" t="e">
+      <c r="H44" s="29">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
+        <v>6.0343842356489263</v>
       </c>
       <c r="I44" s="29" t="e">
         <f t="shared" si="3"/>
@@ -2759,7 +2821,7 @@
       </c>
       <c r="V44" s="29">
         <f t="shared" si="3"/>
-        <v>0.3871065662047885</v>
+        <v>0.38400738560412356</v>
       </c>
       <c r="W44"/>
     </row>
@@ -2791,9 +2853,9 @@
         <f t="shared" si="4"/>
         <v>12</v>
       </c>
-      <c r="H45" s="29" t="e">
+      <c r="H45" s="29">
         <f t="shared" si="4"/>
-        <v>#NUM!</v>
+        <v>12</v>
       </c>
       <c r="I45" s="29" t="e">
         <f t="shared" si="4"/>
@@ -2849,7 +2911,7 @@
       </c>
       <c r="V45" s="29">
         <f t="shared" si="4"/>
-        <v>0.84</v>
+        <v>0.8833333333333333</v>
       </c>
       <c r="W45"/>
     </row>
@@ -2883,7 +2945,7 @@
       </c>
       <c r="H46" s="32">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I46" s="32">
         <f t="shared" si="5"/>
@@ -3923,7 +3985,7 @@
       </c>
       <c r="B2" s="33">
         <f>Quiz!V2</f>
-        <v>0.8</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="C2" s="41">
         <f>Exams!B2</f>
@@ -3935,7 +3997,7 @@
       </c>
       <c r="E2" s="33">
         <f>$B2+($C2/$C$42)*3.5+($D2/$D$42)*4.5</f>
-        <v>0.8</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="F2" s="33">
         <f>0.5*INT(E2/0.5)+INT( ((E2-INT(E2/0.5)*0.5)/0.25))*0.5</f>
@@ -3953,7 +4015,7 @@
       </c>
       <c r="B3" s="33">
         <f>Quiz!V3</f>
-        <v>0.72</v>
+        <v>0.73333333333333328</v>
       </c>
       <c r="C3" s="41">
         <f>Exams!B3</f>
@@ -3965,7 +4027,7 @@
       </c>
       <c r="E3" s="33">
         <f t="shared" ref="E3:E40" si="0">$B3+($C3/$C$42)*3.5+($D3/$D$42)*4.5</f>
-        <v>0.72</v>
+        <v>0.73333333333333328</v>
       </c>
       <c r="F3" s="33">
         <f t="shared" ref="F3:F19" si="1">0.5*INT(E3/0.5)+INT( ((E3-INT(E3/0.5)*0.5)/0.25))*0.5</f>
@@ -3982,7 +4044,7 @@
       </c>
       <c r="B4" s="33">
         <f>Quiz!V4</f>
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="C4" s="41">
         <f>Exams!B4</f>
@@ -3994,7 +4056,7 @@
       </c>
       <c r="E4" s="33">
         <f t="shared" si="0"/>
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="F4" s="33">
         <f t="shared" si="1"/>
@@ -4011,7 +4073,7 @@
       </c>
       <c r="B5" s="33">
         <f>Quiz!V5</f>
-        <v>0.32</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="C5" s="41">
         <f>Exams!B5</f>
@@ -4023,7 +4085,7 @@
       </c>
       <c r="E5" s="33">
         <f t="shared" si="0"/>
-        <v>0.32</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="F5" s="33">
         <f t="shared" si="1"/>
@@ -4040,7 +4102,7 @@
       </c>
       <c r="B6" s="33">
         <f>Quiz!V6</f>
-        <v>1.1200000000000001</v>
+        <v>1</v>
       </c>
       <c r="C6" s="41">
         <f>Exams!B6</f>
@@ -4052,7 +4114,7 @@
       </c>
       <c r="E6" s="33">
         <f t="shared" si="0"/>
-        <v>1.1200000000000001</v>
+        <v>1</v>
       </c>
       <c r="F6" s="33">
         <f t="shared" si="1"/>
@@ -4069,7 +4131,7 @@
       </c>
       <c r="B7" s="33">
         <f>Quiz!V7</f>
-        <v>1.44</v>
+        <v>1.5333333333333334</v>
       </c>
       <c r="C7" s="41">
         <f>Exams!B7</f>
@@ -4081,7 +4143,7 @@
       </c>
       <c r="E7" s="33">
         <f t="shared" si="0"/>
-        <v>1.44</v>
+        <v>1.5333333333333334</v>
       </c>
       <c r="F7" s="33">
         <f t="shared" si="1"/>
@@ -4098,7 +4160,7 @@
       </c>
       <c r="B8" s="33">
         <f>Quiz!V8</f>
-        <v>0.84</v>
+        <v>0.76666666666666672</v>
       </c>
       <c r="C8" s="41">
         <f>Exams!B8</f>
@@ -4110,7 +4172,7 @@
       </c>
       <c r="E8" s="33">
         <f t="shared" si="0"/>
-        <v>0.84</v>
+        <v>0.76666666666666672</v>
       </c>
       <c r="F8" s="33">
         <f t="shared" si="1"/>
@@ -4127,7 +4189,7 @@
       </c>
       <c r="B9" s="33">
         <f>Quiz!V9</f>
-        <v>0.72</v>
+        <v>0.8</v>
       </c>
       <c r="C9" s="41">
         <f>Exams!B9</f>
@@ -4139,11 +4201,11 @@
       </c>
       <c r="E9" s="33">
         <f t="shared" si="0"/>
-        <v>0.72</v>
+        <v>0.8</v>
       </c>
       <c r="F9" s="33">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G9" s="47">
         <f t="shared" si="2"/>
@@ -4156,7 +4218,7 @@
       </c>
       <c r="B10" s="33">
         <f>Quiz!V10</f>
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="C10" s="41">
         <f>Exams!B10</f>
@@ -4168,7 +4230,7 @@
       </c>
       <c r="E10" s="33">
         <f t="shared" si="0"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="F10" s="33">
         <f t="shared" si="1"/>
@@ -4185,7 +4247,7 @@
       </c>
       <c r="B11" s="33">
         <f>Quiz!V11</f>
-        <v>0.32</v>
+        <v>0.6</v>
       </c>
       <c r="C11" s="41">
         <f>Exams!B11</f>
@@ -4197,7 +4259,7 @@
       </c>
       <c r="E11" s="33">
         <f t="shared" si="0"/>
-        <v>0.32</v>
+        <v>0.6</v>
       </c>
       <c r="F11" s="33">
         <f t="shared" si="1"/>
@@ -4214,7 +4276,7 @@
       </c>
       <c r="B12" s="33">
         <f>Quiz!V12</f>
-        <v>1.04</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="C12" s="41">
         <f>Exams!B12</f>
@@ -4226,7 +4288,7 @@
       </c>
       <c r="E12" s="33">
         <f t="shared" si="0"/>
-        <v>1.04</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="F12" s="33">
         <f t="shared" si="1"/>
@@ -4243,7 +4305,7 @@
       </c>
       <c r="B13" s="33">
         <f>Quiz!V13</f>
-        <v>0.76</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="C13" s="41">
         <f>Exams!B13</f>
@@ -4255,7 +4317,7 @@
       </c>
       <c r="E13" s="33">
         <f t="shared" si="0"/>
-        <v>0.76</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="F13" s="33">
         <f t="shared" si="1"/>
@@ -4272,7 +4334,7 @@
       </c>
       <c r="B14" s="33">
         <f>Quiz!V14</f>
-        <v>1.08</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="C14" s="41">
         <f>Exams!B14</f>
@@ -4284,7 +4346,7 @@
       </c>
       <c r="E14" s="33">
         <f t="shared" si="0"/>
-        <v>1.08</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="F14" s="33">
         <f t="shared" si="1"/>
@@ -4301,7 +4363,7 @@
       </c>
       <c r="B15" s="33">
         <f>Quiz!V15</f>
-        <v>1.8</v>
+        <v>1.8333333333333333</v>
       </c>
       <c r="C15" s="41">
         <f>Exams!B15</f>
@@ -4313,7 +4375,7 @@
       </c>
       <c r="E15" s="33">
         <f t="shared" si="0"/>
-        <v>1.8</v>
+        <v>1.8333333333333333</v>
       </c>
       <c r="F15" s="33">
         <f t="shared" si="1"/>
@@ -4330,7 +4392,7 @@
       </c>
       <c r="B16" s="33">
         <f>Quiz!V16</f>
-        <v>0.76</v>
+        <v>0.96666666666666667</v>
       </c>
       <c r="C16" s="41">
         <f>Exams!B16</f>
@@ -4342,7 +4404,7 @@
       </c>
       <c r="E16" s="33">
         <f t="shared" si="0"/>
-        <v>0.76</v>
+        <v>0.96666666666666667</v>
       </c>
       <c r="F16" s="33">
         <f t="shared" si="1"/>
@@ -4388,7 +4450,7 @@
       </c>
       <c r="B18" s="33">
         <f>Quiz!V18</f>
-        <v>0.88</v>
+        <v>0.73333333333333328</v>
       </c>
       <c r="C18" s="41">
         <f>Exams!B18</f>
@@ -4400,11 +4462,11 @@
       </c>
       <c r="E18" s="33">
         <f t="shared" si="0"/>
-        <v>0.88</v>
+        <v>0.73333333333333328</v>
       </c>
       <c r="F18" s="33">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G18" s="47">
         <f t="shared" si="2"/>
@@ -4417,7 +4479,7 @@
       </c>
       <c r="B19" s="33">
         <f>Quiz!V19</f>
-        <v>1.1599999999999999</v>
+        <v>1.0333333333333334</v>
       </c>
       <c r="C19" s="41">
         <f>Exams!B19</f>
@@ -4429,7 +4491,7 @@
       </c>
       <c r="E19" s="33">
         <f t="shared" si="0"/>
-        <v>1.1599999999999999</v>
+        <v>1.0333333333333334</v>
       </c>
       <c r="F19" s="33">
         <f t="shared" si="1"/>
@@ -4446,7 +4508,7 @@
       </c>
       <c r="B20" s="33">
         <f>Quiz!V20</f>
-        <v>0.8</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="C20" s="41">
         <f>Exams!B20</f>
@@ -4458,7 +4520,7 @@
       </c>
       <c r="E20" s="33">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="F20" s="33">
         <f t="shared" ref="F20:F25" si="3">0.5*INT(E20/0.5)+INT( ((E20-INT(E20/0.5)*0.5)/0.25))*0.5</f>
@@ -4475,7 +4537,7 @@
       </c>
       <c r="B21" s="33">
         <f>Quiz!V21</f>
-        <v>1.36</v>
+        <v>1.4666666666666666</v>
       </c>
       <c r="C21" s="41">
         <f>Exams!B21</f>
@@ -4487,7 +4549,7 @@
       </c>
       <c r="E21" s="33">
         <f t="shared" si="0"/>
-        <v>1.36</v>
+        <v>1.4666666666666666</v>
       </c>
       <c r="F21" s="33">
         <f t="shared" si="3"/>
@@ -4504,7 +4566,7 @@
       </c>
       <c r="B22" s="33">
         <f>Quiz!V22</f>
-        <v>1.08</v>
+        <v>0.9</v>
       </c>
       <c r="C22" s="41">
         <f>Exams!B22</f>
@@ -4516,7 +4578,7 @@
       </c>
       <c r="E22" s="33">
         <f t="shared" si="0"/>
-        <v>1.08</v>
+        <v>0.9</v>
       </c>
       <c r="F22" s="33">
         <f t="shared" si="3"/>
@@ -4533,7 +4595,7 @@
       </c>
       <c r="B23" s="33">
         <f>Quiz!V23</f>
-        <v>1.56</v>
+        <v>1.6333333333333333</v>
       </c>
       <c r="C23" s="41">
         <f>Exams!B23</f>
@@ -4545,7 +4607,7 @@
       </c>
       <c r="E23" s="33">
         <f t="shared" si="0"/>
-        <v>1.56</v>
+        <v>1.6333333333333333</v>
       </c>
       <c r="F23" s="33">
         <f t="shared" si="3"/>
@@ -4562,7 +4624,7 @@
       </c>
       <c r="B24" s="33">
         <f>Quiz!V24</f>
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="C24" s="41">
         <f>Exams!B24</f>
@@ -4574,11 +4636,11 @@
       </c>
       <c r="E24" s="33">
         <f t="shared" si="0"/>
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="F24" s="33">
         <f t="shared" si="3"/>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G24" s="47">
         <f t="shared" si="4"/>
@@ -4591,7 +4653,7 @@
       </c>
       <c r="B25" s="33">
         <f>Quiz!V25</f>
-        <v>0.92</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="C25" s="41">
         <f>Exams!B25</f>
@@ -4603,7 +4665,7 @@
       </c>
       <c r="E25" s="33">
         <f t="shared" si="0"/>
-        <v>0.92</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="F25" s="33">
         <f t="shared" si="3"/>
@@ -4620,7 +4682,7 @@
       </c>
       <c r="B26" s="33">
         <f>Quiz!V26</f>
-        <v>0.56000000000000005</v>
+        <v>0.6</v>
       </c>
       <c r="C26" s="41">
         <f>Exams!B26</f>
@@ -4632,7 +4694,7 @@
       </c>
       <c r="E26" s="33">
         <f t="shared" si="0"/>
-        <v>0.56000000000000005</v>
+        <v>0.6</v>
       </c>
       <c r="F26" s="33">
         <f t="shared" ref="F26:F40" si="5">0.5*INT(E26/0.5)+INT( ((E26-INT(E26/0.5)*0.5)/0.25))*0.5</f>
@@ -4649,7 +4711,7 @@
       </c>
       <c r="B27" s="33">
         <f>Quiz!V27</f>
-        <v>0.64</v>
+        <v>0.53333333333333333</v>
       </c>
       <c r="C27" s="41">
         <f>Exams!B27</f>
@@ -4661,7 +4723,7 @@
       </c>
       <c r="E27" s="33">
         <f t="shared" si="0"/>
-        <v>0.64</v>
+        <v>0.53333333333333333</v>
       </c>
       <c r="F27" s="33">
         <f t="shared" si="5"/>
@@ -4678,7 +4740,7 @@
       </c>
       <c r="B28" s="33">
         <f>Quiz!V28</f>
-        <v>0.88</v>
+        <v>0.73333333333333328</v>
       </c>
       <c r="C28" s="41">
         <f>Exams!B28</f>
@@ -4690,11 +4752,11 @@
       </c>
       <c r="E28" s="33">
         <f t="shared" si="0"/>
-        <v>0.88</v>
+        <v>0.73333333333333328</v>
       </c>
       <c r="F28" s="33">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G28" s="47">
         <f t="shared" si="6"/>
@@ -4707,7 +4769,7 @@
       </c>
       <c r="B29" s="33">
         <f>Quiz!V29</f>
-        <v>0.84</v>
+        <v>0.9</v>
       </c>
       <c r="C29" s="41">
         <f>Exams!B29</f>
@@ -4719,7 +4781,7 @@
       </c>
       <c r="E29" s="33">
         <f t="shared" si="0"/>
-        <v>0.84</v>
+        <v>0.9</v>
       </c>
       <c r="F29" s="33">
         <f t="shared" si="5"/>
@@ -4736,7 +4798,7 @@
       </c>
       <c r="B30" s="33">
         <f>Quiz!V30</f>
-        <v>0.88</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="C30" s="41">
         <f>Exams!B30</f>
@@ -4748,7 +4810,7 @@
       </c>
       <c r="E30" s="33">
         <f t="shared" si="0"/>
-        <v>0.88</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="F30" s="33">
         <f t="shared" si="5"/>
@@ -4765,7 +4827,7 @@
       </c>
       <c r="B31" s="33">
         <f>Quiz!V31</f>
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="C31" s="41">
         <f>Exams!B31</f>
@@ -4777,7 +4839,7 @@
       </c>
       <c r="E31" s="33">
         <f t="shared" si="0"/>
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="F31" s="33">
         <f t="shared" si="5"/>
@@ -4794,7 +4856,7 @@
       </c>
       <c r="B32" s="33">
         <f>Quiz!V32</f>
-        <v>1.04</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="C32" s="41">
         <f>Exams!B32</f>
@@ -4806,7 +4868,7 @@
       </c>
       <c r="E32" s="33">
         <f t="shared" si="0"/>
-        <v>1.04</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="F32" s="33">
         <f t="shared" si="5"/>
@@ -4852,7 +4914,7 @@
       </c>
       <c r="B34" s="33">
         <f>Quiz!V34</f>
-        <v>0.32</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="C34" s="41">
         <f>Exams!B34</f>
@@ -4864,7 +4926,7 @@
       </c>
       <c r="E34" s="33">
         <f t="shared" si="0"/>
-        <v>0.32</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="F34" s="33">
         <f t="shared" si="5"/>
@@ -4881,7 +4943,7 @@
       </c>
       <c r="B35" s="33">
         <f>Quiz!V35</f>
-        <v>0.7</v>
+        <v>0.85</v>
       </c>
       <c r="C35" s="41">
         <f>Exams!B35</f>
@@ -4893,11 +4955,11 @@
       </c>
       <c r="E35" s="33">
         <f t="shared" si="0"/>
-        <v>0.7</v>
+        <v>0.85</v>
       </c>
       <c r="F35" s="33">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G35" s="47">
         <f t="shared" si="7"/>
@@ -4910,7 +4972,7 @@
       </c>
       <c r="B36" s="33">
         <f>Quiz!V36</f>
-        <v>0.48</v>
+        <v>0.6</v>
       </c>
       <c r="C36" s="41">
         <f>Exams!B36</f>
@@ -4922,7 +4984,7 @@
       </c>
       <c r="E36" s="33">
         <f t="shared" si="0"/>
-        <v>0.48</v>
+        <v>0.6</v>
       </c>
       <c r="F36" s="33">
         <f t="shared" si="5"/>
@@ -4939,7 +5001,7 @@
       </c>
       <c r="B37" s="33">
         <f>Quiz!V37</f>
-        <v>1.08</v>
+        <v>1.1666666666666667</v>
       </c>
       <c r="C37" s="41">
         <f>Exams!B37</f>
@@ -4951,7 +5013,7 @@
       </c>
       <c r="E37" s="33">
         <f t="shared" si="0"/>
-        <v>1.08</v>
+        <v>1.1666666666666667</v>
       </c>
       <c r="F37" s="33">
         <f t="shared" si="5"/>
@@ -4968,7 +5030,7 @@
       </c>
       <c r="B38" s="33">
         <f>Quiz!V38</f>
-        <v>0.8</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="C38" s="41">
         <f>Exams!B38</f>
@@ -4980,11 +5042,11 @@
       </c>
       <c r="E38" s="33">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="F38" s="33">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G38" s="47">
         <f t="shared" si="7"/>
@@ -4997,7 +5059,7 @@
       </c>
       <c r="B39" s="33">
         <f>Quiz!V39</f>
-        <v>1.28</v>
+        <v>1.2666666666666666</v>
       </c>
       <c r="C39" s="41">
         <f>Exams!B39</f>
@@ -5009,7 +5071,7 @@
       </c>
       <c r="E39" s="33">
         <f t="shared" si="0"/>
-        <v>1.28</v>
+        <v>1.2666666666666666</v>
       </c>
       <c r="F39" s="33">
         <f t="shared" ref="F39" si="8">0.5*INT(E39/0.5)+INT( ((E39-INT(E39/0.5)*0.5)/0.25))*0.5</f>
@@ -5026,7 +5088,7 @@
       </c>
       <c r="B40" s="33">
         <f>Quiz!V40</f>
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="C40" s="41">
         <f>Exams!B40</f>
@@ -5038,11 +5100,11 @@
       </c>
       <c r="E40" s="33">
         <f t="shared" si="0"/>
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="F40" s="33">
         <f t="shared" si="5"/>
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G40" s="47">
         <f t="shared" si="7"/>
@@ -5091,7 +5153,7 @@
       </c>
       <c r="B43" s="29">
         <f t="shared" ref="B43:G43" si="10">AVERAGE(B$2:B$40)</f>
-        <v>0.86461538461538445</v>
+        <v>0.8760683760683764</v>
       </c>
       <c r="C43" s="29">
         <f t="shared" si="10"/>
@@ -5103,11 +5165,11 @@
       </c>
       <c r="E43" s="29">
         <f t="shared" si="10"/>
-        <v>0.86461538461538445</v>
+        <v>0.8760683760683764</v>
       </c>
       <c r="F43" s="29">
         <f t="shared" si="10"/>
-        <v>0.89743589743589747</v>
+        <v>0.88461538461538458</v>
       </c>
       <c r="G43" s="29">
         <f t="shared" si="10"/>
@@ -5120,7 +5182,7 @@
       </c>
       <c r="B44" s="29">
         <f t="shared" ref="B44:G44" si="11">STDEV(B$2:B$40)</f>
-        <v>0.39055861581670981</v>
+        <v>0.38264229994160714</v>
       </c>
       <c r="C44" s="29">
         <f t="shared" si="11"/>
@@ -5132,11 +5194,11 @@
       </c>
       <c r="E44" s="29">
         <f t="shared" si="11"/>
-        <v>0.39055861581670981</v>
+        <v>0.38264229994160714</v>
       </c>
       <c r="F44" s="29">
         <f t="shared" si="11"/>
-        <v>0.41643043235725746</v>
+        <v>0.40492914359926274</v>
       </c>
       <c r="G44" s="29">
         <f t="shared" si="11"/>
@@ -5149,7 +5211,7 @@
       </c>
       <c r="B45" s="29">
         <f t="shared" ref="B45:G45" si="12">MEDIAN(B$2:B$40)</f>
-        <v>0.84</v>
+        <v>0.9</v>
       </c>
       <c r="C45" s="29">
         <f t="shared" si="12"/>
@@ -5161,7 +5223,7 @@
       </c>
       <c r="E45" s="29">
         <f t="shared" si="12"/>
-        <v>0.84</v>
+        <v>0.9</v>
       </c>
       <c r="F45" s="29">
         <f t="shared" si="12"/>

--- a/phy112/Grades/grades_report_2026.xlsx
+++ b/phy112/Grades/grades_report_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ptohos/Documents/MyCourses/FYS112/2026/Grades/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CF5C68F-C9FD-4D44-A6C2-2E5F0C1991AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09A4A60D-239E-5E4D-A0FC-1B6818B57E35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="540" yWindow="7020" windowWidth="32920" windowHeight="19260" tabRatio="334" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="540" yWindow="3080" windowWidth="32920" windowHeight="19260" tabRatio="334" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Quiz" sheetId="1" r:id="rId1"/>
@@ -1011,7 +1011,9 @@
       <c r="H2" s="18">
         <v>12</v>
       </c>
-      <c r="I2" s="18"/>
+      <c r="I2" s="18">
+        <v>4</v>
+      </c>
       <c r="J2" s="18"/>
       <c r="K2" s="18"/>
       <c r="L2" s="18"/>
@@ -1026,7 +1028,7 @@
       <c r="U2" s="18"/>
       <c r="V2" s="33">
         <f t="shared" ref="V2:V39" si="0">$V$42 * ( (SUM(B2:U2))/((SUM($B$46:$U$46))*$B$42) )</f>
-        <v>0.8666666666666667</v>
+        <v>0.8</v>
       </c>
       <c r="W2"/>
     </row>
@@ -1068,7 +1070,7 @@
       <c r="U3" s="18"/>
       <c r="V3" s="33">
         <f t="shared" si="0"/>
-        <v>0.73333333333333328</v>
+        <v>0.62857142857142856</v>
       </c>
       <c r="W3"/>
     </row>
@@ -1095,7 +1097,9 @@
       <c r="H4" s="18">
         <v>12</v>
       </c>
-      <c r="I4" s="18"/>
+      <c r="I4" s="18">
+        <v>4</v>
+      </c>
       <c r="J4" s="18"/>
       <c r="K4" s="18"/>
       <c r="L4" s="18"/>
@@ -1110,7 +1114,7 @@
       <c r="U4" s="18"/>
       <c r="V4" s="33">
         <f t="shared" si="0"/>
-        <v>1.05</v>
+        <v>0.95714285714285718</v>
       </c>
       <c r="W4"/>
     </row>
@@ -1135,7 +1139,9 @@
       <c r="H5" s="18">
         <v>4</v>
       </c>
-      <c r="I5" s="18"/>
+      <c r="I5" s="18">
+        <v>4</v>
+      </c>
       <c r="J5" s="18"/>
       <c r="K5" s="18"/>
       <c r="L5" s="18"/>
@@ -1150,7 +1156,7 @@
       <c r="U5" s="18"/>
       <c r="V5" s="33">
         <f t="shared" si="0"/>
-        <v>0.33333333333333331</v>
+        <v>0.34285714285714286</v>
       </c>
       <c r="W5"/>
     </row>
@@ -1177,7 +1183,9 @@
       <c r="H6" s="18">
         <v>4</v>
       </c>
-      <c r="I6" s="18"/>
+      <c r="I6" s="18">
+        <v>4</v>
+      </c>
       <c r="J6" s="18"/>
       <c r="K6" s="18"/>
       <c r="L6" s="18"/>
@@ -1192,7 +1200,7 @@
       <c r="U6" s="18"/>
       <c r="V6" s="33">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.91428571428571426</v>
       </c>
       <c r="W6"/>
     </row>
@@ -1219,7 +1227,9 @@
       <c r="H7" s="18">
         <v>20</v>
       </c>
-      <c r="I7" s="18"/>
+      <c r="I7" s="18">
+        <v>4</v>
+      </c>
       <c r="J7" s="18"/>
       <c r="K7" s="18"/>
       <c r="L7" s="18"/>
@@ -1234,7 +1244,7 @@
       <c r="U7" s="18"/>
       <c r="V7" s="33">
         <f t="shared" si="0"/>
-        <v>1.5333333333333334</v>
+        <v>1.3714285714285714</v>
       </c>
       <c r="W7"/>
     </row>
@@ -1261,7 +1271,9 @@
       <c r="H8" s="18">
         <v>4</v>
       </c>
-      <c r="I8" s="18"/>
+      <c r="I8" s="18">
+        <v>4</v>
+      </c>
       <c r="J8" s="18"/>
       <c r="K8" s="18"/>
       <c r="L8" s="18"/>
@@ -1276,7 +1288,7 @@
       <c r="U8" s="18"/>
       <c r="V8" s="33">
         <f t="shared" si="0"/>
-        <v>0.76666666666666672</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="W8"/>
     </row>
@@ -1299,7 +1311,9 @@
       <c r="H9" s="18">
         <v>12</v>
       </c>
-      <c r="I9" s="18"/>
+      <c r="I9" s="18">
+        <v>4</v>
+      </c>
       <c r="J9" s="18"/>
       <c r="K9" s="18"/>
       <c r="L9" s="18"/>
@@ -1314,7 +1328,7 @@
       <c r="U9" s="18"/>
       <c r="V9" s="33">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.74285714285714288</v>
       </c>
       <c r="W9"/>
     </row>
@@ -1337,7 +1351,9 @@
       </c>
       <c r="G10" s="18"/>
       <c r="H10" s="18"/>
-      <c r="I10" s="18"/>
+      <c r="I10" s="18">
+        <v>4</v>
+      </c>
       <c r="J10" s="18"/>
       <c r="K10" s="18"/>
       <c r="L10" s="18"/>
@@ -1352,7 +1368,7 @@
       <c r="U10" s="18"/>
       <c r="V10" s="33">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.91428571428571426</v>
       </c>
       <c r="W10"/>
     </row>
@@ -1377,7 +1393,9 @@
       <c r="H11" s="18">
         <v>20</v>
       </c>
-      <c r="I11" s="18"/>
+      <c r="I11" s="18">
+        <v>12</v>
+      </c>
       <c r="J11" s="18"/>
       <c r="K11" s="18"/>
       <c r="L11" s="18"/>
@@ -1392,7 +1410,7 @@
       <c r="U11" s="18"/>
       <c r="V11" s="33">
         <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.68571428571428572</v>
       </c>
       <c r="W11"/>
     </row>
@@ -1419,7 +1437,9 @@
       <c r="H12" s="18">
         <v>4</v>
       </c>
-      <c r="I12" s="18"/>
+      <c r="I12" s="18">
+        <v>12</v>
+      </c>
       <c r="J12" s="18"/>
       <c r="K12" s="18"/>
       <c r="L12" s="18"/>
@@ -1434,7 +1454,7 @@
       <c r="U12" s="18"/>
       <c r="V12" s="33">
         <f t="shared" si="0"/>
-        <v>0.93333333333333335</v>
+        <v>0.97142857142857142</v>
       </c>
       <c r="W12"/>
     </row>
@@ -1461,7 +1481,9 @@
       <c r="H13" s="18">
         <v>12</v>
       </c>
-      <c r="I13" s="18"/>
+      <c r="I13" s="18">
+        <v>12</v>
+      </c>
       <c r="J13" s="18"/>
       <c r="K13" s="18"/>
       <c r="L13" s="18"/>
@@ -1476,7 +1498,7 @@
       <c r="U13" s="18"/>
       <c r="V13" s="33">
         <f t="shared" si="0"/>
-        <v>0.83333333333333337</v>
+        <v>0.88571428571428568</v>
       </c>
       <c r="W13"/>
     </row>
@@ -1503,7 +1525,9 @@
       <c r="H14" s="18">
         <v>12</v>
       </c>
-      <c r="I14" s="18"/>
+      <c r="I14" s="18">
+        <v>12</v>
+      </c>
       <c r="J14" s="18"/>
       <c r="K14" s="18"/>
       <c r="L14" s="18"/>
@@ -1518,7 +1542,7 @@
       <c r="U14" s="18"/>
       <c r="V14" s="33">
         <f t="shared" si="0"/>
-        <v>1.1000000000000001</v>
+        <v>1.1142857142857143</v>
       </c>
     </row>
     <row r="15" spans="1:23" ht="29" customHeight="1" x14ac:dyDescent="0.15">
@@ -1544,7 +1568,9 @@
       <c r="H15" s="18">
         <v>20</v>
       </c>
-      <c r="I15" s="18"/>
+      <c r="I15" s="18">
+        <v>20</v>
+      </c>
       <c r="J15" s="18"/>
       <c r="K15" s="18"/>
       <c r="L15" s="18"/>
@@ -1559,7 +1585,7 @@
       <c r="U15" s="18"/>
       <c r="V15" s="33">
         <f t="shared" si="0"/>
-        <v>1.8333333333333333</v>
+        <v>1.8571428571428572</v>
       </c>
       <c r="W15"/>
     </row>
@@ -1586,7 +1612,9 @@
       <c r="H16" s="18">
         <v>20</v>
       </c>
-      <c r="I16" s="18"/>
+      <c r="I16" s="18">
+        <v>4</v>
+      </c>
       <c r="J16" s="18"/>
       <c r="K16" s="18"/>
       <c r="L16" s="18"/>
@@ -1601,7 +1629,7 @@
       <c r="U16" s="18"/>
       <c r="V16" s="33">
         <f t="shared" si="0"/>
-        <v>0.96666666666666667</v>
+        <v>0.88571428571428568</v>
       </c>
       <c r="W16"/>
     </row>
@@ -1671,7 +1699,7 @@
       <c r="U18" s="18"/>
       <c r="V18" s="33">
         <f t="shared" si="0"/>
-        <v>0.73333333333333328</v>
+        <v>0.62857142857142856</v>
       </c>
       <c r="W18"/>
     </row>
@@ -1698,7 +1726,9 @@
       <c r="H19" s="18">
         <v>4</v>
       </c>
-      <c r="I19" s="18"/>
+      <c r="I19" s="18">
+        <v>4</v>
+      </c>
       <c r="J19" s="18"/>
       <c r="K19" s="18"/>
       <c r="L19" s="18"/>
@@ -1713,7 +1743,7 @@
       <c r="U19" s="18"/>
       <c r="V19" s="33">
         <f t="shared" si="0"/>
-        <v>1.0333333333333334</v>
+        <v>0.94285714285714284</v>
       </c>
       <c r="W19"/>
     </row>
@@ -1738,7 +1768,9 @@
       <c r="H20" s="18">
         <v>16</v>
       </c>
-      <c r="I20" s="18"/>
+      <c r="I20" s="18">
+        <v>12</v>
+      </c>
       <c r="J20" s="18"/>
       <c r="K20" s="18"/>
       <c r="L20" s="18"/>
@@ -1753,7 +1785,7 @@
       <c r="U20" s="18"/>
       <c r="V20" s="33">
         <f t="shared" si="0"/>
-        <v>0.93333333333333335</v>
+        <v>0.97142857142857142</v>
       </c>
       <c r="W20"/>
     </row>
@@ -1780,7 +1812,9 @@
       <c r="H21" s="18">
         <v>20</v>
       </c>
-      <c r="I21" s="18"/>
+      <c r="I21" s="18">
+        <v>12</v>
+      </c>
       <c r="J21" s="18"/>
       <c r="K21" s="18"/>
       <c r="L21" s="18"/>
@@ -1795,7 +1829,7 @@
       <c r="U21" s="18"/>
       <c r="V21" s="33">
         <f t="shared" si="0"/>
-        <v>1.4666666666666666</v>
+        <v>1.4285714285714286</v>
       </c>
       <c r="W21"/>
     </row>
@@ -1820,7 +1854,9 @@
         <v>12</v>
       </c>
       <c r="H22" s="18"/>
-      <c r="I22" s="18"/>
+      <c r="I22" s="18">
+        <v>12</v>
+      </c>
       <c r="J22" s="18"/>
       <c r="K22" s="18"/>
       <c r="L22" s="18"/>
@@ -1835,7 +1871,7 @@
       <c r="U22" s="18"/>
       <c r="V22" s="33">
         <f t="shared" si="0"/>
-        <v>0.9</v>
+        <v>0.94285714285714284</v>
       </c>
       <c r="W22"/>
     </row>
@@ -1862,7 +1898,9 @@
       <c r="H23" s="18">
         <v>20</v>
       </c>
-      <c r="I23" s="18"/>
+      <c r="I23" s="18">
+        <v>16</v>
+      </c>
       <c r="J23" s="18"/>
       <c r="K23" s="18"/>
       <c r="L23" s="18"/>
@@ -1877,7 +1915,7 @@
       <c r="U23" s="18"/>
       <c r="V23" s="33">
         <f t="shared" si="0"/>
-        <v>1.6333333333333333</v>
+        <v>1.6285714285714286</v>
       </c>
       <c r="W23"/>
     </row>
@@ -1902,7 +1940,9 @@
       <c r="H24" s="18">
         <v>16</v>
       </c>
-      <c r="I24" s="18"/>
+      <c r="I24" s="18">
+        <v>12</v>
+      </c>
       <c r="J24" s="18"/>
       <c r="K24" s="18"/>
       <c r="L24" s="18"/>
@@ -1917,7 +1957,7 @@
       <c r="U24" s="18"/>
       <c r="V24" s="33">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="W24"/>
     </row>
@@ -1940,7 +1980,9 @@
       <c r="H25" s="18">
         <v>20</v>
       </c>
-      <c r="I25" s="18"/>
+      <c r="I25" s="18">
+        <v>12</v>
+      </c>
       <c r="J25" s="18"/>
       <c r="K25" s="18"/>
       <c r="L25" s="18"/>
@@ -1955,7 +1997,7 @@
       <c r="U25" s="18"/>
       <c r="V25" s="33">
         <f t="shared" si="0"/>
-        <v>1.1000000000000001</v>
+        <v>1.1142857142857143</v>
       </c>
       <c r="W25"/>
     </row>
@@ -1982,7 +2024,9 @@
       <c r="H26" s="18">
         <v>8</v>
       </c>
-      <c r="I26" s="18"/>
+      <c r="I26" s="18">
+        <v>4</v>
+      </c>
       <c r="J26" s="18"/>
       <c r="K26" s="18"/>
       <c r="L26" s="18"/>
@@ -1997,7 +2041,7 @@
       <c r="U26" s="18"/>
       <c r="V26" s="33">
         <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="W26"/>
     </row>
@@ -2020,7 +2064,9 @@
         <v>4</v>
       </c>
       <c r="H27" s="18"/>
-      <c r="I27" s="18"/>
+      <c r="I27" s="18">
+        <v>12</v>
+      </c>
       <c r="J27" s="18"/>
       <c r="K27" s="18"/>
       <c r="L27" s="18"/>
@@ -2035,7 +2081,7 @@
       <c r="U27" s="18"/>
       <c r="V27" s="33">
         <f t="shared" si="0"/>
-        <v>0.53333333333333333</v>
+        <v>0.62857142857142856</v>
       </c>
       <c r="W27"/>
     </row>
@@ -2060,7 +2106,9 @@
         <v>4</v>
       </c>
       <c r="H28" s="18"/>
-      <c r="I28" s="18"/>
+      <c r="I28" s="18">
+        <v>12</v>
+      </c>
       <c r="J28" s="18"/>
       <c r="K28" s="18"/>
       <c r="L28" s="18"/>
@@ -2075,7 +2123,7 @@
       <c r="U28" s="18"/>
       <c r="V28" s="33">
         <f t="shared" si="0"/>
-        <v>0.73333333333333328</v>
+        <v>0.8</v>
       </c>
       <c r="W28"/>
     </row>
@@ -2102,7 +2150,9 @@
       <c r="H29" s="18">
         <v>12</v>
       </c>
-      <c r="I29" s="18"/>
+      <c r="I29" s="18">
+        <v>4</v>
+      </c>
       <c r="J29" s="18"/>
       <c r="K29" s="18"/>
       <c r="L29" s="18"/>
@@ -2117,7 +2167,7 @@
       <c r="U29" s="18"/>
       <c r="V29" s="33">
         <f t="shared" si="0"/>
-        <v>0.9</v>
+        <v>0.82857142857142863</v>
       </c>
       <c r="W29"/>
     </row>
@@ -2144,7 +2194,9 @@
       <c r="H30" s="18">
         <v>12</v>
       </c>
-      <c r="I30" s="18"/>
+      <c r="I30" s="18">
+        <v>12</v>
+      </c>
       <c r="J30" s="18"/>
       <c r="K30" s="18"/>
       <c r="L30" s="18"/>
@@ -2159,7 +2211,7 @@
       <c r="U30" s="18"/>
       <c r="V30" s="33">
         <f t="shared" si="0"/>
-        <v>0.93333333333333335</v>
+        <v>0.97142857142857142</v>
       </c>
       <c r="W30"/>
     </row>
@@ -2184,7 +2236,9 @@
       <c r="H31" s="18">
         <v>4</v>
       </c>
-      <c r="I31" s="18"/>
+      <c r="I31" s="18">
+        <v>4</v>
+      </c>
       <c r="J31" s="18"/>
       <c r="K31" s="18"/>
       <c r="L31" s="18"/>
@@ -2199,7 +2253,7 @@
       <c r="U31" s="18"/>
       <c r="V31" s="33">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0.48571428571428571</v>
       </c>
       <c r="W31"/>
     </row>
@@ -2226,7 +2280,9 @@
       <c r="H32" s="18">
         <v>4</v>
       </c>
-      <c r="I32" s="18"/>
+      <c r="I32" s="18">
+        <v>15</v>
+      </c>
       <c r="J32" s="18"/>
       <c r="K32" s="18"/>
       <c r="L32" s="18"/>
@@ -2241,7 +2297,7 @@
       <c r="U32" s="18"/>
       <c r="V32" s="33">
         <f t="shared" si="0"/>
-        <v>0.93333333333333335</v>
+        <v>1.0142857142857142</v>
       </c>
       <c r="W32"/>
     </row>
@@ -2292,7 +2348,9 @@
       <c r="H34" s="18">
         <v>4</v>
       </c>
-      <c r="I34" s="18"/>
+      <c r="I34" s="18">
+        <v>4</v>
+      </c>
       <c r="J34" s="18"/>
       <c r="K34" s="18"/>
       <c r="L34" s="18"/>
@@ -2307,7 +2365,7 @@
       <c r="U34" s="18"/>
       <c r="V34" s="33">
         <f t="shared" si="0"/>
-        <v>0.33333333333333331</v>
+        <v>0.34285714285714286</v>
       </c>
       <c r="W34"/>
     </row>
@@ -2334,7 +2392,9 @@
       <c r="H35" s="18">
         <v>16</v>
       </c>
-      <c r="I35" s="18"/>
+      <c r="I35" s="18">
+        <v>12</v>
+      </c>
       <c r="J35" s="18"/>
       <c r="K35" s="18"/>
       <c r="L35" s="18"/>
@@ -2349,7 +2409,7 @@
       <c r="U35" s="18"/>
       <c r="V35" s="33">
         <f t="shared" si="0"/>
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="W35"/>
     </row>
@@ -2370,7 +2430,9 @@
       <c r="H36" s="18">
         <v>12</v>
       </c>
-      <c r="I36" s="18"/>
+      <c r="I36" s="18">
+        <v>4</v>
+      </c>
       <c r="J36" s="18"/>
       <c r="K36" s="18"/>
       <c r="L36" s="18"/>
@@ -2385,7 +2447,7 @@
       <c r="U36" s="18"/>
       <c r="V36" s="33">
         <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="W36"/>
     </row>
@@ -2412,7 +2474,9 @@
       <c r="H37" s="18">
         <v>16</v>
       </c>
-      <c r="I37" s="18"/>
+      <c r="I37" s="18">
+        <v>12</v>
+      </c>
       <c r="J37" s="18"/>
       <c r="K37" s="18"/>
       <c r="L37" s="18"/>
@@ -2427,7 +2491,7 @@
       <c r="U37" s="18"/>
       <c r="V37" s="33">
         <f t="shared" si="0"/>
-        <v>1.1666666666666667</v>
+        <v>1.1714285714285715</v>
       </c>
       <c r="W37"/>
     </row>
@@ -2465,7 +2529,7 @@
       <c r="U38" s="18"/>
       <c r="V38" s="33">
         <f t="shared" si="0"/>
-        <v>0.66666666666666663</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="W38"/>
     </row>
@@ -2492,7 +2556,9 @@
       <c r="H39" s="18">
         <v>12</v>
       </c>
-      <c r="I39" s="18"/>
+      <c r="I39" s="18">
+        <v>4</v>
+      </c>
       <c r="J39" s="18"/>
       <c r="K39" s="18"/>
       <c r="L39" s="18"/>
@@ -2507,7 +2573,7 @@
       <c r="U39" s="18"/>
       <c r="V39" s="33">
         <f t="shared" si="0"/>
-        <v>1.2666666666666666</v>
+        <v>1.1428571428571428</v>
       </c>
       <c r="W39"/>
     </row>
@@ -2532,7 +2598,9 @@
       <c r="H40" s="18">
         <v>4</v>
       </c>
-      <c r="I40" s="18"/>
+      <c r="I40" s="18">
+        <v>4</v>
+      </c>
       <c r="J40" s="18"/>
       <c r="K40" s="18"/>
       <c r="L40" s="18"/>
@@ -2547,7 +2615,7 @@
       <c r="U40" s="18"/>
       <c r="V40" s="33">
         <f t="shared" ref="V40" si="1">$V$42 * ( (SUM(B40:U40))/((SUM($B$46:$U$46))*$B$42) )</f>
-        <v>1.2</v>
+        <v>1.0857142857142856</v>
       </c>
       <c r="W40"/>
     </row>
@@ -2677,9 +2745,9 @@
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="I43" s="29" t="e">
+      <c r="I43" s="29">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+        <v>8.5757575757575761</v>
       </c>
       <c r="J43" s="29" t="e">
         <f t="shared" si="2"/>
@@ -2731,7 +2799,7 @@
       </c>
       <c r="V43" s="29">
         <f t="shared" si="2"/>
-        <v>0.86754385964912306</v>
+        <v>0.85000000000000009</v>
       </c>
       <c r="W43"/>
     </row>
@@ -2767,9 +2835,9 @@
         <f t="shared" si="3"/>
         <v>6.0343842356489263</v>
       </c>
-      <c r="I44" s="29" t="e">
+      <c r="I44" s="29">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
+        <v>4.7633385287415733</v>
       </c>
       <c r="J44" s="29" t="e">
         <f t="shared" si="3"/>
@@ -2821,7 +2889,7 @@
       </c>
       <c r="V44" s="29">
         <f t="shared" si="3"/>
-        <v>0.38400738560412356</v>
+        <v>0.37501608717102453</v>
       </c>
       <c r="W44"/>
     </row>
@@ -2857,9 +2925,9 @@
         <f t="shared" si="4"/>
         <v>12</v>
       </c>
-      <c r="I45" s="29" t="e">
+      <c r="I45" s="29">
         <f t="shared" si="4"/>
-        <v>#NUM!</v>
+        <v>12</v>
       </c>
       <c r="J45" s="29" t="e">
         <f t="shared" si="4"/>
@@ -2911,7 +2979,7 @@
       </c>
       <c r="V45" s="29">
         <f t="shared" si="4"/>
-        <v>0.8833333333333333</v>
+        <v>0.88571428571428568</v>
       </c>
       <c r="W45"/>
     </row>
@@ -2949,7 +3017,7 @@
       </c>
       <c r="I46" s="32">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J46" s="32">
         <f t="shared" si="5"/>
@@ -3985,7 +4053,7 @@
       </c>
       <c r="B2" s="33">
         <f>Quiz!V2</f>
-        <v>0.8666666666666667</v>
+        <v>0.8</v>
       </c>
       <c r="C2" s="41">
         <f>Exams!B2</f>
@@ -3997,7 +4065,7 @@
       </c>
       <c r="E2" s="33">
         <f>$B2+($C2/$C$42)*3.5+($D2/$D$42)*4.5</f>
-        <v>0.8666666666666667</v>
+        <v>0.8</v>
       </c>
       <c r="F2" s="33">
         <f>0.5*INT(E2/0.5)+INT( ((E2-INT(E2/0.5)*0.5)/0.25))*0.5</f>
@@ -4015,7 +4083,7 @@
       </c>
       <c r="B3" s="33">
         <f>Quiz!V3</f>
-        <v>0.73333333333333328</v>
+        <v>0.62857142857142856</v>
       </c>
       <c r="C3" s="41">
         <f>Exams!B3</f>
@@ -4027,7 +4095,7 @@
       </c>
       <c r="E3" s="33">
         <f t="shared" ref="E3:E40" si="0">$B3+($C3/$C$42)*3.5+($D3/$D$42)*4.5</f>
-        <v>0.73333333333333328</v>
+        <v>0.62857142857142856</v>
       </c>
       <c r="F3" s="33">
         <f t="shared" ref="F3:F19" si="1">0.5*INT(E3/0.5)+INT( ((E3-INT(E3/0.5)*0.5)/0.25))*0.5</f>
@@ -4044,7 +4112,7 @@
       </c>
       <c r="B4" s="33">
         <f>Quiz!V4</f>
-        <v>1.05</v>
+        <v>0.95714285714285718</v>
       </c>
       <c r="C4" s="41">
         <f>Exams!B4</f>
@@ -4056,7 +4124,7 @@
       </c>
       <c r="E4" s="33">
         <f t="shared" si="0"/>
-        <v>1.05</v>
+        <v>0.95714285714285718</v>
       </c>
       <c r="F4" s="33">
         <f t="shared" si="1"/>
@@ -4073,7 +4141,7 @@
       </c>
       <c r="B5" s="33">
         <f>Quiz!V5</f>
-        <v>0.33333333333333331</v>
+        <v>0.34285714285714286</v>
       </c>
       <c r="C5" s="41">
         <f>Exams!B5</f>
@@ -4085,7 +4153,7 @@
       </c>
       <c r="E5" s="33">
         <f t="shared" si="0"/>
-        <v>0.33333333333333331</v>
+        <v>0.34285714285714286</v>
       </c>
       <c r="F5" s="33">
         <f t="shared" si="1"/>
@@ -4102,7 +4170,7 @@
       </c>
       <c r="B6" s="33">
         <f>Quiz!V6</f>
-        <v>1</v>
+        <v>0.91428571428571426</v>
       </c>
       <c r="C6" s="41">
         <f>Exams!B6</f>
@@ -4114,7 +4182,7 @@
       </c>
       <c r="E6" s="33">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.91428571428571426</v>
       </c>
       <c r="F6" s="33">
         <f t="shared" si="1"/>
@@ -4131,7 +4199,7 @@
       </c>
       <c r="B7" s="33">
         <f>Quiz!V7</f>
-        <v>1.5333333333333334</v>
+        <v>1.3714285714285714</v>
       </c>
       <c r="C7" s="41">
         <f>Exams!B7</f>
@@ -4143,7 +4211,7 @@
       </c>
       <c r="E7" s="33">
         <f t="shared" si="0"/>
-        <v>1.5333333333333334</v>
+        <v>1.3714285714285714</v>
       </c>
       <c r="F7" s="33">
         <f t="shared" si="1"/>
@@ -4160,7 +4228,7 @@
       </c>
       <c r="B8" s="33">
         <f>Quiz!V8</f>
-        <v>0.76666666666666672</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="C8" s="41">
         <f>Exams!B8</f>
@@ -4172,11 +4240,11 @@
       </c>
       <c r="E8" s="33">
         <f t="shared" si="0"/>
-        <v>0.76666666666666672</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="F8" s="33">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G8" s="47">
         <f t="shared" si="2"/>
@@ -4189,7 +4257,7 @@
       </c>
       <c r="B9" s="33">
         <f>Quiz!V9</f>
-        <v>0.8</v>
+        <v>0.74285714285714288</v>
       </c>
       <c r="C9" s="41">
         <f>Exams!B9</f>
@@ -4201,11 +4269,11 @@
       </c>
       <c r="E9" s="33">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.74285714285714288</v>
       </c>
       <c r="F9" s="33">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G9" s="47">
         <f t="shared" si="2"/>
@@ -4218,7 +4286,7 @@
       </c>
       <c r="B10" s="33">
         <f>Quiz!V10</f>
-        <v>1</v>
+        <v>0.91428571428571426</v>
       </c>
       <c r="C10" s="41">
         <f>Exams!B10</f>
@@ -4230,7 +4298,7 @@
       </c>
       <c r="E10" s="33">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.91428571428571426</v>
       </c>
       <c r="F10" s="33">
         <f t="shared" si="1"/>
@@ -4247,7 +4315,7 @@
       </c>
       <c r="B11" s="33">
         <f>Quiz!V11</f>
-        <v>0.6</v>
+        <v>0.68571428571428572</v>
       </c>
       <c r="C11" s="41">
         <f>Exams!B11</f>
@@ -4259,7 +4327,7 @@
       </c>
       <c r="E11" s="33">
         <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.68571428571428572</v>
       </c>
       <c r="F11" s="33">
         <f t="shared" si="1"/>
@@ -4276,7 +4344,7 @@
       </c>
       <c r="B12" s="33">
         <f>Quiz!V12</f>
-        <v>0.93333333333333335</v>
+        <v>0.97142857142857142</v>
       </c>
       <c r="C12" s="41">
         <f>Exams!B12</f>
@@ -4288,7 +4356,7 @@
       </c>
       <c r="E12" s="33">
         <f t="shared" si="0"/>
-        <v>0.93333333333333335</v>
+        <v>0.97142857142857142</v>
       </c>
       <c r="F12" s="33">
         <f t="shared" si="1"/>
@@ -4305,7 +4373,7 @@
       </c>
       <c r="B13" s="33">
         <f>Quiz!V13</f>
-        <v>0.83333333333333337</v>
+        <v>0.88571428571428568</v>
       </c>
       <c r="C13" s="41">
         <f>Exams!B13</f>
@@ -4317,7 +4385,7 @@
       </c>
       <c r="E13" s="33">
         <f t="shared" si="0"/>
-        <v>0.83333333333333337</v>
+        <v>0.88571428571428568</v>
       </c>
       <c r="F13" s="33">
         <f t="shared" si="1"/>
@@ -4334,7 +4402,7 @@
       </c>
       <c r="B14" s="33">
         <f>Quiz!V14</f>
-        <v>1.1000000000000001</v>
+        <v>1.1142857142857143</v>
       </c>
       <c r="C14" s="41">
         <f>Exams!B14</f>
@@ -4346,7 +4414,7 @@
       </c>
       <c r="E14" s="33">
         <f t="shared" si="0"/>
-        <v>1.1000000000000001</v>
+        <v>1.1142857142857143</v>
       </c>
       <c r="F14" s="33">
         <f t="shared" si="1"/>
@@ -4363,7 +4431,7 @@
       </c>
       <c r="B15" s="33">
         <f>Quiz!V15</f>
-        <v>1.8333333333333333</v>
+        <v>1.8571428571428572</v>
       </c>
       <c r="C15" s="41">
         <f>Exams!B15</f>
@@ -4375,7 +4443,7 @@
       </c>
       <c r="E15" s="33">
         <f t="shared" si="0"/>
-        <v>1.8333333333333333</v>
+        <v>1.8571428571428572</v>
       </c>
       <c r="F15" s="33">
         <f t="shared" si="1"/>
@@ -4392,7 +4460,7 @@
       </c>
       <c r="B16" s="33">
         <f>Quiz!V16</f>
-        <v>0.96666666666666667</v>
+        <v>0.88571428571428568</v>
       </c>
       <c r="C16" s="41">
         <f>Exams!B16</f>
@@ -4404,7 +4472,7 @@
       </c>
       <c r="E16" s="33">
         <f t="shared" si="0"/>
-        <v>0.96666666666666667</v>
+        <v>0.88571428571428568</v>
       </c>
       <c r="F16" s="33">
         <f t="shared" si="1"/>
@@ -4450,7 +4518,7 @@
       </c>
       <c r="B18" s="33">
         <f>Quiz!V18</f>
-        <v>0.73333333333333328</v>
+        <v>0.62857142857142856</v>
       </c>
       <c r="C18" s="41">
         <f>Exams!B18</f>
@@ -4462,7 +4530,7 @@
       </c>
       <c r="E18" s="33">
         <f t="shared" si="0"/>
-        <v>0.73333333333333328</v>
+        <v>0.62857142857142856</v>
       </c>
       <c r="F18" s="33">
         <f t="shared" si="1"/>
@@ -4479,7 +4547,7 @@
       </c>
       <c r="B19" s="33">
         <f>Quiz!V19</f>
-        <v>1.0333333333333334</v>
+        <v>0.94285714285714284</v>
       </c>
       <c r="C19" s="41">
         <f>Exams!B19</f>
@@ -4491,7 +4559,7 @@
       </c>
       <c r="E19" s="33">
         <f t="shared" si="0"/>
-        <v>1.0333333333333334</v>
+        <v>0.94285714285714284</v>
       </c>
       <c r="F19" s="33">
         <f t="shared" si="1"/>
@@ -4508,7 +4576,7 @@
       </c>
       <c r="B20" s="33">
         <f>Quiz!V20</f>
-        <v>0.93333333333333335</v>
+        <v>0.97142857142857142</v>
       </c>
       <c r="C20" s="41">
         <f>Exams!B20</f>
@@ -4520,7 +4588,7 @@
       </c>
       <c r="E20" s="33">
         <f t="shared" si="0"/>
-        <v>0.93333333333333335</v>
+        <v>0.97142857142857142</v>
       </c>
       <c r="F20" s="33">
         <f t="shared" ref="F20:F25" si="3">0.5*INT(E20/0.5)+INT( ((E20-INT(E20/0.5)*0.5)/0.25))*0.5</f>
@@ -4537,7 +4605,7 @@
       </c>
       <c r="B21" s="33">
         <f>Quiz!V21</f>
-        <v>1.4666666666666666</v>
+        <v>1.4285714285714286</v>
       </c>
       <c r="C21" s="41">
         <f>Exams!B21</f>
@@ -4549,7 +4617,7 @@
       </c>
       <c r="E21" s="33">
         <f t="shared" si="0"/>
-        <v>1.4666666666666666</v>
+        <v>1.4285714285714286</v>
       </c>
       <c r="F21" s="33">
         <f t="shared" si="3"/>
@@ -4566,7 +4634,7 @@
       </c>
       <c r="B22" s="33">
         <f>Quiz!V22</f>
-        <v>0.9</v>
+        <v>0.94285714285714284</v>
       </c>
       <c r="C22" s="41">
         <f>Exams!B22</f>
@@ -4578,7 +4646,7 @@
       </c>
       <c r="E22" s="33">
         <f t="shared" si="0"/>
-        <v>0.9</v>
+        <v>0.94285714285714284</v>
       </c>
       <c r="F22" s="33">
         <f t="shared" si="3"/>
@@ -4595,7 +4663,7 @@
       </c>
       <c r="B23" s="33">
         <f>Quiz!V23</f>
-        <v>1.6333333333333333</v>
+        <v>1.6285714285714286</v>
       </c>
       <c r="C23" s="41">
         <f>Exams!B23</f>
@@ -4607,7 +4675,7 @@
       </c>
       <c r="E23" s="33">
         <f t="shared" si="0"/>
-        <v>1.6333333333333333</v>
+        <v>1.6285714285714286</v>
       </c>
       <c r="F23" s="33">
         <f t="shared" si="3"/>
@@ -4624,7 +4692,7 @@
       </c>
       <c r="B24" s="33">
         <f>Quiz!V24</f>
-        <v>0.8</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="C24" s="41">
         <f>Exams!B24</f>
@@ -4636,7 +4704,7 @@
       </c>
       <c r="E24" s="33">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="F24" s="33">
         <f t="shared" si="3"/>
@@ -4653,7 +4721,7 @@
       </c>
       <c r="B25" s="33">
         <f>Quiz!V25</f>
-        <v>1.1000000000000001</v>
+        <v>1.1142857142857143</v>
       </c>
       <c r="C25" s="41">
         <f>Exams!B25</f>
@@ -4665,7 +4733,7 @@
       </c>
       <c r="E25" s="33">
         <f t="shared" si="0"/>
-        <v>1.1000000000000001</v>
+        <v>1.1142857142857143</v>
       </c>
       <c r="F25" s="33">
         <f t="shared" si="3"/>
@@ -4682,7 +4750,7 @@
       </c>
       <c r="B26" s="33">
         <f>Quiz!V26</f>
-        <v>0.6</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="C26" s="41">
         <f>Exams!B26</f>
@@ -4694,7 +4762,7 @@
       </c>
       <c r="E26" s="33">
         <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="F26" s="33">
         <f t="shared" ref="F26:F40" si="5">0.5*INT(E26/0.5)+INT( ((E26-INT(E26/0.5)*0.5)/0.25))*0.5</f>
@@ -4711,7 +4779,7 @@
       </c>
       <c r="B27" s="33">
         <f>Quiz!V27</f>
-        <v>0.53333333333333333</v>
+        <v>0.62857142857142856</v>
       </c>
       <c r="C27" s="41">
         <f>Exams!B27</f>
@@ -4723,7 +4791,7 @@
       </c>
       <c r="E27" s="33">
         <f t="shared" si="0"/>
-        <v>0.53333333333333333</v>
+        <v>0.62857142857142856</v>
       </c>
       <c r="F27" s="33">
         <f t="shared" si="5"/>
@@ -4740,7 +4808,7 @@
       </c>
       <c r="B28" s="33">
         <f>Quiz!V28</f>
-        <v>0.73333333333333328</v>
+        <v>0.8</v>
       </c>
       <c r="C28" s="41">
         <f>Exams!B28</f>
@@ -4752,11 +4820,11 @@
       </c>
       <c r="E28" s="33">
         <f t="shared" si="0"/>
-        <v>0.73333333333333328</v>
+        <v>0.8</v>
       </c>
       <c r="F28" s="33">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G28" s="47">
         <f t="shared" si="6"/>
@@ -4769,7 +4837,7 @@
       </c>
       <c r="B29" s="33">
         <f>Quiz!V29</f>
-        <v>0.9</v>
+        <v>0.82857142857142863</v>
       </c>
       <c r="C29" s="41">
         <f>Exams!B29</f>
@@ -4781,7 +4849,7 @@
       </c>
       <c r="E29" s="33">
         <f t="shared" si="0"/>
-        <v>0.9</v>
+        <v>0.82857142857142863</v>
       </c>
       <c r="F29" s="33">
         <f t="shared" si="5"/>
@@ -4798,7 +4866,7 @@
       </c>
       <c r="B30" s="33">
         <f>Quiz!V30</f>
-        <v>0.93333333333333335</v>
+        <v>0.97142857142857142</v>
       </c>
       <c r="C30" s="41">
         <f>Exams!B30</f>
@@ -4810,7 +4878,7 @@
       </c>
       <c r="E30" s="33">
         <f t="shared" si="0"/>
-        <v>0.93333333333333335</v>
+        <v>0.97142857142857142</v>
       </c>
       <c r="F30" s="33">
         <f t="shared" si="5"/>
@@ -4827,7 +4895,7 @@
       </c>
       <c r="B31" s="33">
         <f>Quiz!V31</f>
-        <v>0.5</v>
+        <v>0.48571428571428571</v>
       </c>
       <c r="C31" s="41">
         <f>Exams!B31</f>
@@ -4839,7 +4907,7 @@
       </c>
       <c r="E31" s="33">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0.48571428571428571</v>
       </c>
       <c r="F31" s="33">
         <f t="shared" si="5"/>
@@ -4856,7 +4924,7 @@
       </c>
       <c r="B32" s="33">
         <f>Quiz!V32</f>
-        <v>0.93333333333333335</v>
+        <v>1.0142857142857142</v>
       </c>
       <c r="C32" s="41">
         <f>Exams!B32</f>
@@ -4868,7 +4936,7 @@
       </c>
       <c r="E32" s="33">
         <f t="shared" si="0"/>
-        <v>0.93333333333333335</v>
+        <v>1.0142857142857142</v>
       </c>
       <c r="F32" s="33">
         <f t="shared" si="5"/>
@@ -4914,7 +4982,7 @@
       </c>
       <c r="B34" s="33">
         <f>Quiz!V34</f>
-        <v>0.33333333333333331</v>
+        <v>0.34285714285714286</v>
       </c>
       <c r="C34" s="41">
         <f>Exams!B34</f>
@@ -4926,7 +4994,7 @@
       </c>
       <c r="E34" s="33">
         <f t="shared" si="0"/>
-        <v>0.33333333333333331</v>
+        <v>0.34285714285714286</v>
       </c>
       <c r="F34" s="33">
         <f t="shared" si="5"/>
@@ -4943,7 +5011,7 @@
       </c>
       <c r="B35" s="33">
         <f>Quiz!V35</f>
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="C35" s="41">
         <f>Exams!B35</f>
@@ -4955,7 +5023,7 @@
       </c>
       <c r="E35" s="33">
         <f t="shared" si="0"/>
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="F35" s="33">
         <f t="shared" si="5"/>
@@ -4972,7 +5040,7 @@
       </c>
       <c r="B36" s="33">
         <f>Quiz!V36</f>
-        <v>0.6</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="C36" s="41">
         <f>Exams!B36</f>
@@ -4984,7 +5052,7 @@
       </c>
       <c r="E36" s="33">
         <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="F36" s="33">
         <f t="shared" si="5"/>
@@ -5001,7 +5069,7 @@
       </c>
       <c r="B37" s="33">
         <f>Quiz!V37</f>
-        <v>1.1666666666666667</v>
+        <v>1.1714285714285715</v>
       </c>
       <c r="C37" s="41">
         <f>Exams!B37</f>
@@ -5013,7 +5081,7 @@
       </c>
       <c r="E37" s="33">
         <f t="shared" si="0"/>
-        <v>1.1666666666666667</v>
+        <v>1.1714285714285715</v>
       </c>
       <c r="F37" s="33">
         <f t="shared" si="5"/>
@@ -5030,7 +5098,7 @@
       </c>
       <c r="B38" s="33">
         <f>Quiz!V38</f>
-        <v>0.66666666666666663</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="C38" s="41">
         <f>Exams!B38</f>
@@ -5042,7 +5110,7 @@
       </c>
       <c r="E38" s="33">
         <f t="shared" si="0"/>
-        <v>0.66666666666666663</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="F38" s="33">
         <f t="shared" si="5"/>
@@ -5059,7 +5127,7 @@
       </c>
       <c r="B39" s="33">
         <f>Quiz!V39</f>
-        <v>1.2666666666666666</v>
+        <v>1.1428571428571428</v>
       </c>
       <c r="C39" s="41">
         <f>Exams!B39</f>
@@ -5071,11 +5139,11 @@
       </c>
       <c r="E39" s="33">
         <f t="shared" si="0"/>
-        <v>1.2666666666666666</v>
+        <v>1.1428571428571428</v>
       </c>
       <c r="F39" s="33">
         <f t="shared" ref="F39" si="8">0.5*INT(E39/0.5)+INT( ((E39-INT(E39/0.5)*0.5)/0.25))*0.5</f>
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G39" s="47">
         <f t="shared" ref="G39" si="9">IF(F39&gt;4.75,1,0)</f>
@@ -5088,7 +5156,7 @@
       </c>
       <c r="B40" s="33">
         <f>Quiz!V40</f>
-        <v>1.2</v>
+        <v>1.0857142857142856</v>
       </c>
       <c r="C40" s="41">
         <f>Exams!B40</f>
@@ -5100,7 +5168,7 @@
       </c>
       <c r="E40" s="33">
         <f t="shared" si="0"/>
-        <v>1.2</v>
+        <v>1.0857142857142856</v>
       </c>
       <c r="F40" s="33">
         <f t="shared" si="5"/>
@@ -5153,7 +5221,7 @@
       </c>
       <c r="B43" s="29">
         <f t="shared" ref="B43:G43" si="10">AVERAGE(B$2:B$40)</f>
-        <v>0.8760683760683764</v>
+        <v>0.85604395604395622</v>
       </c>
       <c r="C43" s="29">
         <f t="shared" si="10"/>
@@ -5165,11 +5233,11 @@
       </c>
       <c r="E43" s="29">
         <f t="shared" si="10"/>
-        <v>0.8760683760683764</v>
+        <v>0.85604395604395622</v>
       </c>
       <c r="F43" s="29">
         <f t="shared" si="10"/>
-        <v>0.88461538461538458</v>
+        <v>0.85897435897435892</v>
       </c>
       <c r="G43" s="29">
         <f t="shared" si="10"/>
@@ -5182,7 +5250,7 @@
       </c>
       <c r="B44" s="29">
         <f t="shared" ref="B44:G44" si="11">STDEV(B$2:B$40)</f>
-        <v>0.38264229994160714</v>
+        <v>0.37196873122260321</v>
       </c>
       <c r="C44" s="29">
         <f t="shared" si="11"/>
@@ -5194,11 +5262,11 @@
       </c>
       <c r="E44" s="29">
         <f t="shared" si="11"/>
-        <v>0.38264229994160714</v>
+        <v>0.37196873122260321</v>
       </c>
       <c r="F44" s="29">
         <f t="shared" si="11"/>
-        <v>0.40492914359926274</v>
+        <v>0.39650973885826146</v>
       </c>
       <c r="G44" s="29">
         <f t="shared" si="11"/>
@@ -5211,7 +5279,7 @@
       </c>
       <c r="B45" s="29">
         <f t="shared" ref="B45:G45" si="12">MEDIAN(B$2:B$40)</f>
-        <v>0.9</v>
+        <v>0.88571428571428568</v>
       </c>
       <c r="C45" s="29">
         <f t="shared" si="12"/>
@@ -5223,7 +5291,7 @@
       </c>
       <c r="E45" s="29">
         <f t="shared" si="12"/>
-        <v>0.9</v>
+        <v>0.88571428571428568</v>
       </c>
       <c r="F45" s="29">
         <f t="shared" si="12"/>

--- a/phy112/Grades/grades_report_2026.xlsx
+++ b/phy112/Grades/grades_report_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ptohos/Documents/MyCourses/FYS112/2026/Grades/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09A4A60D-239E-5E4D-A0FC-1B6818B57E35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9A2C49B-7897-6242-915D-BFC339752EC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="540" yWindow="3080" windowWidth="32920" windowHeight="19260" tabRatio="334" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1014,7 +1014,9 @@
       <c r="I2" s="18">
         <v>4</v>
       </c>
-      <c r="J2" s="18"/>
+      <c r="J2" s="18">
+        <v>12</v>
+      </c>
       <c r="K2" s="18"/>
       <c r="L2" s="18"/>
       <c r="M2" s="18"/>
@@ -1028,7 +1030,7 @@
       <c r="U2" s="18"/>
       <c r="V2" s="33">
         <f t="shared" ref="V2:V39" si="0">$V$42 * ( (SUM(B2:U2))/((SUM($B$46:$U$46))*$B$42) )</f>
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="W2"/>
     </row>
@@ -1070,7 +1072,7 @@
       <c r="U3" s="18"/>
       <c r="V3" s="33">
         <f t="shared" si="0"/>
-        <v>0.62857142857142856</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="W3"/>
     </row>
@@ -1100,7 +1102,9 @@
       <c r="I4" s="18">
         <v>4</v>
       </c>
-      <c r="J4" s="18"/>
+      <c r="J4" s="18">
+        <v>12</v>
+      </c>
       <c r="K4" s="18"/>
       <c r="L4" s="18"/>
       <c r="M4" s="18"/>
@@ -1114,7 +1118,7 @@
       <c r="U4" s="18"/>
       <c r="V4" s="33">
         <f t="shared" si="0"/>
-        <v>0.95714285714285718</v>
+        <v>0.98750000000000004</v>
       </c>
       <c r="W4"/>
     </row>
@@ -1142,7 +1146,9 @@
       <c r="I5" s="18">
         <v>4</v>
       </c>
-      <c r="J5" s="18"/>
+      <c r="J5" s="18">
+        <v>12</v>
+      </c>
       <c r="K5" s="18"/>
       <c r="L5" s="18"/>
       <c r="M5" s="18"/>
@@ -1156,7 +1162,7 @@
       <c r="U5" s="18"/>
       <c r="V5" s="33">
         <f t="shared" si="0"/>
-        <v>0.34285714285714286</v>
+        <v>0.45</v>
       </c>
       <c r="W5"/>
     </row>
@@ -1186,7 +1192,9 @@
       <c r="I6" s="18">
         <v>4</v>
       </c>
-      <c r="J6" s="18"/>
+      <c r="J6" s="18">
+        <v>4</v>
+      </c>
       <c r="K6" s="18"/>
       <c r="L6" s="18"/>
       <c r="M6" s="18"/>
@@ -1200,7 +1208,7 @@
       <c r="U6" s="18"/>
       <c r="V6" s="33">
         <f t="shared" si="0"/>
-        <v>0.91428571428571426</v>
+        <v>0.85</v>
       </c>
       <c r="W6"/>
     </row>
@@ -1230,7 +1238,9 @@
       <c r="I7" s="18">
         <v>4</v>
       </c>
-      <c r="J7" s="18"/>
+      <c r="J7" s="18">
+        <v>12</v>
+      </c>
       <c r="K7" s="18"/>
       <c r="L7" s="18"/>
       <c r="M7" s="18"/>
@@ -1244,7 +1254,7 @@
       <c r="U7" s="18"/>
       <c r="V7" s="33">
         <f t="shared" si="0"/>
-        <v>1.3714285714285714</v>
+        <v>1.35</v>
       </c>
       <c r="W7"/>
     </row>
@@ -1288,7 +1298,7 @@
       <c r="U8" s="18"/>
       <c r="V8" s="33">
         <f t="shared" si="0"/>
-        <v>0.7142857142857143</v>
+        <v>0.625</v>
       </c>
       <c r="W8"/>
     </row>
@@ -1314,7 +1324,9 @@
       <c r="I9" s="18">
         <v>4</v>
       </c>
-      <c r="J9" s="18"/>
+      <c r="J9" s="18">
+        <v>4</v>
+      </c>
       <c r="K9" s="18"/>
       <c r="L9" s="18"/>
       <c r="M9" s="18"/>
@@ -1328,7 +1340,7 @@
       <c r="U9" s="18"/>
       <c r="V9" s="33">
         <f t="shared" si="0"/>
-        <v>0.74285714285714288</v>
+        <v>0.7</v>
       </c>
       <c r="W9"/>
     </row>
@@ -1354,7 +1366,9 @@
       <c r="I10" s="18">
         <v>4</v>
       </c>
-      <c r="J10" s="18"/>
+      <c r="J10" s="18">
+        <v>4</v>
+      </c>
       <c r="K10" s="18"/>
       <c r="L10" s="18"/>
       <c r="M10" s="18"/>
@@ -1368,7 +1382,7 @@
       <c r="U10" s="18"/>
       <c r="V10" s="33">
         <f t="shared" si="0"/>
-        <v>0.91428571428571426</v>
+        <v>0.85</v>
       </c>
       <c r="W10"/>
     </row>
@@ -1396,7 +1410,9 @@
       <c r="I11" s="18">
         <v>12</v>
       </c>
-      <c r="J11" s="18"/>
+      <c r="J11" s="18">
+        <v>4</v>
+      </c>
       <c r="K11" s="18"/>
       <c r="L11" s="18"/>
       <c r="M11" s="18"/>
@@ -1410,7 +1426,7 @@
       <c r="U11" s="18"/>
       <c r="V11" s="33">
         <f t="shared" si="0"/>
-        <v>0.68571428571428572</v>
+        <v>0.65</v>
       </c>
       <c r="W11"/>
     </row>
@@ -1440,7 +1456,9 @@
       <c r="I12" s="18">
         <v>12</v>
       </c>
-      <c r="J12" s="18"/>
+      <c r="J12" s="18">
+        <v>4</v>
+      </c>
       <c r="K12" s="18"/>
       <c r="L12" s="18"/>
       <c r="M12" s="18"/>
@@ -1454,7 +1472,7 @@
       <c r="U12" s="18"/>
       <c r="V12" s="33">
         <f t="shared" si="0"/>
-        <v>0.97142857142857142</v>
+        <v>0.9</v>
       </c>
       <c r="W12"/>
     </row>
@@ -1484,7 +1502,9 @@
       <c r="I13" s="18">
         <v>12</v>
       </c>
-      <c r="J13" s="18"/>
+      <c r="J13" s="18">
+        <v>4</v>
+      </c>
       <c r="K13" s="18"/>
       <c r="L13" s="18"/>
       <c r="M13" s="18"/>
@@ -1498,7 +1518,7 @@
       <c r="U13" s="18"/>
       <c r="V13" s="33">
         <f t="shared" si="0"/>
-        <v>0.88571428571428568</v>
+        <v>0.82499999999999996</v>
       </c>
       <c r="W13"/>
     </row>
@@ -1528,7 +1548,9 @@
       <c r="I14" s="18">
         <v>12</v>
       </c>
-      <c r="J14" s="18"/>
+      <c r="J14" s="18">
+        <v>12</v>
+      </c>
       <c r="K14" s="18"/>
       <c r="L14" s="18"/>
       <c r="M14" s="18"/>
@@ -1542,7 +1564,7 @@
       <c r="U14" s="18"/>
       <c r="V14" s="33">
         <f t="shared" si="0"/>
-        <v>1.1142857142857143</v>
+        <v>1.125</v>
       </c>
     </row>
     <row r="15" spans="1:23" ht="29" customHeight="1" x14ac:dyDescent="0.15">
@@ -1571,7 +1593,9 @@
       <c r="I15" s="18">
         <v>20</v>
       </c>
-      <c r="J15" s="18"/>
+      <c r="J15" s="18">
+        <v>4</v>
+      </c>
       <c r="K15" s="18"/>
       <c r="L15" s="18"/>
       <c r="M15" s="18"/>
@@ -1585,7 +1609,7 @@
       <c r="U15" s="18"/>
       <c r="V15" s="33">
         <f t="shared" si="0"/>
-        <v>1.8571428571428572</v>
+        <v>1.675</v>
       </c>
       <c r="W15"/>
     </row>
@@ -1615,7 +1639,9 @@
       <c r="I16" s="18">
         <v>4</v>
       </c>
-      <c r="J16" s="18"/>
+      <c r="J16" s="18">
+        <v>4</v>
+      </c>
       <c r="K16" s="18"/>
       <c r="L16" s="18"/>
       <c r="M16" s="18"/>
@@ -1629,7 +1655,7 @@
       <c r="U16" s="18"/>
       <c r="V16" s="33">
         <f t="shared" si="0"/>
-        <v>0.88571428571428568</v>
+        <v>0.82499999999999996</v>
       </c>
       <c r="W16"/>
     </row>
@@ -1685,7 +1711,9 @@
       </c>
       <c r="H18" s="18"/>
       <c r="I18" s="18"/>
-      <c r="J18" s="18"/>
+      <c r="J18" s="18">
+        <v>12</v>
+      </c>
       <c r="K18" s="18"/>
       <c r="L18" s="18"/>
       <c r="M18" s="18"/>
@@ -1699,7 +1727,7 @@
       <c r="U18" s="18"/>
       <c r="V18" s="33">
         <f t="shared" si="0"/>
-        <v>0.62857142857142856</v>
+        <v>0.7</v>
       </c>
       <c r="W18"/>
     </row>
@@ -1729,7 +1757,9 @@
       <c r="I19" s="18">
         <v>4</v>
       </c>
-      <c r="J19" s="18"/>
+      <c r="J19" s="18">
+        <v>12</v>
+      </c>
       <c r="K19" s="18"/>
       <c r="L19" s="18"/>
       <c r="M19" s="18"/>
@@ -1743,7 +1773,7 @@
       <c r="U19" s="18"/>
       <c r="V19" s="33">
         <f t="shared" si="0"/>
-        <v>0.94285714285714284</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="W19"/>
     </row>
@@ -1771,7 +1801,9 @@
       <c r="I20" s="18">
         <v>12</v>
       </c>
-      <c r="J20" s="18"/>
+      <c r="J20" s="18">
+        <v>4</v>
+      </c>
       <c r="K20" s="18"/>
       <c r="L20" s="18"/>
       <c r="M20" s="18"/>
@@ -1785,7 +1817,7 @@
       <c r="U20" s="18"/>
       <c r="V20" s="33">
         <f t="shared" si="0"/>
-        <v>0.97142857142857142</v>
+        <v>0.9</v>
       </c>
       <c r="W20"/>
     </row>
@@ -1815,7 +1847,9 @@
       <c r="I21" s="18">
         <v>12</v>
       </c>
-      <c r="J21" s="18"/>
+      <c r="J21" s="18">
+        <v>4</v>
+      </c>
       <c r="K21" s="18"/>
       <c r="L21" s="18"/>
       <c r="M21" s="18"/>
@@ -1829,7 +1863,7 @@
       <c r="U21" s="18"/>
       <c r="V21" s="33">
         <f t="shared" si="0"/>
-        <v>1.4285714285714286</v>
+        <v>1.3</v>
       </c>
       <c r="W21"/>
     </row>
@@ -1857,7 +1891,9 @@
       <c r="I22" s="18">
         <v>12</v>
       </c>
-      <c r="J22" s="18"/>
+      <c r="J22" s="18">
+        <v>4</v>
+      </c>
       <c r="K22" s="18"/>
       <c r="L22" s="18"/>
       <c r="M22" s="18"/>
@@ -1871,7 +1907,7 @@
       <c r="U22" s="18"/>
       <c r="V22" s="33">
         <f t="shared" si="0"/>
-        <v>0.94285714285714284</v>
+        <v>0.875</v>
       </c>
       <c r="W22"/>
     </row>
@@ -1901,7 +1937,9 @@
       <c r="I23" s="18">
         <v>16</v>
       </c>
-      <c r="J23" s="18"/>
+      <c r="J23" s="18">
+        <v>4</v>
+      </c>
       <c r="K23" s="18"/>
       <c r="L23" s="18"/>
       <c r="M23" s="18"/>
@@ -1915,7 +1953,7 @@
       <c r="U23" s="18"/>
       <c r="V23" s="33">
         <f t="shared" si="0"/>
-        <v>1.6285714285714286</v>
+        <v>1.4750000000000001</v>
       </c>
       <c r="W23"/>
     </row>
@@ -1943,7 +1981,9 @@
       <c r="I24" s="18">
         <v>12</v>
       </c>
-      <c r="J24" s="18"/>
+      <c r="J24" s="18">
+        <v>12</v>
+      </c>
       <c r="K24" s="18"/>
       <c r="L24" s="18"/>
       <c r="M24" s="18"/>
@@ -1957,7 +1997,7 @@
       <c r="U24" s="18"/>
       <c r="V24" s="33">
         <f t="shared" si="0"/>
-        <v>0.8571428571428571</v>
+        <v>0.9</v>
       </c>
       <c r="W24"/>
     </row>
@@ -1983,7 +2023,9 @@
       <c r="I25" s="18">
         <v>12</v>
       </c>
-      <c r="J25" s="18"/>
+      <c r="J25" s="18">
+        <v>4</v>
+      </c>
       <c r="K25" s="18"/>
       <c r="L25" s="18"/>
       <c r="M25" s="18"/>
@@ -1997,7 +2039,7 @@
       <c r="U25" s="18"/>
       <c r="V25" s="33">
         <f t="shared" si="0"/>
-        <v>1.1142857142857143</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="W25"/>
     </row>
@@ -2027,7 +2069,9 @@
       <c r="I26" s="18">
         <v>4</v>
       </c>
-      <c r="J26" s="18"/>
+      <c r="J26" s="18">
+        <v>4</v>
+      </c>
       <c r="K26" s="18"/>
       <c r="L26" s="18"/>
       <c r="M26" s="18"/>
@@ -2041,7 +2085,7 @@
       <c r="U26" s="18"/>
       <c r="V26" s="33">
         <f t="shared" si="0"/>
-        <v>0.5714285714285714</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="W26"/>
     </row>
@@ -2067,7 +2111,9 @@
       <c r="I27" s="18">
         <v>12</v>
       </c>
-      <c r="J27" s="18"/>
+      <c r="J27" s="18">
+        <v>4</v>
+      </c>
       <c r="K27" s="18"/>
       <c r="L27" s="18"/>
       <c r="M27" s="18"/>
@@ -2081,7 +2127,7 @@
       <c r="U27" s="18"/>
       <c r="V27" s="33">
         <f t="shared" si="0"/>
-        <v>0.62857142857142856</v>
+        <v>0.6</v>
       </c>
       <c r="W27"/>
     </row>
@@ -2109,7 +2155,9 @@
       <c r="I28" s="18">
         <v>12</v>
       </c>
-      <c r="J28" s="18"/>
+      <c r="J28" s="18">
+        <v>4</v>
+      </c>
       <c r="K28" s="18"/>
       <c r="L28" s="18"/>
       <c r="M28" s="18"/>
@@ -2123,7 +2171,7 @@
       <c r="U28" s="18"/>
       <c r="V28" s="33">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="W28"/>
     </row>
@@ -2153,7 +2201,9 @@
       <c r="I29" s="18">
         <v>4</v>
       </c>
-      <c r="J29" s="18"/>
+      <c r="J29" s="18">
+        <v>12</v>
+      </c>
       <c r="K29" s="18"/>
       <c r="L29" s="18"/>
       <c r="M29" s="18"/>
@@ -2167,7 +2217,7 @@
       <c r="U29" s="18"/>
       <c r="V29" s="33">
         <f t="shared" si="0"/>
-        <v>0.82857142857142863</v>
+        <v>0.875</v>
       </c>
       <c r="W29"/>
     </row>
@@ -2197,7 +2247,9 @@
       <c r="I30" s="18">
         <v>12</v>
       </c>
-      <c r="J30" s="18"/>
+      <c r="J30" s="18">
+        <v>4</v>
+      </c>
       <c r="K30" s="18"/>
       <c r="L30" s="18"/>
       <c r="M30" s="18"/>
@@ -2211,7 +2263,7 @@
       <c r="U30" s="18"/>
       <c r="V30" s="33">
         <f t="shared" si="0"/>
-        <v>0.97142857142857142</v>
+        <v>0.9</v>
       </c>
       <c r="W30"/>
     </row>
@@ -2253,7 +2305,7 @@
       <c r="U31" s="18"/>
       <c r="V31" s="33">
         <f t="shared" si="0"/>
-        <v>0.48571428571428571</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="W31"/>
     </row>
@@ -2283,7 +2335,9 @@
       <c r="I32" s="18">
         <v>15</v>
       </c>
-      <c r="J32" s="18"/>
+      <c r="J32" s="18">
+        <v>4</v>
+      </c>
       <c r="K32" s="18"/>
       <c r="L32" s="18"/>
       <c r="M32" s="18"/>
@@ -2297,7 +2351,7 @@
       <c r="U32" s="18"/>
       <c r="V32" s="33">
         <f t="shared" si="0"/>
-        <v>1.0142857142857142</v>
+        <v>0.9375</v>
       </c>
       <c r="W32"/>
     </row>
@@ -2351,7 +2405,9 @@
       <c r="I34" s="18">
         <v>4</v>
       </c>
-      <c r="J34" s="18"/>
+      <c r="J34" s="18">
+        <v>12</v>
+      </c>
       <c r="K34" s="18"/>
       <c r="L34" s="18"/>
       <c r="M34" s="18"/>
@@ -2365,7 +2421,7 @@
       <c r="U34" s="18"/>
       <c r="V34" s="33">
         <f t="shared" si="0"/>
-        <v>0.34285714285714286</v>
+        <v>0.45</v>
       </c>
       <c r="W34"/>
     </row>
@@ -2395,7 +2451,9 @@
       <c r="I35" s="18">
         <v>12</v>
       </c>
-      <c r="J35" s="18"/>
+      <c r="J35" s="18">
+        <v>12</v>
+      </c>
       <c r="K35" s="18"/>
       <c r="L35" s="18"/>
       <c r="M35" s="18"/>
@@ -2409,7 +2467,7 @@
       <c r="U35" s="18"/>
       <c r="V35" s="33">
         <f t="shared" si="0"/>
-        <v>0.9</v>
+        <v>0.9375</v>
       </c>
       <c r="W35"/>
     </row>
@@ -2433,7 +2491,9 @@
       <c r="I36" s="18">
         <v>4</v>
       </c>
-      <c r="J36" s="18"/>
+      <c r="J36" s="18">
+        <v>12</v>
+      </c>
       <c r="K36" s="18"/>
       <c r="L36" s="18"/>
       <c r="M36" s="18"/>
@@ -2447,7 +2507,7 @@
       <c r="U36" s="18"/>
       <c r="V36" s="33">
         <f t="shared" si="0"/>
-        <v>0.5714285714285714</v>
+        <v>0.65</v>
       </c>
       <c r="W36"/>
     </row>
@@ -2477,7 +2537,9 @@
       <c r="I37" s="18">
         <v>12</v>
       </c>
-      <c r="J37" s="18"/>
+      <c r="J37" s="18">
+        <v>12</v>
+      </c>
       <c r="K37" s="18"/>
       <c r="L37" s="18"/>
       <c r="M37" s="18"/>
@@ -2491,7 +2553,7 @@
       <c r="U37" s="18"/>
       <c r="V37" s="33">
         <f t="shared" si="0"/>
-        <v>1.1714285714285715</v>
+        <v>1.175</v>
       </c>
       <c r="W37"/>
     </row>
@@ -2515,7 +2577,9 @@
       </c>
       <c r="H38" s="18"/>
       <c r="I38" s="18"/>
-      <c r="J38" s="18"/>
+      <c r="J38" s="18">
+        <v>12</v>
+      </c>
       <c r="K38" s="18"/>
       <c r="L38" s="18"/>
       <c r="M38" s="18"/>
@@ -2529,7 +2593,7 @@
       <c r="U38" s="18"/>
       <c r="V38" s="33">
         <f t="shared" si="0"/>
-        <v>0.5714285714285714</v>
+        <v>0.65</v>
       </c>
       <c r="W38"/>
     </row>
@@ -2559,7 +2623,9 @@
       <c r="I39" s="18">
         <v>4</v>
       </c>
-      <c r="J39" s="18"/>
+      <c r="J39" s="18">
+        <v>4</v>
+      </c>
       <c r="K39" s="18"/>
       <c r="L39" s="18"/>
       <c r="M39" s="18"/>
@@ -2573,7 +2639,7 @@
       <c r="U39" s="18"/>
       <c r="V39" s="33">
         <f t="shared" si="0"/>
-        <v>1.1428571428571428</v>
+        <v>1.05</v>
       </c>
       <c r="W39"/>
     </row>
@@ -2601,7 +2667,9 @@
       <c r="I40" s="18">
         <v>4</v>
       </c>
-      <c r="J40" s="18"/>
+      <c r="J40" s="18">
+        <v>4</v>
+      </c>
       <c r="K40" s="18"/>
       <c r="L40" s="18"/>
       <c r="M40" s="18"/>
@@ -2615,7 +2683,7 @@
       <c r="U40" s="18"/>
       <c r="V40" s="33">
         <f t="shared" ref="V40" si="1">$V$42 * ( (SUM(B40:U40))/((SUM($B$46:$U$46))*$B$42) )</f>
-        <v>1.0857142857142856</v>
+        <v>1</v>
       </c>
       <c r="W40"/>
     </row>
@@ -2749,9 +2817,9 @@
         <f t="shared" si="2"/>
         <v>8.5757575757575761</v>
       </c>
-      <c r="J43" s="29" t="e">
+      <c r="J43" s="29">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+        <v>7.3939393939393936</v>
       </c>
       <c r="K43" s="29" t="e">
         <f t="shared" si="2"/>
@@ -2799,7 +2867,7 @@
       </c>
       <c r="V43" s="29">
         <f t="shared" si="2"/>
-        <v>0.85000000000000009</v>
+        <v>0.82401315789473673</v>
       </c>
       <c r="W43"/>
     </row>
@@ -2839,9 +2907,9 @@
         <f t="shared" si="3"/>
         <v>4.7633385287415733</v>
       </c>
-      <c r="J44" s="29" t="e">
+      <c r="J44" s="29">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
+        <v>4.0151229272853062</v>
       </c>
       <c r="K44" s="29" t="e">
         <f t="shared" si="3"/>
@@ -2889,7 +2957,7 @@
       </c>
       <c r="V44" s="29">
         <f t="shared" si="3"/>
-        <v>0.37501608717102453</v>
+        <v>0.33796116614515131</v>
       </c>
       <c r="W44"/>
     </row>
@@ -2929,9 +2997,9 @@
         <f t="shared" si="4"/>
         <v>12</v>
       </c>
-      <c r="J45" s="29" t="e">
+      <c r="J45" s="29">
         <f t="shared" si="4"/>
-        <v>#NUM!</v>
+        <v>4</v>
       </c>
       <c r="K45" s="29" t="e">
         <f t="shared" si="4"/>
@@ -2979,7 +3047,7 @@
       </c>
       <c r="V45" s="29">
         <f t="shared" si="4"/>
-        <v>0.88571428571428568</v>
+        <v>0.85</v>
       </c>
       <c r="W45"/>
     </row>
@@ -3021,7 +3089,7 @@
       </c>
       <c r="J46" s="32">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K46" s="32">
         <f t="shared" si="5"/>
@@ -4053,7 +4121,7 @@
       </c>
       <c r="B2" s="33">
         <f>Quiz!V2</f>
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="C2" s="41">
         <f>Exams!B2</f>
@@ -4065,7 +4133,7 @@
       </c>
       <c r="E2" s="33">
         <f>$B2+($C2/$C$42)*3.5+($D2/$D$42)*4.5</f>
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="F2" s="33">
         <f>0.5*INT(E2/0.5)+INT( ((E2-INT(E2/0.5)*0.5)/0.25))*0.5</f>
@@ -4083,7 +4151,7 @@
       </c>
       <c r="B3" s="33">
         <f>Quiz!V3</f>
-        <v>0.62857142857142856</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="C3" s="41">
         <f>Exams!B3</f>
@@ -4095,7 +4163,7 @@
       </c>
       <c r="E3" s="33">
         <f t="shared" ref="E3:E40" si="0">$B3+($C3/$C$42)*3.5+($D3/$D$42)*4.5</f>
-        <v>0.62857142857142856</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="F3" s="33">
         <f t="shared" ref="F3:F19" si="1">0.5*INT(E3/0.5)+INT( ((E3-INT(E3/0.5)*0.5)/0.25))*0.5</f>
@@ -4112,7 +4180,7 @@
       </c>
       <c r="B4" s="33">
         <f>Quiz!V4</f>
-        <v>0.95714285714285718</v>
+        <v>0.98750000000000004</v>
       </c>
       <c r="C4" s="41">
         <f>Exams!B4</f>
@@ -4124,7 +4192,7 @@
       </c>
       <c r="E4" s="33">
         <f t="shared" si="0"/>
-        <v>0.95714285714285718</v>
+        <v>0.98750000000000004</v>
       </c>
       <c r="F4" s="33">
         <f t="shared" si="1"/>
@@ -4141,7 +4209,7 @@
       </c>
       <c r="B5" s="33">
         <f>Quiz!V5</f>
-        <v>0.34285714285714286</v>
+        <v>0.45</v>
       </c>
       <c r="C5" s="41">
         <f>Exams!B5</f>
@@ -4153,7 +4221,7 @@
       </c>
       <c r="E5" s="33">
         <f t="shared" si="0"/>
-        <v>0.34285714285714286</v>
+        <v>0.45</v>
       </c>
       <c r="F5" s="33">
         <f t="shared" si="1"/>
@@ -4170,7 +4238,7 @@
       </c>
       <c r="B6" s="33">
         <f>Quiz!V6</f>
-        <v>0.91428571428571426</v>
+        <v>0.85</v>
       </c>
       <c r="C6" s="41">
         <f>Exams!B6</f>
@@ -4182,7 +4250,7 @@
       </c>
       <c r="E6" s="33">
         <f t="shared" si="0"/>
-        <v>0.91428571428571426</v>
+        <v>0.85</v>
       </c>
       <c r="F6" s="33">
         <f t="shared" si="1"/>
@@ -4199,7 +4267,7 @@
       </c>
       <c r="B7" s="33">
         <f>Quiz!V7</f>
-        <v>1.3714285714285714</v>
+        <v>1.35</v>
       </c>
       <c r="C7" s="41">
         <f>Exams!B7</f>
@@ -4211,7 +4279,7 @@
       </c>
       <c r="E7" s="33">
         <f t="shared" si="0"/>
-        <v>1.3714285714285714</v>
+        <v>1.35</v>
       </c>
       <c r="F7" s="33">
         <f t="shared" si="1"/>
@@ -4228,7 +4296,7 @@
       </c>
       <c r="B8" s="33">
         <f>Quiz!V8</f>
-        <v>0.7142857142857143</v>
+        <v>0.625</v>
       </c>
       <c r="C8" s="41">
         <f>Exams!B8</f>
@@ -4240,7 +4308,7 @@
       </c>
       <c r="E8" s="33">
         <f t="shared" si="0"/>
-        <v>0.7142857142857143</v>
+        <v>0.625</v>
       </c>
       <c r="F8" s="33">
         <f t="shared" si="1"/>
@@ -4257,7 +4325,7 @@
       </c>
       <c r="B9" s="33">
         <f>Quiz!V9</f>
-        <v>0.74285714285714288</v>
+        <v>0.7</v>
       </c>
       <c r="C9" s="41">
         <f>Exams!B9</f>
@@ -4269,7 +4337,7 @@
       </c>
       <c r="E9" s="33">
         <f t="shared" si="0"/>
-        <v>0.74285714285714288</v>
+        <v>0.7</v>
       </c>
       <c r="F9" s="33">
         <f t="shared" si="1"/>
@@ -4286,7 +4354,7 @@
       </c>
       <c r="B10" s="33">
         <f>Quiz!V10</f>
-        <v>0.91428571428571426</v>
+        <v>0.85</v>
       </c>
       <c r="C10" s="41">
         <f>Exams!B10</f>
@@ -4298,7 +4366,7 @@
       </c>
       <c r="E10" s="33">
         <f t="shared" si="0"/>
-        <v>0.91428571428571426</v>
+        <v>0.85</v>
       </c>
       <c r="F10" s="33">
         <f t="shared" si="1"/>
@@ -4315,7 +4383,7 @@
       </c>
       <c r="B11" s="33">
         <f>Quiz!V11</f>
-        <v>0.68571428571428572</v>
+        <v>0.65</v>
       </c>
       <c r="C11" s="41">
         <f>Exams!B11</f>
@@ -4327,7 +4395,7 @@
       </c>
       <c r="E11" s="33">
         <f t="shared" si="0"/>
-        <v>0.68571428571428572</v>
+        <v>0.65</v>
       </c>
       <c r="F11" s="33">
         <f t="shared" si="1"/>
@@ -4344,7 +4412,7 @@
       </c>
       <c r="B12" s="33">
         <f>Quiz!V12</f>
-        <v>0.97142857142857142</v>
+        <v>0.9</v>
       </c>
       <c r="C12" s="41">
         <f>Exams!B12</f>
@@ -4356,7 +4424,7 @@
       </c>
       <c r="E12" s="33">
         <f t="shared" si="0"/>
-        <v>0.97142857142857142</v>
+        <v>0.9</v>
       </c>
       <c r="F12" s="33">
         <f t="shared" si="1"/>
@@ -4373,7 +4441,7 @@
       </c>
       <c r="B13" s="33">
         <f>Quiz!V13</f>
-        <v>0.88571428571428568</v>
+        <v>0.82499999999999996</v>
       </c>
       <c r="C13" s="41">
         <f>Exams!B13</f>
@@ -4385,7 +4453,7 @@
       </c>
       <c r="E13" s="33">
         <f t="shared" si="0"/>
-        <v>0.88571428571428568</v>
+        <v>0.82499999999999996</v>
       </c>
       <c r="F13" s="33">
         <f t="shared" si="1"/>
@@ -4402,7 +4470,7 @@
       </c>
       <c r="B14" s="33">
         <f>Quiz!V14</f>
-        <v>1.1142857142857143</v>
+        <v>1.125</v>
       </c>
       <c r="C14" s="41">
         <f>Exams!B14</f>
@@ -4414,7 +4482,7 @@
       </c>
       <c r="E14" s="33">
         <f t="shared" si="0"/>
-        <v>1.1142857142857143</v>
+        <v>1.125</v>
       </c>
       <c r="F14" s="33">
         <f t="shared" si="1"/>
@@ -4431,7 +4499,7 @@
       </c>
       <c r="B15" s="33">
         <f>Quiz!V15</f>
-        <v>1.8571428571428572</v>
+        <v>1.675</v>
       </c>
       <c r="C15" s="41">
         <f>Exams!B15</f>
@@ -4443,11 +4511,11 @@
       </c>
       <c r="E15" s="33">
         <f t="shared" si="0"/>
-        <v>1.8571428571428572</v>
+        <v>1.675</v>
       </c>
       <c r="F15" s="33">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="G15" s="47">
         <f t="shared" si="2"/>
@@ -4460,7 +4528,7 @@
       </c>
       <c r="B16" s="33">
         <f>Quiz!V16</f>
-        <v>0.88571428571428568</v>
+        <v>0.82499999999999996</v>
       </c>
       <c r="C16" s="41">
         <f>Exams!B16</f>
@@ -4472,7 +4540,7 @@
       </c>
       <c r="E16" s="33">
         <f t="shared" si="0"/>
-        <v>0.88571428571428568</v>
+        <v>0.82499999999999996</v>
       </c>
       <c r="F16" s="33">
         <f t="shared" si="1"/>
@@ -4518,7 +4586,7 @@
       </c>
       <c r="B18" s="33">
         <f>Quiz!V18</f>
-        <v>0.62857142857142856</v>
+        <v>0.7</v>
       </c>
       <c r="C18" s="41">
         <f>Exams!B18</f>
@@ -4530,7 +4598,7 @@
       </c>
       <c r="E18" s="33">
         <f t="shared" si="0"/>
-        <v>0.62857142857142856</v>
+        <v>0.7</v>
       </c>
       <c r="F18" s="33">
         <f t="shared" si="1"/>
@@ -4547,7 +4615,7 @@
       </c>
       <c r="B19" s="33">
         <f>Quiz!V19</f>
-        <v>0.94285714285714284</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="C19" s="41">
         <f>Exams!B19</f>
@@ -4559,7 +4627,7 @@
       </c>
       <c r="E19" s="33">
         <f t="shared" si="0"/>
-        <v>0.94285714285714284</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="F19" s="33">
         <f t="shared" si="1"/>
@@ -4576,7 +4644,7 @@
       </c>
       <c r="B20" s="33">
         <f>Quiz!V20</f>
-        <v>0.97142857142857142</v>
+        <v>0.9</v>
       </c>
       <c r="C20" s="41">
         <f>Exams!B20</f>
@@ -4588,7 +4656,7 @@
       </c>
       <c r="E20" s="33">
         <f t="shared" si="0"/>
-        <v>0.97142857142857142</v>
+        <v>0.9</v>
       </c>
       <c r="F20" s="33">
         <f t="shared" ref="F20:F25" si="3">0.5*INT(E20/0.5)+INT( ((E20-INT(E20/0.5)*0.5)/0.25))*0.5</f>
@@ -4605,7 +4673,7 @@
       </c>
       <c r="B21" s="33">
         <f>Quiz!V21</f>
-        <v>1.4285714285714286</v>
+        <v>1.3</v>
       </c>
       <c r="C21" s="41">
         <f>Exams!B21</f>
@@ -4617,7 +4685,7 @@
       </c>
       <c r="E21" s="33">
         <f t="shared" si="0"/>
-        <v>1.4285714285714286</v>
+        <v>1.3</v>
       </c>
       <c r="F21" s="33">
         <f t="shared" si="3"/>
@@ -4634,7 +4702,7 @@
       </c>
       <c r="B22" s="33">
         <f>Quiz!V22</f>
-        <v>0.94285714285714284</v>
+        <v>0.875</v>
       </c>
       <c r="C22" s="41">
         <f>Exams!B22</f>
@@ -4646,7 +4714,7 @@
       </c>
       <c r="E22" s="33">
         <f t="shared" si="0"/>
-        <v>0.94285714285714284</v>
+        <v>0.875</v>
       </c>
       <c r="F22" s="33">
         <f t="shared" si="3"/>
@@ -4663,7 +4731,7 @@
       </c>
       <c r="B23" s="33">
         <f>Quiz!V23</f>
-        <v>1.6285714285714286</v>
+        <v>1.4750000000000001</v>
       </c>
       <c r="C23" s="41">
         <f>Exams!B23</f>
@@ -4675,7 +4743,7 @@
       </c>
       <c r="E23" s="33">
         <f t="shared" si="0"/>
-        <v>1.6285714285714286</v>
+        <v>1.4750000000000001</v>
       </c>
       <c r="F23" s="33">
         <f t="shared" si="3"/>
@@ -4692,7 +4760,7 @@
       </c>
       <c r="B24" s="33">
         <f>Quiz!V24</f>
-        <v>0.8571428571428571</v>
+        <v>0.9</v>
       </c>
       <c r="C24" s="41">
         <f>Exams!B24</f>
@@ -4704,7 +4772,7 @@
       </c>
       <c r="E24" s="33">
         <f t="shared" si="0"/>
-        <v>0.8571428571428571</v>
+        <v>0.9</v>
       </c>
       <c r="F24" s="33">
         <f t="shared" si="3"/>
@@ -4721,7 +4789,7 @@
       </c>
       <c r="B25" s="33">
         <f>Quiz!V25</f>
-        <v>1.1142857142857143</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="C25" s="41">
         <f>Exams!B25</f>
@@ -4733,7 +4801,7 @@
       </c>
       <c r="E25" s="33">
         <f t="shared" si="0"/>
-        <v>1.1142857142857143</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="F25" s="33">
         <f t="shared" si="3"/>
@@ -4750,7 +4818,7 @@
       </c>
       <c r="B26" s="33">
         <f>Quiz!V26</f>
-        <v>0.5714285714285714</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="C26" s="41">
         <f>Exams!B26</f>
@@ -4762,7 +4830,7 @@
       </c>
       <c r="E26" s="33">
         <f t="shared" si="0"/>
-        <v>0.5714285714285714</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="F26" s="33">
         <f t="shared" ref="F26:F40" si="5">0.5*INT(E26/0.5)+INT( ((E26-INT(E26/0.5)*0.5)/0.25))*0.5</f>
@@ -4779,7 +4847,7 @@
       </c>
       <c r="B27" s="33">
         <f>Quiz!V27</f>
-        <v>0.62857142857142856</v>
+        <v>0.6</v>
       </c>
       <c r="C27" s="41">
         <f>Exams!B27</f>
@@ -4791,7 +4859,7 @@
       </c>
       <c r="E27" s="33">
         <f t="shared" si="0"/>
-        <v>0.62857142857142856</v>
+        <v>0.6</v>
       </c>
       <c r="F27" s="33">
         <f t="shared" si="5"/>
@@ -4808,7 +4876,7 @@
       </c>
       <c r="B28" s="33">
         <f>Quiz!V28</f>
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="C28" s="41">
         <f>Exams!B28</f>
@@ -4820,7 +4888,7 @@
       </c>
       <c r="E28" s="33">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="F28" s="33">
         <f t="shared" si="5"/>
@@ -4837,7 +4905,7 @@
       </c>
       <c r="B29" s="33">
         <f>Quiz!V29</f>
-        <v>0.82857142857142863</v>
+        <v>0.875</v>
       </c>
       <c r="C29" s="41">
         <f>Exams!B29</f>
@@ -4849,7 +4917,7 @@
       </c>
       <c r="E29" s="33">
         <f t="shared" si="0"/>
-        <v>0.82857142857142863</v>
+        <v>0.875</v>
       </c>
       <c r="F29" s="33">
         <f t="shared" si="5"/>
@@ -4866,7 +4934,7 @@
       </c>
       <c r="B30" s="33">
         <f>Quiz!V30</f>
-        <v>0.97142857142857142</v>
+        <v>0.9</v>
       </c>
       <c r="C30" s="41">
         <f>Exams!B30</f>
@@ -4878,7 +4946,7 @@
       </c>
       <c r="E30" s="33">
         <f t="shared" si="0"/>
-        <v>0.97142857142857142</v>
+        <v>0.9</v>
       </c>
       <c r="F30" s="33">
         <f t="shared" si="5"/>
@@ -4895,7 +4963,7 @@
       </c>
       <c r="B31" s="33">
         <f>Quiz!V31</f>
-        <v>0.48571428571428571</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="C31" s="41">
         <f>Exams!B31</f>
@@ -4907,7 +4975,7 @@
       </c>
       <c r="E31" s="33">
         <f t="shared" si="0"/>
-        <v>0.48571428571428571</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="F31" s="33">
         <f t="shared" si="5"/>
@@ -4924,7 +4992,7 @@
       </c>
       <c r="B32" s="33">
         <f>Quiz!V32</f>
-        <v>1.0142857142857142</v>
+        <v>0.9375</v>
       </c>
       <c r="C32" s="41">
         <f>Exams!B32</f>
@@ -4936,7 +5004,7 @@
       </c>
       <c r="E32" s="33">
         <f t="shared" si="0"/>
-        <v>1.0142857142857142</v>
+        <v>0.9375</v>
       </c>
       <c r="F32" s="33">
         <f t="shared" si="5"/>
@@ -4982,7 +5050,7 @@
       </c>
       <c r="B34" s="33">
         <f>Quiz!V34</f>
-        <v>0.34285714285714286</v>
+        <v>0.45</v>
       </c>
       <c r="C34" s="41">
         <f>Exams!B34</f>
@@ -4994,7 +5062,7 @@
       </c>
       <c r="E34" s="33">
         <f t="shared" si="0"/>
-        <v>0.34285714285714286</v>
+        <v>0.45</v>
       </c>
       <c r="F34" s="33">
         <f t="shared" si="5"/>
@@ -5011,7 +5079,7 @@
       </c>
       <c r="B35" s="33">
         <f>Quiz!V35</f>
-        <v>0.9</v>
+        <v>0.9375</v>
       </c>
       <c r="C35" s="41">
         <f>Exams!B35</f>
@@ -5023,7 +5091,7 @@
       </c>
       <c r="E35" s="33">
         <f t="shared" si="0"/>
-        <v>0.9</v>
+        <v>0.9375</v>
       </c>
       <c r="F35" s="33">
         <f t="shared" si="5"/>
@@ -5040,7 +5108,7 @@
       </c>
       <c r="B36" s="33">
         <f>Quiz!V36</f>
-        <v>0.5714285714285714</v>
+        <v>0.65</v>
       </c>
       <c r="C36" s="41">
         <f>Exams!B36</f>
@@ -5052,7 +5120,7 @@
       </c>
       <c r="E36" s="33">
         <f t="shared" si="0"/>
-        <v>0.5714285714285714</v>
+        <v>0.65</v>
       </c>
       <c r="F36" s="33">
         <f t="shared" si="5"/>
@@ -5069,7 +5137,7 @@
       </c>
       <c r="B37" s="33">
         <f>Quiz!V37</f>
-        <v>1.1714285714285715</v>
+        <v>1.175</v>
       </c>
       <c r="C37" s="41">
         <f>Exams!B37</f>
@@ -5081,7 +5149,7 @@
       </c>
       <c r="E37" s="33">
         <f t="shared" si="0"/>
-        <v>1.1714285714285715</v>
+        <v>1.175</v>
       </c>
       <c r="F37" s="33">
         <f t="shared" si="5"/>
@@ -5098,7 +5166,7 @@
       </c>
       <c r="B38" s="33">
         <f>Quiz!V38</f>
-        <v>0.5714285714285714</v>
+        <v>0.65</v>
       </c>
       <c r="C38" s="41">
         <f>Exams!B38</f>
@@ -5110,7 +5178,7 @@
       </c>
       <c r="E38" s="33">
         <f t="shared" si="0"/>
-        <v>0.5714285714285714</v>
+        <v>0.65</v>
       </c>
       <c r="F38" s="33">
         <f t="shared" si="5"/>
@@ -5127,7 +5195,7 @@
       </c>
       <c r="B39" s="33">
         <f>Quiz!V39</f>
-        <v>1.1428571428571428</v>
+        <v>1.05</v>
       </c>
       <c r="C39" s="41">
         <f>Exams!B39</f>
@@ -5139,7 +5207,7 @@
       </c>
       <c r="E39" s="33">
         <f t="shared" si="0"/>
-        <v>1.1428571428571428</v>
+        <v>1.05</v>
       </c>
       <c r="F39" s="33">
         <f t="shared" ref="F39" si="8">0.5*INT(E39/0.5)+INT( ((E39-INT(E39/0.5)*0.5)/0.25))*0.5</f>
@@ -5156,7 +5224,7 @@
       </c>
       <c r="B40" s="33">
         <f>Quiz!V40</f>
-        <v>1.0857142857142856</v>
+        <v>1</v>
       </c>
       <c r="C40" s="41">
         <f>Exams!B40</f>
@@ -5168,7 +5236,7 @@
       </c>
       <c r="E40" s="33">
         <f t="shared" si="0"/>
-        <v>1.0857142857142856</v>
+        <v>1</v>
       </c>
       <c r="F40" s="33">
         <f t="shared" si="5"/>
@@ -5221,7 +5289,7 @@
       </c>
       <c r="B43" s="29">
         <f t="shared" ref="B43:G43" si="10">AVERAGE(B$2:B$40)</f>
-        <v>0.85604395604395622</v>
+        <v>0.82852564102564108</v>
       </c>
       <c r="C43" s="29">
         <f t="shared" si="10"/>
@@ -5233,11 +5301,11 @@
       </c>
       <c r="E43" s="29">
         <f t="shared" si="10"/>
-        <v>0.85604395604395622</v>
+        <v>0.82852564102564108</v>
       </c>
       <c r="F43" s="29">
         <f t="shared" si="10"/>
-        <v>0.85897435897435892</v>
+        <v>0.84615384615384615</v>
       </c>
       <c r="G43" s="29">
         <f t="shared" si="10"/>
@@ -5250,7 +5318,7 @@
       </c>
       <c r="B44" s="29">
         <f t="shared" ref="B44:G44" si="11">STDEV(B$2:B$40)</f>
-        <v>0.37196873122260321</v>
+        <v>0.3346732095940349</v>
       </c>
       <c r="C44" s="29">
         <f t="shared" si="11"/>
@@ -5262,11 +5330,11 @@
       </c>
       <c r="E44" s="29">
         <f t="shared" si="11"/>
-        <v>0.37196873122260321</v>
+        <v>0.3346732095940349</v>
       </c>
       <c r="F44" s="29">
         <f t="shared" si="11"/>
-        <v>0.39650973885826146</v>
+        <v>0.3655177681951956</v>
       </c>
       <c r="G44" s="29">
         <f t="shared" si="11"/>
@@ -5279,7 +5347,7 @@
       </c>
       <c r="B45" s="29">
         <f t="shared" ref="B45:G45" si="12">MEDIAN(B$2:B$40)</f>
-        <v>0.88571428571428568</v>
+        <v>0.85</v>
       </c>
       <c r="C45" s="29">
         <f t="shared" si="12"/>
@@ -5291,7 +5359,7 @@
       </c>
       <c r="E45" s="29">
         <f t="shared" si="12"/>
-        <v>0.88571428571428568</v>
+        <v>0.85</v>
       </c>
       <c r="F45" s="29">
         <f t="shared" si="12"/>

--- a/phy112/Grades/grades_report_2026.xlsx
+++ b/phy112/Grades/grades_report_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ptohos/Documents/MyCourses/FYS112/2026/Grades/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9A2C49B-7897-6242-915D-BFC339752EC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28D028F9-017D-384D-BA6D-59E415A2E86D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="540" yWindow="3080" windowWidth="32920" windowHeight="19260" tabRatio="334" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1640" yWindow="680" windowWidth="32920" windowHeight="19260" tabRatio="334" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Quiz" sheetId="1" r:id="rId1"/>
@@ -1017,7 +1017,9 @@
       <c r="J2" s="18">
         <v>12</v>
       </c>
-      <c r="K2" s="18"/>
+      <c r="K2" s="18">
+        <v>20</v>
+      </c>
       <c r="L2" s="18"/>
       <c r="M2" s="18"/>
       <c r="N2" s="18"/>
@@ -1030,7 +1032,7 @@
       <c r="U2" s="18"/>
       <c r="V2" s="33">
         <f t="shared" ref="V2:V39" si="0">$V$42 * ( (SUM(B2:U2))/((SUM($B$46:$U$46))*$B$42) )</f>
-        <v>0.85</v>
+        <v>0.97777777777777775</v>
       </c>
       <c r="W2"/>
     </row>
@@ -1059,7 +1061,9 @@
       </c>
       <c r="I3" s="18"/>
       <c r="J3" s="18"/>
-      <c r="K3" s="18"/>
+      <c r="K3" s="18">
+        <v>4</v>
+      </c>
       <c r="L3" s="18"/>
       <c r="M3" s="18"/>
       <c r="N3" s="18"/>
@@ -1072,7 +1076,7 @@
       <c r="U3" s="18"/>
       <c r="V3" s="33">
         <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
+        <v>0.53333333333333333</v>
       </c>
       <c r="W3"/>
     </row>
@@ -1105,7 +1109,9 @@
       <c r="J4" s="18">
         <v>12</v>
       </c>
-      <c r="K4" s="18"/>
+      <c r="K4" s="18">
+        <v>20</v>
+      </c>
       <c r="L4" s="18"/>
       <c r="M4" s="18"/>
       <c r="N4" s="18"/>
@@ -1118,7 +1124,7 @@
       <c r="U4" s="18"/>
       <c r="V4" s="33">
         <f t="shared" si="0"/>
-        <v>0.98750000000000004</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="W4"/>
     </row>
@@ -1149,7 +1155,9 @@
       <c r="J5" s="18">
         <v>12</v>
       </c>
-      <c r="K5" s="18"/>
+      <c r="K5" s="18">
+        <v>20</v>
+      </c>
       <c r="L5" s="18"/>
       <c r="M5" s="18"/>
       <c r="N5" s="18"/>
@@ -1162,7 +1170,7 @@
       <c r="U5" s="18"/>
       <c r="V5" s="33">
         <f t="shared" si="0"/>
-        <v>0.45</v>
+        <v>0.62222222222222223</v>
       </c>
       <c r="W5"/>
     </row>
@@ -1195,7 +1203,9 @@
       <c r="J6" s="18">
         <v>4</v>
       </c>
-      <c r="K6" s="18"/>
+      <c r="K6" s="18">
+        <v>12</v>
+      </c>
       <c r="L6" s="18"/>
       <c r="M6" s="18"/>
       <c r="N6" s="18"/>
@@ -1208,7 +1218,7 @@
       <c r="U6" s="18"/>
       <c r="V6" s="33">
         <f t="shared" si="0"/>
-        <v>0.85</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="W6"/>
     </row>
@@ -1241,7 +1251,9 @@
       <c r="J7" s="18">
         <v>12</v>
       </c>
-      <c r="K7" s="18"/>
+      <c r="K7" s="18">
+        <v>4</v>
+      </c>
       <c r="L7" s="18"/>
       <c r="M7" s="18"/>
       <c r="N7" s="18"/>
@@ -1254,7 +1266,7 @@
       <c r="U7" s="18"/>
       <c r="V7" s="33">
         <f t="shared" si="0"/>
-        <v>1.35</v>
+        <v>1.2444444444444445</v>
       </c>
       <c r="W7"/>
     </row>
@@ -1285,7 +1297,9 @@
         <v>4</v>
       </c>
       <c r="J8" s="18"/>
-      <c r="K8" s="18"/>
+      <c r="K8" s="18">
+        <v>20</v>
+      </c>
       <c r="L8" s="18"/>
       <c r="M8" s="18"/>
       <c r="N8" s="18"/>
@@ -1298,7 +1312,7 @@
       <c r="U8" s="18"/>
       <c r="V8" s="33">
         <f t="shared" si="0"/>
-        <v>0.625</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="W8"/>
     </row>
@@ -1327,7 +1341,9 @@
       <c r="J9" s="18">
         <v>4</v>
       </c>
-      <c r="K9" s="18"/>
+      <c r="K9" s="18">
+        <v>20</v>
+      </c>
       <c r="L9" s="18"/>
       <c r="M9" s="18"/>
       <c r="N9" s="18"/>
@@ -1340,7 +1356,7 @@
       <c r="U9" s="18"/>
       <c r="V9" s="33">
         <f t="shared" si="0"/>
-        <v>0.7</v>
+        <v>0.84444444444444444</v>
       </c>
       <c r="W9"/>
     </row>
@@ -1382,7 +1398,7 @@
       <c r="U10" s="18"/>
       <c r="V10" s="33">
         <f t="shared" si="0"/>
-        <v>0.85</v>
+        <v>0.75555555555555554</v>
       </c>
       <c r="W10"/>
     </row>
@@ -1413,7 +1429,9 @@
       <c r="J11" s="18">
         <v>4</v>
       </c>
-      <c r="K11" s="18"/>
+      <c r="K11" s="18">
+        <v>20</v>
+      </c>
       <c r="L11" s="18"/>
       <c r="M11" s="18"/>
       <c r="N11" s="18"/>
@@ -1426,7 +1444,7 @@
       <c r="U11" s="18"/>
       <c r="V11" s="33">
         <f t="shared" si="0"/>
-        <v>0.65</v>
+        <v>0.8</v>
       </c>
       <c r="W11"/>
     </row>
@@ -1459,7 +1477,9 @@
       <c r="J12" s="18">
         <v>4</v>
       </c>
-      <c r="K12" s="18"/>
+      <c r="K12" s="18">
+        <v>4</v>
+      </c>
       <c r="L12" s="18"/>
       <c r="M12" s="18"/>
       <c r="N12" s="18"/>
@@ -1472,7 +1492,7 @@
       <c r="U12" s="18"/>
       <c r="V12" s="33">
         <f t="shared" si="0"/>
-        <v>0.9</v>
+        <v>0.84444444444444444</v>
       </c>
       <c r="W12"/>
     </row>
@@ -1505,7 +1525,9 @@
       <c r="J13" s="18">
         <v>4</v>
       </c>
-      <c r="K13" s="18"/>
+      <c r="K13" s="18">
+        <v>4</v>
+      </c>
       <c r="L13" s="18"/>
       <c r="M13" s="18"/>
       <c r="N13" s="18"/>
@@ -1518,7 +1540,7 @@
       <c r="U13" s="18"/>
       <c r="V13" s="33">
         <f t="shared" si="0"/>
-        <v>0.82499999999999996</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="W13"/>
     </row>
@@ -1551,7 +1573,9 @@
       <c r="J14" s="18">
         <v>12</v>
       </c>
-      <c r="K14" s="18"/>
+      <c r="K14" s="18">
+        <v>4</v>
+      </c>
       <c r="L14" s="18"/>
       <c r="M14" s="18"/>
       <c r="N14" s="18"/>
@@ -1564,7 +1588,7 @@
       <c r="U14" s="18"/>
       <c r="V14" s="33">
         <f t="shared" si="0"/>
-        <v>1.125</v>
+        <v>1.0444444444444445</v>
       </c>
     </row>
     <row r="15" spans="1:23" ht="29" customHeight="1" x14ac:dyDescent="0.15">
@@ -1596,7 +1620,9 @@
       <c r="J15" s="18">
         <v>4</v>
       </c>
-      <c r="K15" s="18"/>
+      <c r="K15" s="18">
+        <v>20</v>
+      </c>
       <c r="L15" s="18"/>
       <c r="M15" s="18"/>
       <c r="N15" s="18"/>
@@ -1609,7 +1635,7 @@
       <c r="U15" s="18"/>
       <c r="V15" s="33">
         <f t="shared" si="0"/>
-        <v>1.675</v>
+        <v>1.711111111111111</v>
       </c>
       <c r="W15"/>
     </row>
@@ -1642,7 +1668,9 @@
       <c r="J16" s="18">
         <v>4</v>
       </c>
-      <c r="K16" s="18"/>
+      <c r="K16" s="18">
+        <v>20</v>
+      </c>
       <c r="L16" s="18"/>
       <c r="M16" s="18"/>
       <c r="N16" s="18"/>
@@ -1655,7 +1683,7 @@
       <c r="U16" s="18"/>
       <c r="V16" s="33">
         <f t="shared" si="0"/>
-        <v>0.82499999999999996</v>
+        <v>0.9555555555555556</v>
       </c>
       <c r="W16"/>
     </row>
@@ -1714,7 +1742,9 @@
       <c r="J18" s="18">
         <v>12</v>
       </c>
-      <c r="K18" s="18"/>
+      <c r="K18" s="18">
+        <v>20</v>
+      </c>
       <c r="L18" s="18"/>
       <c r="M18" s="18"/>
       <c r="N18" s="18"/>
@@ -1727,7 +1757,7 @@
       <c r="U18" s="18"/>
       <c r="V18" s="33">
         <f t="shared" si="0"/>
-        <v>0.7</v>
+        <v>0.84444444444444444</v>
       </c>
       <c r="W18"/>
     </row>
@@ -1760,7 +1790,9 @@
       <c r="J19" s="18">
         <v>12</v>
       </c>
-      <c r="K19" s="18"/>
+      <c r="K19" s="18">
+        <v>20</v>
+      </c>
       <c r="L19" s="18"/>
       <c r="M19" s="18"/>
       <c r="N19" s="18"/>
@@ -1773,7 +1805,7 @@
       <c r="U19" s="18"/>
       <c r="V19" s="33">
         <f t="shared" si="0"/>
-        <v>0.97499999999999998</v>
+        <v>1.0888888888888888</v>
       </c>
       <c r="W19"/>
     </row>
@@ -1804,7 +1836,9 @@
       <c r="J20" s="18">
         <v>4</v>
       </c>
-      <c r="K20" s="18"/>
+      <c r="K20" s="18">
+        <v>20</v>
+      </c>
       <c r="L20" s="18"/>
       <c r="M20" s="18"/>
       <c r="N20" s="18"/>
@@ -1817,7 +1851,7 @@
       <c r="U20" s="18"/>
       <c r="V20" s="33">
         <f t="shared" si="0"/>
-        <v>0.9</v>
+        <v>1.0222222222222221</v>
       </c>
       <c r="W20"/>
     </row>
@@ -1863,7 +1897,7 @@
       <c r="U21" s="18"/>
       <c r="V21" s="33">
         <f t="shared" si="0"/>
-        <v>1.3</v>
+        <v>1.1555555555555554</v>
       </c>
       <c r="W21"/>
     </row>
@@ -1894,7 +1928,9 @@
       <c r="J22" s="18">
         <v>4</v>
       </c>
-      <c r="K22" s="18"/>
+      <c r="K22" s="18">
+        <v>4</v>
+      </c>
       <c r="L22" s="18"/>
       <c r="M22" s="18"/>
       <c r="N22" s="18"/>
@@ -1907,7 +1943,7 @@
       <c r="U22" s="18"/>
       <c r="V22" s="33">
         <f t="shared" si="0"/>
-        <v>0.875</v>
+        <v>0.82222222222222219</v>
       </c>
       <c r="W22"/>
     </row>
@@ -1940,7 +1976,9 @@
       <c r="J23" s="18">
         <v>4</v>
       </c>
-      <c r="K23" s="18"/>
+      <c r="K23" s="18">
+        <v>20</v>
+      </c>
       <c r="L23" s="18"/>
       <c r="M23" s="18"/>
       <c r="N23" s="18"/>
@@ -1953,7 +1991,7 @@
       <c r="U23" s="18"/>
       <c r="V23" s="33">
         <f t="shared" si="0"/>
-        <v>1.4750000000000001</v>
+        <v>1.5333333333333334</v>
       </c>
       <c r="W23"/>
     </row>
@@ -1984,7 +2022,9 @@
       <c r="J24" s="18">
         <v>12</v>
       </c>
-      <c r="K24" s="18"/>
+      <c r="K24" s="18">
+        <v>20</v>
+      </c>
       <c r="L24" s="18"/>
       <c r="M24" s="18"/>
       <c r="N24" s="18"/>
@@ -1997,7 +2037,7 @@
       <c r="U24" s="18"/>
       <c r="V24" s="33">
         <f t="shared" si="0"/>
-        <v>0.9</v>
+        <v>1.0222222222222221</v>
       </c>
       <c r="W24"/>
     </row>
@@ -2026,7 +2066,9 @@
       <c r="J25" s="18">
         <v>4</v>
       </c>
-      <c r="K25" s="18"/>
+      <c r="K25" s="18">
+        <v>20</v>
+      </c>
       <c r="L25" s="18"/>
       <c r="M25" s="18"/>
       <c r="N25" s="18"/>
@@ -2039,7 +2081,7 @@
       <c r="U25" s="18"/>
       <c r="V25" s="33">
         <f t="shared" si="0"/>
-        <v>1.0249999999999999</v>
+        <v>1.1333333333333333</v>
       </c>
       <c r="W25"/>
     </row>
@@ -2072,7 +2114,9 @@
       <c r="J26" s="18">
         <v>4</v>
       </c>
-      <c r="K26" s="18"/>
+      <c r="K26" s="18">
+        <v>4</v>
+      </c>
       <c r="L26" s="18"/>
       <c r="M26" s="18"/>
       <c r="N26" s="18"/>
@@ -2085,7 +2129,7 @@
       <c r="U26" s="18"/>
       <c r="V26" s="33">
         <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
+        <v>0.53333333333333333</v>
       </c>
       <c r="W26"/>
     </row>
@@ -2114,7 +2158,9 @@
       <c r="J27" s="18">
         <v>4</v>
       </c>
-      <c r="K27" s="18"/>
+      <c r="K27" s="18">
+        <v>20</v>
+      </c>
       <c r="L27" s="18"/>
       <c r="M27" s="18"/>
       <c r="N27" s="18"/>
@@ -2127,7 +2173,7 @@
       <c r="U27" s="18"/>
       <c r="V27" s="33">
         <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.75555555555555554</v>
       </c>
       <c r="W27"/>
     </row>
@@ -2158,7 +2204,9 @@
       <c r="J28" s="18">
         <v>4</v>
       </c>
-      <c r="K28" s="18"/>
+      <c r="K28" s="18">
+        <v>20</v>
+      </c>
       <c r="L28" s="18"/>
       <c r="M28" s="18"/>
       <c r="N28" s="18"/>
@@ -2171,7 +2219,7 @@
       <c r="U28" s="18"/>
       <c r="V28" s="33">
         <f t="shared" si="0"/>
-        <v>0.75</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="W28"/>
     </row>
@@ -2204,7 +2252,9 @@
       <c r="J29" s="18">
         <v>12</v>
       </c>
-      <c r="K29" s="18"/>
+      <c r="K29" s="18">
+        <v>20</v>
+      </c>
       <c r="L29" s="18"/>
       <c r="M29" s="18"/>
       <c r="N29" s="18"/>
@@ -2217,7 +2267,7 @@
       <c r="U29" s="18"/>
       <c r="V29" s="33">
         <f t="shared" si="0"/>
-        <v>0.875</v>
+        <v>1</v>
       </c>
       <c r="W29"/>
     </row>
@@ -2250,7 +2300,9 @@
       <c r="J30" s="18">
         <v>4</v>
       </c>
-      <c r="K30" s="18"/>
+      <c r="K30" s="18">
+        <v>12</v>
+      </c>
       <c r="L30" s="18"/>
       <c r="M30" s="18"/>
       <c r="N30" s="18"/>
@@ -2263,7 +2315,7 @@
       <c r="U30" s="18"/>
       <c r="V30" s="33">
         <f t="shared" si="0"/>
-        <v>0.9</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="W30"/>
     </row>
@@ -2292,7 +2344,9 @@
         <v>4</v>
       </c>
       <c r="J31" s="18"/>
-      <c r="K31" s="18"/>
+      <c r="K31" s="18">
+        <v>20</v>
+      </c>
       <c r="L31" s="18"/>
       <c r="M31" s="18"/>
       <c r="N31" s="18"/>
@@ -2305,7 +2359,7 @@
       <c r="U31" s="18"/>
       <c r="V31" s="33">
         <f t="shared" si="0"/>
-        <v>0.42499999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="W31"/>
     </row>
@@ -2338,7 +2392,9 @@
       <c r="J32" s="18">
         <v>4</v>
       </c>
-      <c r="K32" s="18"/>
+      <c r="K32" s="18">
+        <v>4</v>
+      </c>
       <c r="L32" s="18"/>
       <c r="M32" s="18"/>
       <c r="N32" s="18"/>
@@ -2351,7 +2407,7 @@
       <c r="U32" s="18"/>
       <c r="V32" s="33">
         <f t="shared" si="0"/>
-        <v>0.9375</v>
+        <v>0.87777777777777777</v>
       </c>
       <c r="W32"/>
     </row>
@@ -2408,7 +2464,9 @@
       <c r="J34" s="18">
         <v>12</v>
       </c>
-      <c r="K34" s="18"/>
+      <c r="K34" s="18">
+        <v>4</v>
+      </c>
       <c r="L34" s="18"/>
       <c r="M34" s="18"/>
       <c r="N34" s="18"/>
@@ -2421,7 +2479,7 @@
       <c r="U34" s="18"/>
       <c r="V34" s="33">
         <f t="shared" si="0"/>
-        <v>0.45</v>
+        <v>0.44444444444444442</v>
       </c>
       <c r="W34"/>
     </row>
@@ -2454,7 +2512,9 @@
       <c r="J35" s="18">
         <v>12</v>
       </c>
-      <c r="K35" s="18"/>
+      <c r="K35" s="18">
+        <v>4</v>
+      </c>
       <c r="L35" s="18"/>
       <c r="M35" s="18"/>
       <c r="N35" s="18"/>
@@ -2467,7 +2527,7 @@
       <c r="U35" s="18"/>
       <c r="V35" s="33">
         <f t="shared" si="0"/>
-        <v>0.9375</v>
+        <v>0.87777777777777777</v>
       </c>
       <c r="W35"/>
     </row>
@@ -2507,7 +2567,7 @@
       <c r="U36" s="18"/>
       <c r="V36" s="33">
         <f t="shared" si="0"/>
-        <v>0.65</v>
+        <v>0.57777777777777772</v>
       </c>
       <c r="W36"/>
     </row>
@@ -2540,7 +2600,9 @@
       <c r="J37" s="18">
         <v>12</v>
       </c>
-      <c r="K37" s="18"/>
+      <c r="K37" s="18">
+        <v>4</v>
+      </c>
       <c r="L37" s="18"/>
       <c r="M37" s="18"/>
       <c r="N37" s="18"/>
@@ -2553,7 +2615,7 @@
       <c r="U37" s="18"/>
       <c r="V37" s="33">
         <f t="shared" si="0"/>
-        <v>1.175</v>
+        <v>1.0888888888888888</v>
       </c>
       <c r="W37"/>
     </row>
@@ -2580,7 +2642,9 @@
       <c r="J38" s="18">
         <v>12</v>
       </c>
-      <c r="K38" s="18"/>
+      <c r="K38" s="18">
+        <v>4</v>
+      </c>
       <c r="L38" s="18"/>
       <c r="M38" s="18"/>
       <c r="N38" s="18"/>
@@ -2593,7 +2657,7 @@
       <c r="U38" s="18"/>
       <c r="V38" s="33">
         <f t="shared" si="0"/>
-        <v>0.65</v>
+        <v>0.62222222222222223</v>
       </c>
       <c r="W38"/>
     </row>
@@ -2639,7 +2703,7 @@
       <c r="U39" s="18"/>
       <c r="V39" s="33">
         <f t="shared" si="0"/>
-        <v>1.05</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="W39"/>
     </row>
@@ -2683,7 +2747,7 @@
       <c r="U40" s="18"/>
       <c r="V40" s="33">
         <f t="shared" ref="V40" si="1">$V$42 * ( (SUM(B40:U40))/((SUM($B$46:$U$46))*$B$42) )</f>
-        <v>1</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="W40"/>
     </row>
@@ -2821,9 +2885,9 @@
         <f t="shared" si="2"/>
         <v>7.3939393939393936</v>
       </c>
-      <c r="K43" s="29" t="e">
+      <c r="K43" s="29">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+        <v>13.5</v>
       </c>
       <c r="L43" s="29" t="e">
         <f t="shared" si="2"/>
@@ -2867,7 +2931,7 @@
       </c>
       <c r="V43" s="29">
         <f t="shared" si="2"/>
-        <v>0.82401315789473673</v>
+        <v>0.85877192982456163</v>
       </c>
       <c r="W43"/>
     </row>
@@ -2911,9 +2975,9 @@
         <f t="shared" si="3"/>
         <v>4.0151229272853062</v>
       </c>
-      <c r="K44" s="29" t="e">
+      <c r="K44" s="29">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
+        <v>7.7209392709570279</v>
       </c>
       <c r="L44" s="29" t="e">
         <f t="shared" si="3"/>
@@ -2957,7 +3021,7 @@
       </c>
       <c r="V44" s="29">
         <f t="shared" si="3"/>
-        <v>0.33796116614515131</v>
+        <v>0.32710811518099425</v>
       </c>
       <c r="W44"/>
     </row>
@@ -3001,9 +3065,9 @@
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="K45" s="29" t="e">
+      <c r="K45" s="29">
         <f t="shared" si="4"/>
-        <v>#NUM!</v>
+        <v>20</v>
       </c>
       <c r="L45" s="29" t="e">
         <f t="shared" si="4"/>
@@ -3047,7 +3111,7 @@
       </c>
       <c r="V45" s="29">
         <f t="shared" si="4"/>
-        <v>0.85</v>
+        <v>0.87777777777777777</v>
       </c>
       <c r="W45"/>
     </row>
@@ -3093,7 +3157,7 @@
       </c>
       <c r="K46" s="32">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" s="32">
         <f t="shared" si="5"/>
@@ -4121,7 +4185,7 @@
       </c>
       <c r="B2" s="33">
         <f>Quiz!V2</f>
-        <v>0.85</v>
+        <v>0.97777777777777775</v>
       </c>
       <c r="C2" s="41">
         <f>Exams!B2</f>
@@ -4133,7 +4197,7 @@
       </c>
       <c r="E2" s="33">
         <f>$B2+($C2/$C$42)*3.5+($D2/$D$42)*4.5</f>
-        <v>0.85</v>
+        <v>0.97777777777777775</v>
       </c>
       <c r="F2" s="33">
         <f>0.5*INT(E2/0.5)+INT( ((E2-INT(E2/0.5)*0.5)/0.25))*0.5</f>
@@ -4151,7 +4215,7 @@
       </c>
       <c r="B3" s="33">
         <f>Quiz!V3</f>
-        <v>0.55000000000000004</v>
+        <v>0.53333333333333333</v>
       </c>
       <c r="C3" s="41">
         <f>Exams!B3</f>
@@ -4163,7 +4227,7 @@
       </c>
       <c r="E3" s="33">
         <f t="shared" ref="E3:E40" si="0">$B3+($C3/$C$42)*3.5+($D3/$D$42)*4.5</f>
-        <v>0.55000000000000004</v>
+        <v>0.53333333333333333</v>
       </c>
       <c r="F3" s="33">
         <f t="shared" ref="F3:F19" si="1">0.5*INT(E3/0.5)+INT( ((E3-INT(E3/0.5)*0.5)/0.25))*0.5</f>
@@ -4180,7 +4244,7 @@
       </c>
       <c r="B4" s="33">
         <f>Quiz!V4</f>
-        <v>0.98750000000000004</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="C4" s="41">
         <f>Exams!B4</f>
@@ -4192,7 +4256,7 @@
       </c>
       <c r="E4" s="33">
         <f t="shared" si="0"/>
-        <v>0.98750000000000004</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="F4" s="33">
         <f t="shared" si="1"/>
@@ -4209,7 +4273,7 @@
       </c>
       <c r="B5" s="33">
         <f>Quiz!V5</f>
-        <v>0.45</v>
+        <v>0.62222222222222223</v>
       </c>
       <c r="C5" s="41">
         <f>Exams!B5</f>
@@ -4221,7 +4285,7 @@
       </c>
       <c r="E5" s="33">
         <f t="shared" si="0"/>
-        <v>0.45</v>
+        <v>0.62222222222222223</v>
       </c>
       <c r="F5" s="33">
         <f t="shared" si="1"/>
@@ -4238,7 +4302,7 @@
       </c>
       <c r="B6" s="33">
         <f>Quiz!V6</f>
-        <v>0.85</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="C6" s="41">
         <f>Exams!B6</f>
@@ -4250,7 +4314,7 @@
       </c>
       <c r="E6" s="33">
         <f t="shared" si="0"/>
-        <v>0.85</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="F6" s="33">
         <f t="shared" si="1"/>
@@ -4267,7 +4331,7 @@
       </c>
       <c r="B7" s="33">
         <f>Quiz!V7</f>
-        <v>1.35</v>
+        <v>1.2444444444444445</v>
       </c>
       <c r="C7" s="41">
         <f>Exams!B7</f>
@@ -4279,11 +4343,11 @@
       </c>
       <c r="E7" s="33">
         <f t="shared" si="0"/>
-        <v>1.35</v>
+        <v>1.2444444444444445</v>
       </c>
       <c r="F7" s="33">
         <f t="shared" si="1"/>
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G7" s="47">
         <f t="shared" si="2"/>
@@ -4296,7 +4360,7 @@
       </c>
       <c r="B8" s="33">
         <f>Quiz!V8</f>
-        <v>0.625</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="C8" s="41">
         <f>Exams!B8</f>
@@ -4308,11 +4372,11 @@
       </c>
       <c r="E8" s="33">
         <f t="shared" si="0"/>
-        <v>0.625</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="F8" s="33">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G8" s="47">
         <f t="shared" si="2"/>
@@ -4325,7 +4389,7 @@
       </c>
       <c r="B9" s="33">
         <f>Quiz!V9</f>
-        <v>0.7</v>
+        <v>0.84444444444444444</v>
       </c>
       <c r="C9" s="41">
         <f>Exams!B9</f>
@@ -4337,11 +4401,11 @@
       </c>
       <c r="E9" s="33">
         <f t="shared" si="0"/>
-        <v>0.7</v>
+        <v>0.84444444444444444</v>
       </c>
       <c r="F9" s="33">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G9" s="47">
         <f t="shared" si="2"/>
@@ -4354,7 +4418,7 @@
       </c>
       <c r="B10" s="33">
         <f>Quiz!V10</f>
-        <v>0.85</v>
+        <v>0.75555555555555554</v>
       </c>
       <c r="C10" s="41">
         <f>Exams!B10</f>
@@ -4366,7 +4430,7 @@
       </c>
       <c r="E10" s="33">
         <f t="shared" si="0"/>
-        <v>0.85</v>
+        <v>0.75555555555555554</v>
       </c>
       <c r="F10" s="33">
         <f t="shared" si="1"/>
@@ -4383,7 +4447,7 @@
       </c>
       <c r="B11" s="33">
         <f>Quiz!V11</f>
-        <v>0.65</v>
+        <v>0.8</v>
       </c>
       <c r="C11" s="41">
         <f>Exams!B11</f>
@@ -4395,11 +4459,11 @@
       </c>
       <c r="E11" s="33">
         <f t="shared" si="0"/>
-        <v>0.65</v>
+        <v>0.8</v>
       </c>
       <c r="F11" s="33">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G11" s="47">
         <f t="shared" si="2"/>
@@ -4412,7 +4476,7 @@
       </c>
       <c r="B12" s="33">
         <f>Quiz!V12</f>
-        <v>0.9</v>
+        <v>0.84444444444444444</v>
       </c>
       <c r="C12" s="41">
         <f>Exams!B12</f>
@@ -4424,7 +4488,7 @@
       </c>
       <c r="E12" s="33">
         <f t="shared" si="0"/>
-        <v>0.9</v>
+        <v>0.84444444444444444</v>
       </c>
       <c r="F12" s="33">
         <f t="shared" si="1"/>
@@ -4441,7 +4505,7 @@
       </c>
       <c r="B13" s="33">
         <f>Quiz!V13</f>
-        <v>0.82499999999999996</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="C13" s="41">
         <f>Exams!B13</f>
@@ -4453,7 +4517,7 @@
       </c>
       <c r="E13" s="33">
         <f t="shared" si="0"/>
-        <v>0.82499999999999996</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="F13" s="33">
         <f t="shared" si="1"/>
@@ -4470,7 +4534,7 @@
       </c>
       <c r="B14" s="33">
         <f>Quiz!V14</f>
-        <v>1.125</v>
+        <v>1.0444444444444445</v>
       </c>
       <c r="C14" s="41">
         <f>Exams!B14</f>
@@ -4482,7 +4546,7 @@
       </c>
       <c r="E14" s="33">
         <f t="shared" si="0"/>
-        <v>1.125</v>
+        <v>1.0444444444444445</v>
       </c>
       <c r="F14" s="33">
         <f t="shared" si="1"/>
@@ -4499,7 +4563,7 @@
       </c>
       <c r="B15" s="33">
         <f>Quiz!V15</f>
-        <v>1.675</v>
+        <v>1.711111111111111</v>
       </c>
       <c r="C15" s="41">
         <f>Exams!B15</f>
@@ -4511,7 +4575,7 @@
       </c>
       <c r="E15" s="33">
         <f t="shared" si="0"/>
-        <v>1.675</v>
+        <v>1.711111111111111</v>
       </c>
       <c r="F15" s="33">
         <f t="shared" si="1"/>
@@ -4528,7 +4592,7 @@
       </c>
       <c r="B16" s="33">
         <f>Quiz!V16</f>
-        <v>0.82499999999999996</v>
+        <v>0.9555555555555556</v>
       </c>
       <c r="C16" s="41">
         <f>Exams!B16</f>
@@ -4540,7 +4604,7 @@
       </c>
       <c r="E16" s="33">
         <f t="shared" si="0"/>
-        <v>0.82499999999999996</v>
+        <v>0.9555555555555556</v>
       </c>
       <c r="F16" s="33">
         <f t="shared" si="1"/>
@@ -4586,7 +4650,7 @@
       </c>
       <c r="B18" s="33">
         <f>Quiz!V18</f>
-        <v>0.7</v>
+        <v>0.84444444444444444</v>
       </c>
       <c r="C18" s="41">
         <f>Exams!B18</f>
@@ -4598,11 +4662,11 @@
       </c>
       <c r="E18" s="33">
         <f t="shared" si="0"/>
-        <v>0.7</v>
+        <v>0.84444444444444444</v>
       </c>
       <c r="F18" s="33">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G18" s="47">
         <f t="shared" si="2"/>
@@ -4615,7 +4679,7 @@
       </c>
       <c r="B19" s="33">
         <f>Quiz!V19</f>
-        <v>0.97499999999999998</v>
+        <v>1.0888888888888888</v>
       </c>
       <c r="C19" s="41">
         <f>Exams!B19</f>
@@ -4627,7 +4691,7 @@
       </c>
       <c r="E19" s="33">
         <f t="shared" si="0"/>
-        <v>0.97499999999999998</v>
+        <v>1.0888888888888888</v>
       </c>
       <c r="F19" s="33">
         <f t="shared" si="1"/>
@@ -4644,7 +4708,7 @@
       </c>
       <c r="B20" s="33">
         <f>Quiz!V20</f>
-        <v>0.9</v>
+        <v>1.0222222222222221</v>
       </c>
       <c r="C20" s="41">
         <f>Exams!B20</f>
@@ -4656,7 +4720,7 @@
       </c>
       <c r="E20" s="33">
         <f t="shared" si="0"/>
-        <v>0.9</v>
+        <v>1.0222222222222221</v>
       </c>
       <c r="F20" s="33">
         <f t="shared" ref="F20:F25" si="3">0.5*INT(E20/0.5)+INT( ((E20-INT(E20/0.5)*0.5)/0.25))*0.5</f>
@@ -4673,7 +4737,7 @@
       </c>
       <c r="B21" s="33">
         <f>Quiz!V21</f>
-        <v>1.3</v>
+        <v>1.1555555555555554</v>
       </c>
       <c r="C21" s="41">
         <f>Exams!B21</f>
@@ -4685,11 +4749,11 @@
       </c>
       <c r="E21" s="33">
         <f t="shared" si="0"/>
-        <v>1.3</v>
+        <v>1.1555555555555554</v>
       </c>
       <c r="F21" s="33">
         <f t="shared" si="3"/>
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G21" s="47">
         <f t="shared" si="4"/>
@@ -4702,7 +4766,7 @@
       </c>
       <c r="B22" s="33">
         <f>Quiz!V22</f>
-        <v>0.875</v>
+        <v>0.82222222222222219</v>
       </c>
       <c r="C22" s="41">
         <f>Exams!B22</f>
@@ -4714,7 +4778,7 @@
       </c>
       <c r="E22" s="33">
         <f t="shared" si="0"/>
-        <v>0.875</v>
+        <v>0.82222222222222219</v>
       </c>
       <c r="F22" s="33">
         <f t="shared" si="3"/>
@@ -4731,7 +4795,7 @@
       </c>
       <c r="B23" s="33">
         <f>Quiz!V23</f>
-        <v>1.4750000000000001</v>
+        <v>1.5333333333333334</v>
       </c>
       <c r="C23" s="41">
         <f>Exams!B23</f>
@@ -4743,7 +4807,7 @@
       </c>
       <c r="E23" s="33">
         <f t="shared" si="0"/>
-        <v>1.4750000000000001</v>
+        <v>1.5333333333333334</v>
       </c>
       <c r="F23" s="33">
         <f t="shared" si="3"/>
@@ -4760,7 +4824,7 @@
       </c>
       <c r="B24" s="33">
         <f>Quiz!V24</f>
-        <v>0.9</v>
+        <v>1.0222222222222221</v>
       </c>
       <c r="C24" s="41">
         <f>Exams!B24</f>
@@ -4772,7 +4836,7 @@
       </c>
       <c r="E24" s="33">
         <f t="shared" si="0"/>
-        <v>0.9</v>
+        <v>1.0222222222222221</v>
       </c>
       <c r="F24" s="33">
         <f t="shared" si="3"/>
@@ -4789,7 +4853,7 @@
       </c>
       <c r="B25" s="33">
         <f>Quiz!V25</f>
-        <v>1.0249999999999999</v>
+        <v>1.1333333333333333</v>
       </c>
       <c r="C25" s="41">
         <f>Exams!B25</f>
@@ -4801,7 +4865,7 @@
       </c>
       <c r="E25" s="33">
         <f t="shared" si="0"/>
-        <v>1.0249999999999999</v>
+        <v>1.1333333333333333</v>
       </c>
       <c r="F25" s="33">
         <f t="shared" si="3"/>
@@ -4818,7 +4882,7 @@
       </c>
       <c r="B26" s="33">
         <f>Quiz!V26</f>
-        <v>0.55000000000000004</v>
+        <v>0.53333333333333333</v>
       </c>
       <c r="C26" s="41">
         <f>Exams!B26</f>
@@ -4830,7 +4894,7 @@
       </c>
       <c r="E26" s="33">
         <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
+        <v>0.53333333333333333</v>
       </c>
       <c r="F26" s="33">
         <f t="shared" ref="F26:F40" si="5">0.5*INT(E26/0.5)+INT( ((E26-INT(E26/0.5)*0.5)/0.25))*0.5</f>
@@ -4847,7 +4911,7 @@
       </c>
       <c r="B27" s="33">
         <f>Quiz!V27</f>
-        <v>0.6</v>
+        <v>0.75555555555555554</v>
       </c>
       <c r="C27" s="41">
         <f>Exams!B27</f>
@@ -4859,11 +4923,11 @@
       </c>
       <c r="E27" s="33">
         <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.75555555555555554</v>
       </c>
       <c r="F27" s="33">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G27" s="47">
         <f t="shared" si="6"/>
@@ -4876,7 +4940,7 @@
       </c>
       <c r="B28" s="33">
         <f>Quiz!V28</f>
-        <v>0.75</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="C28" s="41">
         <f>Exams!B28</f>
@@ -4888,7 +4952,7 @@
       </c>
       <c r="E28" s="33">
         <f t="shared" si="0"/>
-        <v>0.75</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="F28" s="33">
         <f t="shared" si="5"/>
@@ -4905,7 +4969,7 @@
       </c>
       <c r="B29" s="33">
         <f>Quiz!V29</f>
-        <v>0.875</v>
+        <v>1</v>
       </c>
       <c r="C29" s="41">
         <f>Exams!B29</f>
@@ -4917,7 +4981,7 @@
       </c>
       <c r="E29" s="33">
         <f t="shared" si="0"/>
-        <v>0.875</v>
+        <v>1</v>
       </c>
       <c r="F29" s="33">
         <f t="shared" si="5"/>
@@ -4934,7 +4998,7 @@
       </c>
       <c r="B30" s="33">
         <f>Quiz!V30</f>
-        <v>0.9</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="C30" s="41">
         <f>Exams!B30</f>
@@ -4946,7 +5010,7 @@
       </c>
       <c r="E30" s="33">
         <f t="shared" si="0"/>
-        <v>0.9</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="F30" s="33">
         <f t="shared" si="5"/>
@@ -4963,7 +5027,7 @@
       </c>
       <c r="B31" s="33">
         <f>Quiz!V31</f>
-        <v>0.42499999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="C31" s="41">
         <f>Exams!B31</f>
@@ -4975,7 +5039,7 @@
       </c>
       <c r="E31" s="33">
         <f t="shared" si="0"/>
-        <v>0.42499999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="F31" s="33">
         <f t="shared" si="5"/>
@@ -4992,7 +5056,7 @@
       </c>
       <c r="B32" s="33">
         <f>Quiz!V32</f>
-        <v>0.9375</v>
+        <v>0.87777777777777777</v>
       </c>
       <c r="C32" s="41">
         <f>Exams!B32</f>
@@ -5004,7 +5068,7 @@
       </c>
       <c r="E32" s="33">
         <f t="shared" si="0"/>
-        <v>0.9375</v>
+        <v>0.87777777777777777</v>
       </c>
       <c r="F32" s="33">
         <f t="shared" si="5"/>
@@ -5050,7 +5114,7 @@
       </c>
       <c r="B34" s="33">
         <f>Quiz!V34</f>
-        <v>0.45</v>
+        <v>0.44444444444444442</v>
       </c>
       <c r="C34" s="41">
         <f>Exams!B34</f>
@@ -5062,7 +5126,7 @@
       </c>
       <c r="E34" s="33">
         <f t="shared" si="0"/>
-        <v>0.45</v>
+        <v>0.44444444444444442</v>
       </c>
       <c r="F34" s="33">
         <f t="shared" si="5"/>
@@ -5079,7 +5143,7 @@
       </c>
       <c r="B35" s="33">
         <f>Quiz!V35</f>
-        <v>0.9375</v>
+        <v>0.87777777777777777</v>
       </c>
       <c r="C35" s="41">
         <f>Exams!B35</f>
@@ -5091,7 +5155,7 @@
       </c>
       <c r="E35" s="33">
         <f t="shared" si="0"/>
-        <v>0.9375</v>
+        <v>0.87777777777777777</v>
       </c>
       <c r="F35" s="33">
         <f t="shared" si="5"/>
@@ -5108,7 +5172,7 @@
       </c>
       <c r="B36" s="33">
         <f>Quiz!V36</f>
-        <v>0.65</v>
+        <v>0.57777777777777772</v>
       </c>
       <c r="C36" s="41">
         <f>Exams!B36</f>
@@ -5120,7 +5184,7 @@
       </c>
       <c r="E36" s="33">
         <f t="shared" si="0"/>
-        <v>0.65</v>
+        <v>0.57777777777777772</v>
       </c>
       <c r="F36" s="33">
         <f t="shared" si="5"/>
@@ -5137,7 +5201,7 @@
       </c>
       <c r="B37" s="33">
         <f>Quiz!V37</f>
-        <v>1.175</v>
+        <v>1.0888888888888888</v>
       </c>
       <c r="C37" s="41">
         <f>Exams!B37</f>
@@ -5149,7 +5213,7 @@
       </c>
       <c r="E37" s="33">
         <f t="shared" si="0"/>
-        <v>1.175</v>
+        <v>1.0888888888888888</v>
       </c>
       <c r="F37" s="33">
         <f t="shared" si="5"/>
@@ -5166,7 +5230,7 @@
       </c>
       <c r="B38" s="33">
         <f>Quiz!V38</f>
-        <v>0.65</v>
+        <v>0.62222222222222223</v>
       </c>
       <c r="C38" s="41">
         <f>Exams!B38</f>
@@ -5178,7 +5242,7 @@
       </c>
       <c r="E38" s="33">
         <f t="shared" si="0"/>
-        <v>0.65</v>
+        <v>0.62222222222222223</v>
       </c>
       <c r="F38" s="33">
         <f t="shared" si="5"/>
@@ -5195,7 +5259,7 @@
       </c>
       <c r="B39" s="33">
         <f>Quiz!V39</f>
-        <v>1.05</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="C39" s="41">
         <f>Exams!B39</f>
@@ -5207,7 +5271,7 @@
       </c>
       <c r="E39" s="33">
         <f t="shared" si="0"/>
-        <v>1.05</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="F39" s="33">
         <f t="shared" ref="F39" si="8">0.5*INT(E39/0.5)+INT( ((E39-INT(E39/0.5)*0.5)/0.25))*0.5</f>
@@ -5224,7 +5288,7 @@
       </c>
       <c r="B40" s="33">
         <f>Quiz!V40</f>
-        <v>1</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="C40" s="41">
         <f>Exams!B40</f>
@@ -5236,7 +5300,7 @@
       </c>
       <c r="E40" s="33">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="F40" s="33">
         <f t="shared" si="5"/>
@@ -5289,7 +5353,7 @@
       </c>
       <c r="B43" s="29">
         <f t="shared" ref="B43:G43" si="10">AVERAGE(B$2:B$40)</f>
-        <v>0.82852564102564108</v>
+        <v>0.85954415954415964</v>
       </c>
       <c r="C43" s="29">
         <f t="shared" si="10"/>
@@ -5301,11 +5365,11 @@
       </c>
       <c r="E43" s="29">
         <f t="shared" si="10"/>
-        <v>0.82852564102564108</v>
+        <v>0.85954415954415964</v>
       </c>
       <c r="F43" s="29">
         <f t="shared" si="10"/>
-        <v>0.84615384615384615</v>
+        <v>0.88461538461538458</v>
       </c>
       <c r="G43" s="29">
         <f t="shared" si="10"/>
@@ -5318,7 +5382,7 @@
       </c>
       <c r="B44" s="29">
         <f t="shared" ref="B44:G44" si="11">STDEV(B$2:B$40)</f>
-        <v>0.3346732095940349</v>
+        <v>0.32281139098351896</v>
       </c>
       <c r="C44" s="29">
         <f t="shared" si="11"/>
@@ -5330,11 +5394,11 @@
       </c>
       <c r="E44" s="29">
         <f t="shared" si="11"/>
-        <v>0.3346732095940349</v>
+        <v>0.32281139098351896</v>
       </c>
       <c r="F44" s="29">
         <f t="shared" si="11"/>
-        <v>0.3655177681951956</v>
+        <v>0.31333390759989871</v>
       </c>
       <c r="G44" s="29">
         <f t="shared" si="11"/>
@@ -5347,7 +5411,7 @@
       </c>
       <c r="B45" s="29">
         <f t="shared" ref="B45:G45" si="12">MEDIAN(B$2:B$40)</f>
-        <v>0.85</v>
+        <v>0.87777777777777777</v>
       </c>
       <c r="C45" s="29">
         <f t="shared" si="12"/>
@@ -5359,7 +5423,7 @@
       </c>
       <c r="E45" s="29">
         <f t="shared" si="12"/>
-        <v>0.85</v>
+        <v>0.87777777777777777</v>
       </c>
       <c r="F45" s="29">
         <f t="shared" si="12"/>

--- a/phy112/Grades/grades_report_2026.xlsx
+++ b/phy112/Grades/grades_report_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ptohos/Documents/MyCourses/FYS112/2026/Grades/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28D028F9-017D-384D-BA6D-59E415A2E86D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{665692D4-BE09-D240-B91A-7590DA72E784}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1640" yWindow="680" windowWidth="32920" windowHeight="19260" tabRatio="334" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4100" yWindow="680" windowWidth="32920" windowHeight="19260" tabRatio="334" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Quiz" sheetId="1" r:id="rId1"/>
@@ -1020,7 +1020,9 @@
       <c r="K2" s="18">
         <v>20</v>
       </c>
-      <c r="L2" s="18"/>
+      <c r="L2" s="18">
+        <v>12</v>
+      </c>
       <c r="M2" s="18"/>
       <c r="N2" s="18"/>
       <c r="O2" s="18"/>
@@ -1032,7 +1034,7 @@
       <c r="U2" s="18"/>
       <c r="V2" s="33">
         <f t="shared" ref="V2:V39" si="0">$V$42 * ( (SUM(B2:U2))/((SUM($B$46:$U$46))*$B$42) )</f>
-        <v>0.97777777777777775</v>
+        <v>1</v>
       </c>
       <c r="W2"/>
     </row>
@@ -1064,7 +1066,9 @@
       <c r="K3" s="18">
         <v>4</v>
       </c>
-      <c r="L3" s="18"/>
+      <c r="L3" s="18">
+        <v>4</v>
+      </c>
       <c r="M3" s="18"/>
       <c r="N3" s="18"/>
       <c r="O3" s="18"/>
@@ -1076,7 +1080,7 @@
       <c r="U3" s="18"/>
       <c r="V3" s="33">
         <f t="shared" si="0"/>
-        <v>0.53333333333333333</v>
+        <v>0.52</v>
       </c>
       <c r="W3"/>
     </row>
@@ -1112,7 +1116,9 @@
       <c r="K4" s="18">
         <v>20</v>
       </c>
-      <c r="L4" s="18"/>
+      <c r="L4" s="18">
+        <v>12</v>
+      </c>
       <c r="M4" s="18"/>
       <c r="N4" s="18"/>
       <c r="O4" s="18"/>
@@ -1124,7 +1130,7 @@
       <c r="U4" s="18"/>
       <c r="V4" s="33">
         <f t="shared" si="0"/>
-        <v>1.1000000000000001</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="W4"/>
     </row>
@@ -1158,7 +1164,9 @@
       <c r="K5" s="18">
         <v>20</v>
       </c>
-      <c r="L5" s="18"/>
+      <c r="L5" s="18">
+        <v>4</v>
+      </c>
       <c r="M5" s="18"/>
       <c r="N5" s="18"/>
       <c r="O5" s="18"/>
@@ -1170,7 +1178,7 @@
       <c r="U5" s="18"/>
       <c r="V5" s="33">
         <f t="shared" si="0"/>
-        <v>0.62222222222222223</v>
+        <v>0.6</v>
       </c>
       <c r="W5"/>
     </row>
@@ -1206,7 +1214,9 @@
       <c r="K6" s="18">
         <v>12</v>
       </c>
-      <c r="L6" s="18"/>
+      <c r="L6" s="18">
+        <v>12</v>
+      </c>
       <c r="M6" s="18"/>
       <c r="N6" s="18"/>
       <c r="O6" s="18"/>
@@ -1218,7 +1228,7 @@
       <c r="U6" s="18"/>
       <c r="V6" s="33">
         <f t="shared" si="0"/>
-        <v>0.88888888888888884</v>
+        <v>0.92</v>
       </c>
       <c r="W6"/>
     </row>
@@ -1254,7 +1264,9 @@
       <c r="K7" s="18">
         <v>4</v>
       </c>
-      <c r="L7" s="18"/>
+      <c r="L7" s="18">
+        <v>20</v>
+      </c>
       <c r="M7" s="18"/>
       <c r="N7" s="18"/>
       <c r="O7" s="18"/>
@@ -1266,7 +1278,7 @@
       <c r="U7" s="18"/>
       <c r="V7" s="33">
         <f t="shared" si="0"/>
-        <v>1.2444444444444445</v>
+        <v>1.32</v>
       </c>
       <c r="W7"/>
     </row>
@@ -1300,7 +1312,9 @@
       <c r="K8" s="18">
         <v>20</v>
       </c>
-      <c r="L8" s="18"/>
+      <c r="L8" s="18">
+        <v>20</v>
+      </c>
       <c r="M8" s="18"/>
       <c r="N8" s="18"/>
       <c r="O8" s="18"/>
@@ -1312,7 +1326,7 @@
       <c r="U8" s="18"/>
       <c r="V8" s="33">
         <f t="shared" si="0"/>
-        <v>0.77777777777777779</v>
+        <v>0.9</v>
       </c>
       <c r="W8"/>
     </row>
@@ -1344,7 +1358,9 @@
       <c r="K9" s="18">
         <v>20</v>
       </c>
-      <c r="L9" s="18"/>
+      <c r="L9" s="18">
+        <v>20</v>
+      </c>
       <c r="M9" s="18"/>
       <c r="N9" s="18"/>
       <c r="O9" s="18"/>
@@ -1356,7 +1372,7 @@
       <c r="U9" s="18"/>
       <c r="V9" s="33">
         <f t="shared" si="0"/>
-        <v>0.84444444444444444</v>
+        <v>0.96</v>
       </c>
       <c r="W9"/>
     </row>
@@ -1386,7 +1402,9 @@
         <v>4</v>
       </c>
       <c r="K10" s="18"/>
-      <c r="L10" s="18"/>
+      <c r="L10" s="18">
+        <v>4</v>
+      </c>
       <c r="M10" s="18"/>
       <c r="N10" s="18"/>
       <c r="O10" s="18"/>
@@ -1398,7 +1416,7 @@
       <c r="U10" s="18"/>
       <c r="V10" s="33">
         <f t="shared" si="0"/>
-        <v>0.75555555555555554</v>
+        <v>0.72</v>
       </c>
       <c r="W10"/>
     </row>
@@ -1432,7 +1450,9 @@
       <c r="K11" s="18">
         <v>20</v>
       </c>
-      <c r="L11" s="18"/>
+      <c r="L11" s="18">
+        <v>20</v>
+      </c>
       <c r="M11" s="18"/>
       <c r="N11" s="18"/>
       <c r="O11" s="18"/>
@@ -1444,7 +1464,7 @@
       <c r="U11" s="18"/>
       <c r="V11" s="33">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.92</v>
       </c>
       <c r="W11"/>
     </row>
@@ -1480,7 +1500,9 @@
       <c r="K12" s="18">
         <v>4</v>
       </c>
-      <c r="L12" s="18"/>
+      <c r="L12" s="18">
+        <v>20</v>
+      </c>
       <c r="M12" s="18"/>
       <c r="N12" s="18"/>
       <c r="O12" s="18"/>
@@ -1492,7 +1514,7 @@
       <c r="U12" s="18"/>
       <c r="V12" s="33">
         <f t="shared" si="0"/>
-        <v>0.84444444444444444</v>
+        <v>0.96</v>
       </c>
       <c r="W12"/>
     </row>
@@ -1528,7 +1550,9 @@
       <c r="K13" s="18">
         <v>4</v>
       </c>
-      <c r="L13" s="18"/>
+      <c r="L13" s="18">
+        <v>20</v>
+      </c>
       <c r="M13" s="18"/>
       <c r="N13" s="18"/>
       <c r="O13" s="18"/>
@@ -1540,7 +1564,7 @@
       <c r="U13" s="18"/>
       <c r="V13" s="33">
         <f t="shared" si="0"/>
-        <v>0.77777777777777779</v>
+        <v>0.9</v>
       </c>
       <c r="W13"/>
     </row>
@@ -1576,7 +1600,9 @@
       <c r="K14" s="18">
         <v>4</v>
       </c>
-      <c r="L14" s="18"/>
+      <c r="L14" s="18">
+        <v>20</v>
+      </c>
       <c r="M14" s="18"/>
       <c r="N14" s="18"/>
       <c r="O14" s="18"/>
@@ -1588,7 +1614,7 @@
       <c r="U14" s="18"/>
       <c r="V14" s="33">
         <f t="shared" si="0"/>
-        <v>1.0444444444444445</v>
+        <v>1.1399999999999999</v>
       </c>
     </row>
     <row r="15" spans="1:23" ht="29" customHeight="1" x14ac:dyDescent="0.15">
@@ -1623,7 +1649,9 @@
       <c r="K15" s="18">
         <v>20</v>
       </c>
-      <c r="L15" s="18"/>
+      <c r="L15" s="18">
+        <v>20</v>
+      </c>
       <c r="M15" s="18"/>
       <c r="N15" s="18"/>
       <c r="O15" s="18"/>
@@ -1635,7 +1663,7 @@
       <c r="U15" s="18"/>
       <c r="V15" s="33">
         <f t="shared" si="0"/>
-        <v>1.711111111111111</v>
+        <v>1.74</v>
       </c>
       <c r="W15"/>
     </row>
@@ -1671,7 +1699,9 @@
       <c r="K16" s="18">
         <v>20</v>
       </c>
-      <c r="L16" s="18"/>
+      <c r="L16" s="18">
+        <v>20</v>
+      </c>
       <c r="M16" s="18"/>
       <c r="N16" s="18"/>
       <c r="O16" s="18"/>
@@ -1683,7 +1713,7 @@
       <c r="U16" s="18"/>
       <c r="V16" s="33">
         <f t="shared" si="0"/>
-        <v>0.9555555555555556</v>
+        <v>1.06</v>
       </c>
       <c r="W16"/>
     </row>
@@ -1745,7 +1775,9 @@
       <c r="K18" s="18">
         <v>20</v>
       </c>
-      <c r="L18" s="18"/>
+      <c r="L18" s="18">
+        <v>12</v>
+      </c>
       <c r="M18" s="18"/>
       <c r="N18" s="18"/>
       <c r="O18" s="18"/>
@@ -1757,7 +1789,7 @@
       <c r="U18" s="18"/>
       <c r="V18" s="33">
         <f t="shared" si="0"/>
-        <v>0.84444444444444444</v>
+        <v>0.88</v>
       </c>
       <c r="W18"/>
     </row>
@@ -1793,7 +1825,9 @@
       <c r="K19" s="18">
         <v>20</v>
       </c>
-      <c r="L19" s="18"/>
+      <c r="L19" s="18">
+        <v>4</v>
+      </c>
       <c r="M19" s="18"/>
       <c r="N19" s="18"/>
       <c r="O19" s="18"/>
@@ -1805,7 +1839,7 @@
       <c r="U19" s="18"/>
       <c r="V19" s="33">
         <f t="shared" si="0"/>
-        <v>1.0888888888888888</v>
+        <v>1.02</v>
       </c>
       <c r="W19"/>
     </row>
@@ -1839,7 +1873,9 @@
       <c r="K20" s="18">
         <v>20</v>
       </c>
-      <c r="L20" s="18"/>
+      <c r="L20" s="18">
+        <v>20</v>
+      </c>
       <c r="M20" s="18"/>
       <c r="N20" s="18"/>
       <c r="O20" s="18"/>
@@ -1851,7 +1887,7 @@
       <c r="U20" s="18"/>
       <c r="V20" s="33">
         <f t="shared" si="0"/>
-        <v>1.0222222222222221</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="W20"/>
     </row>
@@ -1885,7 +1921,9 @@
         <v>4</v>
       </c>
       <c r="K21" s="18"/>
-      <c r="L21" s="18"/>
+      <c r="L21" s="18">
+        <v>20</v>
+      </c>
       <c r="M21" s="18"/>
       <c r="N21" s="18"/>
       <c r="O21" s="18"/>
@@ -1897,7 +1935,7 @@
       <c r="U21" s="18"/>
       <c r="V21" s="33">
         <f t="shared" si="0"/>
-        <v>1.1555555555555554</v>
+        <v>1.24</v>
       </c>
       <c r="W21"/>
     </row>
@@ -1931,7 +1969,9 @@
       <c r="K22" s="18">
         <v>4</v>
       </c>
-      <c r="L22" s="18"/>
+      <c r="L22" s="18">
+        <v>12</v>
+      </c>
       <c r="M22" s="18"/>
       <c r="N22" s="18"/>
       <c r="O22" s="18"/>
@@ -1943,7 +1983,7 @@
       <c r="U22" s="18"/>
       <c r="V22" s="33">
         <f t="shared" si="0"/>
-        <v>0.82222222222222219</v>
+        <v>0.86</v>
       </c>
       <c r="W22"/>
     </row>
@@ -1979,7 +2019,9 @@
       <c r="K23" s="18">
         <v>20</v>
       </c>
-      <c r="L23" s="18"/>
+      <c r="L23" s="18">
+        <v>20</v>
+      </c>
       <c r="M23" s="18"/>
       <c r="N23" s="18"/>
       <c r="O23" s="18"/>
@@ -1991,7 +2033,7 @@
       <c r="U23" s="18"/>
       <c r="V23" s="33">
         <f t="shared" si="0"/>
-        <v>1.5333333333333334</v>
+        <v>1.58</v>
       </c>
       <c r="W23"/>
     </row>
@@ -2025,7 +2067,9 @@
       <c r="K24" s="18">
         <v>20</v>
       </c>
-      <c r="L24" s="18"/>
+      <c r="L24" s="18">
+        <v>20</v>
+      </c>
       <c r="M24" s="18"/>
       <c r="N24" s="18"/>
       <c r="O24" s="18"/>
@@ -2037,7 +2081,7 @@
       <c r="U24" s="18"/>
       <c r="V24" s="33">
         <f t="shared" si="0"/>
-        <v>1.0222222222222221</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="W24"/>
     </row>
@@ -2069,7 +2113,9 @@
       <c r="K25" s="18">
         <v>20</v>
       </c>
-      <c r="L25" s="18"/>
+      <c r="L25" s="18">
+        <v>20</v>
+      </c>
       <c r="M25" s="18"/>
       <c r="N25" s="18"/>
       <c r="O25" s="18"/>
@@ -2081,7 +2127,7 @@
       <c r="U25" s="18"/>
       <c r="V25" s="33">
         <f t="shared" si="0"/>
-        <v>1.1333333333333333</v>
+        <v>1.22</v>
       </c>
       <c r="W25"/>
     </row>
@@ -2117,7 +2163,9 @@
       <c r="K26" s="18">
         <v>4</v>
       </c>
-      <c r="L26" s="18"/>
+      <c r="L26" s="18">
+        <v>4</v>
+      </c>
       <c r="M26" s="18"/>
       <c r="N26" s="18"/>
       <c r="O26" s="18"/>
@@ -2129,7 +2177,7 @@
       <c r="U26" s="18"/>
       <c r="V26" s="33">
         <f t="shared" si="0"/>
-        <v>0.53333333333333333</v>
+        <v>0.52</v>
       </c>
       <c r="W26"/>
     </row>
@@ -2161,7 +2209,9 @@
       <c r="K27" s="18">
         <v>20</v>
       </c>
-      <c r="L27" s="18"/>
+      <c r="L27" s="18">
+        <v>12</v>
+      </c>
       <c r="M27" s="18"/>
       <c r="N27" s="18"/>
       <c r="O27" s="18"/>
@@ -2173,7 +2223,7 @@
       <c r="U27" s="18"/>
       <c r="V27" s="33">
         <f t="shared" si="0"/>
-        <v>0.75555555555555554</v>
+        <v>0.8</v>
       </c>
       <c r="W27"/>
     </row>
@@ -2207,7 +2257,9 @@
       <c r="K28" s="18">
         <v>20</v>
       </c>
-      <c r="L28" s="18"/>
+      <c r="L28" s="18">
+        <v>12</v>
+      </c>
       <c r="M28" s="18"/>
       <c r="N28" s="18"/>
       <c r="O28" s="18"/>
@@ -2219,7 +2271,7 @@
       <c r="U28" s="18"/>
       <c r="V28" s="33">
         <f t="shared" si="0"/>
-        <v>0.88888888888888884</v>
+        <v>0.92</v>
       </c>
       <c r="W28"/>
     </row>
@@ -2255,7 +2307,9 @@
       <c r="K29" s="18">
         <v>20</v>
       </c>
-      <c r="L29" s="18"/>
+      <c r="L29" s="18">
+        <v>4</v>
+      </c>
       <c r="M29" s="18"/>
       <c r="N29" s="18"/>
       <c r="O29" s="18"/>
@@ -2267,7 +2321,7 @@
       <c r="U29" s="18"/>
       <c r="V29" s="33">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.94</v>
       </c>
       <c r="W29"/>
     </row>
@@ -2303,7 +2357,9 @@
       <c r="K30" s="18">
         <v>12</v>
       </c>
-      <c r="L30" s="18"/>
+      <c r="L30" s="18">
+        <v>20</v>
+      </c>
       <c r="M30" s="18"/>
       <c r="N30" s="18"/>
       <c r="O30" s="18"/>
@@ -2315,7 +2371,7 @@
       <c r="U30" s="18"/>
       <c r="V30" s="33">
         <f t="shared" si="0"/>
-        <v>0.93333333333333335</v>
+        <v>1.04</v>
       </c>
       <c r="W30"/>
     </row>
@@ -2347,7 +2403,9 @@
       <c r="K31" s="18">
         <v>20</v>
       </c>
-      <c r="L31" s="18"/>
+      <c r="L31" s="18">
+        <v>4</v>
+      </c>
       <c r="M31" s="18"/>
       <c r="N31" s="18"/>
       <c r="O31" s="18"/>
@@ -2359,7 +2417,7 @@
       <c r="U31" s="18"/>
       <c r="V31" s="33">
         <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="W31"/>
     </row>
@@ -2395,7 +2453,9 @@
       <c r="K32" s="18">
         <v>4</v>
       </c>
-      <c r="L32" s="18"/>
+      <c r="L32" s="18">
+        <v>20</v>
+      </c>
       <c r="M32" s="18"/>
       <c r="N32" s="18"/>
       <c r="O32" s="18"/>
@@ -2407,7 +2467,7 @@
       <c r="U32" s="18"/>
       <c r="V32" s="33">
         <f t="shared" si="0"/>
-        <v>0.87777777777777777</v>
+        <v>0.99</v>
       </c>
       <c r="W32"/>
     </row>
@@ -2467,7 +2527,9 @@
       <c r="K34" s="18">
         <v>4</v>
       </c>
-      <c r="L34" s="18"/>
+      <c r="L34" s="18">
+        <v>4</v>
+      </c>
       <c r="M34" s="18"/>
       <c r="N34" s="18"/>
       <c r="O34" s="18"/>
@@ -2479,7 +2541,7 @@
       <c r="U34" s="18"/>
       <c r="V34" s="33">
         <f t="shared" si="0"/>
-        <v>0.44444444444444442</v>
+        <v>0.44</v>
       </c>
       <c r="W34"/>
     </row>
@@ -2515,7 +2577,9 @@
       <c r="K35" s="18">
         <v>4</v>
       </c>
-      <c r="L35" s="18"/>
+      <c r="L35" s="18">
+        <v>20</v>
+      </c>
       <c r="M35" s="18"/>
       <c r="N35" s="18"/>
       <c r="O35" s="18"/>
@@ -2527,7 +2591,7 @@
       <c r="U35" s="18"/>
       <c r="V35" s="33">
         <f t="shared" si="0"/>
-        <v>0.87777777777777777</v>
+        <v>0.99</v>
       </c>
       <c r="W35"/>
     </row>
@@ -2555,7 +2619,9 @@
         <v>12</v>
       </c>
       <c r="K36" s="18"/>
-      <c r="L36" s="18"/>
+      <c r="L36" s="18">
+        <v>4</v>
+      </c>
       <c r="M36" s="18"/>
       <c r="N36" s="18"/>
       <c r="O36" s="18"/>
@@ -2567,7 +2633,7 @@
       <c r="U36" s="18"/>
       <c r="V36" s="33">
         <f t="shared" si="0"/>
-        <v>0.57777777777777772</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="W36"/>
     </row>
@@ -2603,7 +2669,9 @@
       <c r="K37" s="18">
         <v>4</v>
       </c>
-      <c r="L37" s="18"/>
+      <c r="L37" s="18">
+        <v>20</v>
+      </c>
       <c r="M37" s="18"/>
       <c r="N37" s="18"/>
       <c r="O37" s="18"/>
@@ -2615,7 +2683,7 @@
       <c r="U37" s="18"/>
       <c r="V37" s="33">
         <f t="shared" si="0"/>
-        <v>1.0888888888888888</v>
+        <v>1.18</v>
       </c>
       <c r="W37"/>
     </row>
@@ -2657,7 +2725,7 @@
       <c r="U38" s="18"/>
       <c r="V38" s="33">
         <f t="shared" si="0"/>
-        <v>0.62222222222222223</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="W38"/>
     </row>
@@ -2691,7 +2759,9 @@
         <v>4</v>
       </c>
       <c r="K39" s="18"/>
-      <c r="L39" s="18"/>
+      <c r="L39" s="18">
+        <v>20</v>
+      </c>
       <c r="M39" s="18"/>
       <c r="N39" s="18"/>
       <c r="O39" s="18"/>
@@ -2703,7 +2773,7 @@
       <c r="U39" s="18"/>
       <c r="V39" s="33">
         <f t="shared" si="0"/>
-        <v>0.93333333333333335</v>
+        <v>1.04</v>
       </c>
       <c r="W39"/>
     </row>
@@ -2735,7 +2805,9 @@
         <v>4</v>
       </c>
       <c r="K40" s="18"/>
-      <c r="L40" s="18"/>
+      <c r="L40" s="18">
+        <v>4</v>
+      </c>
       <c r="M40" s="18"/>
       <c r="N40" s="18"/>
       <c r="O40" s="18"/>
@@ -2747,7 +2819,7 @@
       <c r="U40" s="18"/>
       <c r="V40" s="33">
         <f t="shared" ref="V40" si="1">$V$42 * ( (SUM(B40:U40))/((SUM($B$46:$U$46))*$B$42) )</f>
-        <v>0.88888888888888884</v>
+        <v>0.84</v>
       </c>
       <c r="W40"/>
     </row>
@@ -2889,9 +2961,9 @@
         <f t="shared" si="2"/>
         <v>13.5</v>
       </c>
-      <c r="L43" s="29" t="e">
+      <c r="L43" s="29">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+        <v>14.285714285714286</v>
       </c>
       <c r="M43" s="29" t="e">
         <f t="shared" si="2"/>
@@ -2931,7 +3003,7 @@
       </c>
       <c r="V43" s="29">
         <f t="shared" si="2"/>
-        <v>0.85877192982456163</v>
+        <v>0.90447368421052621</v>
       </c>
       <c r="W43"/>
     </row>
@@ -2979,9 +3051,9 @@
         <f t="shared" si="3"/>
         <v>7.7209392709570279</v>
       </c>
-      <c r="L44" s="29" t="e">
+      <c r="L44" s="29">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
+        <v>6.8795153239481177</v>
       </c>
       <c r="M44" s="29" t="e">
         <f t="shared" si="3"/>
@@ -3021,7 +3093,7 @@
       </c>
       <c r="V44" s="29">
         <f t="shared" si="3"/>
-        <v>0.32710811518099425</v>
+        <v>0.35037969650251599</v>
       </c>
       <c r="W44"/>
     </row>
@@ -3069,9 +3141,9 @@
         <f t="shared" si="4"/>
         <v>20</v>
       </c>
-      <c r="L45" s="29" t="e">
+      <c r="L45" s="29">
         <f t="shared" si="4"/>
-        <v>#NUM!</v>
+        <v>20</v>
       </c>
       <c r="M45" s="29" t="e">
         <f t="shared" si="4"/>
@@ -3111,7 +3183,7 @@
       </c>
       <c r="V45" s="29">
         <f t="shared" si="4"/>
-        <v>0.87777777777777777</v>
+        <v>0.95</v>
       </c>
       <c r="W45"/>
     </row>
@@ -3161,7 +3233,7 @@
       </c>
       <c r="L46" s="32">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M46" s="32">
         <f t="shared" si="5"/>
@@ -4185,7 +4257,7 @@
       </c>
       <c r="B2" s="33">
         <f>Quiz!V2</f>
-        <v>0.97777777777777775</v>
+        <v>1</v>
       </c>
       <c r="C2" s="41">
         <f>Exams!B2</f>
@@ -4197,7 +4269,7 @@
       </c>
       <c r="E2" s="33">
         <f>$B2+($C2/$C$42)*3.5+($D2/$D$42)*4.5</f>
-        <v>0.97777777777777775</v>
+        <v>1</v>
       </c>
       <c r="F2" s="33">
         <f>0.5*INT(E2/0.5)+INT( ((E2-INT(E2/0.5)*0.5)/0.25))*0.5</f>
@@ -4215,7 +4287,7 @@
       </c>
       <c r="B3" s="33">
         <f>Quiz!V3</f>
-        <v>0.53333333333333333</v>
+        <v>0.52</v>
       </c>
       <c r="C3" s="41">
         <f>Exams!B3</f>
@@ -4227,7 +4299,7 @@
       </c>
       <c r="E3" s="33">
         <f t="shared" ref="E3:E40" si="0">$B3+($C3/$C$42)*3.5+($D3/$D$42)*4.5</f>
-        <v>0.53333333333333333</v>
+        <v>0.52</v>
       </c>
       <c r="F3" s="33">
         <f t="shared" ref="F3:F19" si="1">0.5*INT(E3/0.5)+INT( ((E3-INT(E3/0.5)*0.5)/0.25))*0.5</f>
@@ -4244,7 +4316,7 @@
       </c>
       <c r="B4" s="33">
         <f>Quiz!V4</f>
-        <v>1.1000000000000001</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="C4" s="41">
         <f>Exams!B4</f>
@@ -4256,7 +4328,7 @@
       </c>
       <c r="E4" s="33">
         <f t="shared" si="0"/>
-        <v>1.1000000000000001</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="F4" s="33">
         <f t="shared" si="1"/>
@@ -4273,7 +4345,7 @@
       </c>
       <c r="B5" s="33">
         <f>Quiz!V5</f>
-        <v>0.62222222222222223</v>
+        <v>0.6</v>
       </c>
       <c r="C5" s="41">
         <f>Exams!B5</f>
@@ -4285,7 +4357,7 @@
       </c>
       <c r="E5" s="33">
         <f t="shared" si="0"/>
-        <v>0.62222222222222223</v>
+        <v>0.6</v>
       </c>
       <c r="F5" s="33">
         <f t="shared" si="1"/>
@@ -4302,7 +4374,7 @@
       </c>
       <c r="B6" s="33">
         <f>Quiz!V6</f>
-        <v>0.88888888888888884</v>
+        <v>0.92</v>
       </c>
       <c r="C6" s="41">
         <f>Exams!B6</f>
@@ -4314,7 +4386,7 @@
       </c>
       <c r="E6" s="33">
         <f t="shared" si="0"/>
-        <v>0.88888888888888884</v>
+        <v>0.92</v>
       </c>
       <c r="F6" s="33">
         <f t="shared" si="1"/>
@@ -4331,7 +4403,7 @@
       </c>
       <c r="B7" s="33">
         <f>Quiz!V7</f>
-        <v>1.2444444444444445</v>
+        <v>1.32</v>
       </c>
       <c r="C7" s="41">
         <f>Exams!B7</f>
@@ -4343,11 +4415,11 @@
       </c>
       <c r="E7" s="33">
         <f t="shared" si="0"/>
-        <v>1.2444444444444445</v>
+        <v>1.32</v>
       </c>
       <c r="F7" s="33">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G7" s="47">
         <f t="shared" si="2"/>
@@ -4360,7 +4432,7 @@
       </c>
       <c r="B8" s="33">
         <f>Quiz!V8</f>
-        <v>0.77777777777777779</v>
+        <v>0.9</v>
       </c>
       <c r="C8" s="41">
         <f>Exams!B8</f>
@@ -4372,7 +4444,7 @@
       </c>
       <c r="E8" s="33">
         <f t="shared" si="0"/>
-        <v>0.77777777777777779</v>
+        <v>0.9</v>
       </c>
       <c r="F8" s="33">
         <f t="shared" si="1"/>
@@ -4389,7 +4461,7 @@
       </c>
       <c r="B9" s="33">
         <f>Quiz!V9</f>
-        <v>0.84444444444444444</v>
+        <v>0.96</v>
       </c>
       <c r="C9" s="41">
         <f>Exams!B9</f>
@@ -4401,7 +4473,7 @@
       </c>
       <c r="E9" s="33">
         <f t="shared" si="0"/>
-        <v>0.84444444444444444</v>
+        <v>0.96</v>
       </c>
       <c r="F9" s="33">
         <f t="shared" si="1"/>
@@ -4418,7 +4490,7 @@
       </c>
       <c r="B10" s="33">
         <f>Quiz!V10</f>
-        <v>0.75555555555555554</v>
+        <v>0.72</v>
       </c>
       <c r="C10" s="41">
         <f>Exams!B10</f>
@@ -4430,11 +4502,11 @@
       </c>
       <c r="E10" s="33">
         <f t="shared" si="0"/>
-        <v>0.75555555555555554</v>
+        <v>0.72</v>
       </c>
       <c r="F10" s="33">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G10" s="47">
         <f t="shared" si="2"/>
@@ -4447,7 +4519,7 @@
       </c>
       <c r="B11" s="33">
         <f>Quiz!V11</f>
-        <v>0.8</v>
+        <v>0.92</v>
       </c>
       <c r="C11" s="41">
         <f>Exams!B11</f>
@@ -4459,7 +4531,7 @@
       </c>
       <c r="E11" s="33">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.92</v>
       </c>
       <c r="F11" s="33">
         <f t="shared" si="1"/>
@@ -4476,7 +4548,7 @@
       </c>
       <c r="B12" s="33">
         <f>Quiz!V12</f>
-        <v>0.84444444444444444</v>
+        <v>0.96</v>
       </c>
       <c r="C12" s="41">
         <f>Exams!B12</f>
@@ -4488,7 +4560,7 @@
       </c>
       <c r="E12" s="33">
         <f t="shared" si="0"/>
-        <v>0.84444444444444444</v>
+        <v>0.96</v>
       </c>
       <c r="F12" s="33">
         <f t="shared" si="1"/>
@@ -4505,7 +4577,7 @@
       </c>
       <c r="B13" s="33">
         <f>Quiz!V13</f>
-        <v>0.77777777777777779</v>
+        <v>0.9</v>
       </c>
       <c r="C13" s="41">
         <f>Exams!B13</f>
@@ -4517,7 +4589,7 @@
       </c>
       <c r="E13" s="33">
         <f t="shared" si="0"/>
-        <v>0.77777777777777779</v>
+        <v>0.9</v>
       </c>
       <c r="F13" s="33">
         <f t="shared" si="1"/>
@@ -4534,7 +4606,7 @@
       </c>
       <c r="B14" s="33">
         <f>Quiz!V14</f>
-        <v>1.0444444444444445</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="C14" s="41">
         <f>Exams!B14</f>
@@ -4546,7 +4618,7 @@
       </c>
       <c r="E14" s="33">
         <f t="shared" si="0"/>
-        <v>1.0444444444444445</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="F14" s="33">
         <f t="shared" si="1"/>
@@ -4563,7 +4635,7 @@
       </c>
       <c r="B15" s="33">
         <f>Quiz!V15</f>
-        <v>1.711111111111111</v>
+        <v>1.74</v>
       </c>
       <c r="C15" s="41">
         <f>Exams!B15</f>
@@ -4575,7 +4647,7 @@
       </c>
       <c r="E15" s="33">
         <f t="shared" si="0"/>
-        <v>1.711111111111111</v>
+        <v>1.74</v>
       </c>
       <c r="F15" s="33">
         <f t="shared" si="1"/>
@@ -4592,7 +4664,7 @@
       </c>
       <c r="B16" s="33">
         <f>Quiz!V16</f>
-        <v>0.9555555555555556</v>
+        <v>1.06</v>
       </c>
       <c r="C16" s="41">
         <f>Exams!B16</f>
@@ -4604,7 +4676,7 @@
       </c>
       <c r="E16" s="33">
         <f t="shared" si="0"/>
-        <v>0.9555555555555556</v>
+        <v>1.06</v>
       </c>
       <c r="F16" s="33">
         <f t="shared" si="1"/>
@@ -4650,7 +4722,7 @@
       </c>
       <c r="B18" s="33">
         <f>Quiz!V18</f>
-        <v>0.84444444444444444</v>
+        <v>0.88</v>
       </c>
       <c r="C18" s="41">
         <f>Exams!B18</f>
@@ -4662,7 +4734,7 @@
       </c>
       <c r="E18" s="33">
         <f t="shared" si="0"/>
-        <v>0.84444444444444444</v>
+        <v>0.88</v>
       </c>
       <c r="F18" s="33">
         <f t="shared" si="1"/>
@@ -4679,7 +4751,7 @@
       </c>
       <c r="B19" s="33">
         <f>Quiz!V19</f>
-        <v>1.0888888888888888</v>
+        <v>1.02</v>
       </c>
       <c r="C19" s="41">
         <f>Exams!B19</f>
@@ -4691,7 +4763,7 @@
       </c>
       <c r="E19" s="33">
         <f t="shared" si="0"/>
-        <v>1.0888888888888888</v>
+        <v>1.02</v>
       </c>
       <c r="F19" s="33">
         <f t="shared" si="1"/>
@@ -4708,7 +4780,7 @@
       </c>
       <c r="B20" s="33">
         <f>Quiz!V20</f>
-        <v>1.0222222222222221</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="C20" s="41">
         <f>Exams!B20</f>
@@ -4720,7 +4792,7 @@
       </c>
       <c r="E20" s="33">
         <f t="shared" si="0"/>
-        <v>1.0222222222222221</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="F20" s="33">
         <f t="shared" ref="F20:F25" si="3">0.5*INT(E20/0.5)+INT( ((E20-INT(E20/0.5)*0.5)/0.25))*0.5</f>
@@ -4737,7 +4809,7 @@
       </c>
       <c r="B21" s="33">
         <f>Quiz!V21</f>
-        <v>1.1555555555555554</v>
+        <v>1.24</v>
       </c>
       <c r="C21" s="41">
         <f>Exams!B21</f>
@@ -4749,7 +4821,7 @@
       </c>
       <c r="E21" s="33">
         <f t="shared" si="0"/>
-        <v>1.1555555555555554</v>
+        <v>1.24</v>
       </c>
       <c r="F21" s="33">
         <f t="shared" si="3"/>
@@ -4766,7 +4838,7 @@
       </c>
       <c r="B22" s="33">
         <f>Quiz!V22</f>
-        <v>0.82222222222222219</v>
+        <v>0.86</v>
       </c>
       <c r="C22" s="41">
         <f>Exams!B22</f>
@@ -4778,7 +4850,7 @@
       </c>
       <c r="E22" s="33">
         <f t="shared" si="0"/>
-        <v>0.82222222222222219</v>
+        <v>0.86</v>
       </c>
       <c r="F22" s="33">
         <f t="shared" si="3"/>
@@ -4795,7 +4867,7 @@
       </c>
       <c r="B23" s="33">
         <f>Quiz!V23</f>
-        <v>1.5333333333333334</v>
+        <v>1.58</v>
       </c>
       <c r="C23" s="41">
         <f>Exams!B23</f>
@@ -4807,7 +4879,7 @@
       </c>
       <c r="E23" s="33">
         <f t="shared" si="0"/>
-        <v>1.5333333333333334</v>
+        <v>1.58</v>
       </c>
       <c r="F23" s="33">
         <f t="shared" si="3"/>
@@ -4824,7 +4896,7 @@
       </c>
       <c r="B24" s="33">
         <f>Quiz!V24</f>
-        <v>1.0222222222222221</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="C24" s="41">
         <f>Exams!B24</f>
@@ -4836,7 +4908,7 @@
       </c>
       <c r="E24" s="33">
         <f t="shared" si="0"/>
-        <v>1.0222222222222221</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="F24" s="33">
         <f t="shared" si="3"/>
@@ -4853,7 +4925,7 @@
       </c>
       <c r="B25" s="33">
         <f>Quiz!V25</f>
-        <v>1.1333333333333333</v>
+        <v>1.22</v>
       </c>
       <c r="C25" s="41">
         <f>Exams!B25</f>
@@ -4865,7 +4937,7 @@
       </c>
       <c r="E25" s="33">
         <f t="shared" si="0"/>
-        <v>1.1333333333333333</v>
+        <v>1.22</v>
       </c>
       <c r="F25" s="33">
         <f t="shared" si="3"/>
@@ -4882,7 +4954,7 @@
       </c>
       <c r="B26" s="33">
         <f>Quiz!V26</f>
-        <v>0.53333333333333333</v>
+        <v>0.52</v>
       </c>
       <c r="C26" s="41">
         <f>Exams!B26</f>
@@ -4894,7 +4966,7 @@
       </c>
       <c r="E26" s="33">
         <f t="shared" si="0"/>
-        <v>0.53333333333333333</v>
+        <v>0.52</v>
       </c>
       <c r="F26" s="33">
         <f t="shared" ref="F26:F40" si="5">0.5*INT(E26/0.5)+INT( ((E26-INT(E26/0.5)*0.5)/0.25))*0.5</f>
@@ -4911,7 +4983,7 @@
       </c>
       <c r="B27" s="33">
         <f>Quiz!V27</f>
-        <v>0.75555555555555554</v>
+        <v>0.8</v>
       </c>
       <c r="C27" s="41">
         <f>Exams!B27</f>
@@ -4923,7 +4995,7 @@
       </c>
       <c r="E27" s="33">
         <f t="shared" si="0"/>
-        <v>0.75555555555555554</v>
+        <v>0.8</v>
       </c>
       <c r="F27" s="33">
         <f t="shared" si="5"/>
@@ -4940,7 +5012,7 @@
       </c>
       <c r="B28" s="33">
         <f>Quiz!V28</f>
-        <v>0.88888888888888884</v>
+        <v>0.92</v>
       </c>
       <c r="C28" s="41">
         <f>Exams!B28</f>
@@ -4952,7 +5024,7 @@
       </c>
       <c r="E28" s="33">
         <f t="shared" si="0"/>
-        <v>0.88888888888888884</v>
+        <v>0.92</v>
       </c>
       <c r="F28" s="33">
         <f t="shared" si="5"/>
@@ -4969,7 +5041,7 @@
       </c>
       <c r="B29" s="33">
         <f>Quiz!V29</f>
-        <v>1</v>
+        <v>0.94</v>
       </c>
       <c r="C29" s="41">
         <f>Exams!B29</f>
@@ -4981,7 +5053,7 @@
       </c>
       <c r="E29" s="33">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.94</v>
       </c>
       <c r="F29" s="33">
         <f t="shared" si="5"/>
@@ -4998,7 +5070,7 @@
       </c>
       <c r="B30" s="33">
         <f>Quiz!V30</f>
-        <v>0.93333333333333335</v>
+        <v>1.04</v>
       </c>
       <c r="C30" s="41">
         <f>Exams!B30</f>
@@ -5010,7 +5082,7 @@
       </c>
       <c r="E30" s="33">
         <f t="shared" si="0"/>
-        <v>0.93333333333333335</v>
+        <v>1.04</v>
       </c>
       <c r="F30" s="33">
         <f t="shared" si="5"/>
@@ -5027,7 +5099,7 @@
       </c>
       <c r="B31" s="33">
         <f>Quiz!V31</f>
-        <v>0.6</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="C31" s="41">
         <f>Exams!B31</f>
@@ -5039,7 +5111,7 @@
       </c>
       <c r="E31" s="33">
         <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="F31" s="33">
         <f t="shared" si="5"/>
@@ -5056,7 +5128,7 @@
       </c>
       <c r="B32" s="33">
         <f>Quiz!V32</f>
-        <v>0.87777777777777777</v>
+        <v>0.99</v>
       </c>
       <c r="C32" s="41">
         <f>Exams!B32</f>
@@ -5068,7 +5140,7 @@
       </c>
       <c r="E32" s="33">
         <f t="shared" si="0"/>
-        <v>0.87777777777777777</v>
+        <v>0.99</v>
       </c>
       <c r="F32" s="33">
         <f t="shared" si="5"/>
@@ -5114,7 +5186,7 @@
       </c>
       <c r="B34" s="33">
         <f>Quiz!V34</f>
-        <v>0.44444444444444442</v>
+        <v>0.44</v>
       </c>
       <c r="C34" s="41">
         <f>Exams!B34</f>
@@ -5126,7 +5198,7 @@
       </c>
       <c r="E34" s="33">
         <f t="shared" si="0"/>
-        <v>0.44444444444444442</v>
+        <v>0.44</v>
       </c>
       <c r="F34" s="33">
         <f t="shared" si="5"/>
@@ -5143,7 +5215,7 @@
       </c>
       <c r="B35" s="33">
         <f>Quiz!V35</f>
-        <v>0.87777777777777777</v>
+        <v>0.99</v>
       </c>
       <c r="C35" s="41">
         <f>Exams!B35</f>
@@ -5155,7 +5227,7 @@
       </c>
       <c r="E35" s="33">
         <f t="shared" si="0"/>
-        <v>0.87777777777777777</v>
+        <v>0.99</v>
       </c>
       <c r="F35" s="33">
         <f t="shared" si="5"/>
@@ -5172,7 +5244,7 @@
       </c>
       <c r="B36" s="33">
         <f>Quiz!V36</f>
-        <v>0.57777777777777772</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="C36" s="41">
         <f>Exams!B36</f>
@@ -5184,7 +5256,7 @@
       </c>
       <c r="E36" s="33">
         <f t="shared" si="0"/>
-        <v>0.57777777777777772</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="F36" s="33">
         <f t="shared" si="5"/>
@@ -5201,7 +5273,7 @@
       </c>
       <c r="B37" s="33">
         <f>Quiz!V37</f>
-        <v>1.0888888888888888</v>
+        <v>1.18</v>
       </c>
       <c r="C37" s="41">
         <f>Exams!B37</f>
@@ -5213,7 +5285,7 @@
       </c>
       <c r="E37" s="33">
         <f t="shared" si="0"/>
-        <v>1.0888888888888888</v>
+        <v>1.18</v>
       </c>
       <c r="F37" s="33">
         <f t="shared" si="5"/>
@@ -5230,7 +5302,7 @@
       </c>
       <c r="B38" s="33">
         <f>Quiz!V38</f>
-        <v>0.62222222222222223</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="C38" s="41">
         <f>Exams!B38</f>
@@ -5242,7 +5314,7 @@
       </c>
       <c r="E38" s="33">
         <f t="shared" si="0"/>
-        <v>0.62222222222222223</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="F38" s="33">
         <f t="shared" si="5"/>
@@ -5259,7 +5331,7 @@
       </c>
       <c r="B39" s="33">
         <f>Quiz!V39</f>
-        <v>0.93333333333333335</v>
+        <v>1.04</v>
       </c>
       <c r="C39" s="41">
         <f>Exams!B39</f>
@@ -5271,7 +5343,7 @@
       </c>
       <c r="E39" s="33">
         <f t="shared" si="0"/>
-        <v>0.93333333333333335</v>
+        <v>1.04</v>
       </c>
       <c r="F39" s="33">
         <f t="shared" ref="F39" si="8">0.5*INT(E39/0.5)+INT( ((E39-INT(E39/0.5)*0.5)/0.25))*0.5</f>
@@ -5288,7 +5360,7 @@
       </c>
       <c r="B40" s="33">
         <f>Quiz!V40</f>
-        <v>0.88888888888888884</v>
+        <v>0.84</v>
       </c>
       <c r="C40" s="41">
         <f>Exams!B40</f>
@@ -5300,7 +5372,7 @@
       </c>
       <c r="E40" s="33">
         <f t="shared" si="0"/>
-        <v>0.88888888888888884</v>
+        <v>0.84</v>
       </c>
       <c r="F40" s="33">
         <f t="shared" si="5"/>
@@ -5353,7 +5425,7 @@
       </c>
       <c r="B43" s="29">
         <f t="shared" ref="B43:G43" si="10">AVERAGE(B$2:B$40)</f>
-        <v>0.85954415954415964</v>
+        <v>0.90282051282051279</v>
       </c>
       <c r="C43" s="29">
         <f t="shared" si="10"/>
@@ -5365,7 +5437,7 @@
       </c>
       <c r="E43" s="29">
         <f t="shared" si="10"/>
-        <v>0.85954415954415964</v>
+        <v>0.90282051282051279</v>
       </c>
       <c r="F43" s="29">
         <f t="shared" si="10"/>
@@ -5382,7 +5454,7 @@
       </c>
       <c r="B44" s="29">
         <f t="shared" ref="B44:G44" si="11">STDEV(B$2:B$40)</f>
-        <v>0.32281139098351896</v>
+        <v>0.34589280905740855</v>
       </c>
       <c r="C44" s="29">
         <f t="shared" si="11"/>
@@ -5394,11 +5466,11 @@
       </c>
       <c r="E44" s="29">
         <f t="shared" si="11"/>
-        <v>0.32281139098351896</v>
+        <v>0.34589280905740855</v>
       </c>
       <c r="F44" s="29">
         <f t="shared" si="11"/>
-        <v>0.31333390759989871</v>
+        <v>0.33367054468242163</v>
       </c>
       <c r="G44" s="29">
         <f t="shared" si="11"/>
@@ -5411,7 +5483,7 @@
       </c>
       <c r="B45" s="29">
         <f t="shared" ref="B45:G45" si="12">MEDIAN(B$2:B$40)</f>
-        <v>0.87777777777777777</v>
+        <v>0.94</v>
       </c>
       <c r="C45" s="29">
         <f t="shared" si="12"/>
@@ -5423,7 +5495,7 @@
       </c>
       <c r="E45" s="29">
         <f t="shared" si="12"/>
-        <v>0.87777777777777777</v>
+        <v>0.94</v>
       </c>
       <c r="F45" s="29">
         <f t="shared" si="12"/>
